--- a/TOR330 Data/5. Clean Data for Data Visualisation/TOR330_negative_duration_checkpoints_bib_df.xlsx
+++ b/TOR330 Data/5. Clean Data for Data Visualisation/TOR330_negative_duration_checkpoints_bib_df.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="65">
   <si>
     <t>PK</t>
   </si>
@@ -85,6 +85,9 @@
     <t>Missed Diff_seconds</t>
   </si>
   <si>
+    <t>Retired_Detail</t>
+  </si>
+  <si>
     <t>TOR330_2023_334</t>
   </si>
   <si>
@@ -100,36 +103,66 @@
     <t>TOR330_2023_1334</t>
   </si>
   <si>
-    <t>2023</t>
+    <t>TOR330_2024_404</t>
+  </si>
+  <si>
+    <t>TOR330_2024_1367</t>
+  </si>
+  <si>
+    <t>TOR330_2022_275</t>
+  </si>
+  <si>
+    <t>TOR330_2022_127</t>
+  </si>
+  <si>
+    <t>TOR330_2022_549</t>
+  </si>
+  <si>
+    <t>TOR330_2022_1005</t>
+  </si>
+  <si>
+    <t>TOR330_2022_1205</t>
+  </si>
+  <si>
+    <t>TOR330_2022_1268</t>
+  </si>
+  <si>
+    <t>TOR330_2021_162</t>
+  </si>
+  <si>
+    <t>2021</t>
   </si>
   <si>
     <t>TOR330</t>
   </si>
   <si>
-    <t>334</t>
-  </si>
-  <si>
-    <t>343</t>
-  </si>
-  <si>
-    <t>1291</t>
-  </si>
-  <si>
-    <t>423</t>
-  </si>
-  <si>
-    <t>1334</t>
+    <t>162</t>
   </si>
   <si>
     <t>Finished at Courmayeur</t>
   </si>
   <si>
+    <t>DNF</t>
+  </si>
+  <si>
+    <t>Finished at Bosses</t>
+  </si>
+  <si>
+    <t>Finished at Rifugio Frassati</t>
+  </si>
+  <si>
+    <t>Cogne</t>
+  </si>
+  <si>
     <t>Wave1</t>
   </si>
   <si>
     <t>Wave2</t>
   </si>
   <si>
+    <t>No Wave in 2021</t>
+  </si>
+  <si>
     <t>Donnas IN</t>
   </si>
   <si>
@@ -142,6 +175,9 @@
     <t>Ollomont OUT</t>
   </si>
   <si>
+    <t>Valtournenche OUT</t>
+  </si>
+  <si>
     <t>Sub-130</t>
   </si>
   <si>
@@ -151,6 +187,12 @@
     <t>Sub-150</t>
   </si>
   <si>
+    <t>Sub-90</t>
+  </si>
+  <si>
+    <t>Sub-100</t>
+  </si>
+  <si>
     <t>Stage 3</t>
   </si>
   <si>
@@ -161,6 +203,9 @@
   </si>
   <si>
     <t>Time Spent in Ollomont</t>
+  </si>
+  <si>
+    <t>Time Spent in Valtournenche</t>
   </si>
   <si>
     <t>Within Allocated Time</t>
@@ -526,10 +571,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W6"/>
+  <dimension ref="A1:X65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:24">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -599,45 +644,48 @@
       <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:23">
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24">
       <c r="A2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" t="s">
-        <v>28</v>
+        <v>24</v>
+      </c>
+      <c r="B2">
+        <v>2023</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2" t="s">
-        <v>30</v>
+        <v>39</v>
+      </c>
+      <c r="D2">
+        <v>334</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H2" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I2" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="J2" s="2">
         <v>45180.90565972222</v>
       </c>
       <c r="K2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L2" s="3">
+        <v>54</v>
+      </c>
+      <c r="L2">
         <v>-0.05702546296296297</v>
       </c>
       <c r="M2">
         <v>-4927</v>
       </c>
-      <c r="N2" s="3">
+      <c r="N2">
         <v>1.488993055555556</v>
       </c>
       <c r="O2">
@@ -647,59 +695,59 @@
         <v>45182</v>
       </c>
       <c r="Q2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="R2" t="b">
         <v>0</v>
       </c>
-      <c r="S2" s="3">
+      <c r="S2">
         <v>0.75</v>
       </c>
       <c r="T2" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="U2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:23">
+    <row r="3" spans="1:24">
       <c r="A3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="B3">
+        <v>2023</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" t="s">
-        <v>31</v>
+        <v>39</v>
+      </c>
+      <c r="D3">
+        <v>343</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H3" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I3" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="J3" s="2">
         <v>45182.46465277778</v>
       </c>
       <c r="K3" t="s">
-        <v>43</v>
-      </c>
-      <c r="L3" s="3">
+        <v>55</v>
+      </c>
+      <c r="L3">
         <v>-0.0003935185185185185</v>
       </c>
       <c r="M3">
         <v>-34</v>
       </c>
-      <c r="N3" s="3">
+      <c r="N3">
         <v>3.047986111111111</v>
       </c>
       <c r="O3">
@@ -709,59 +757,59 @@
         <v>45183.04166666666</v>
       </c>
       <c r="Q3" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="R3" t="b">
         <v>0</v>
       </c>
-      <c r="S3" s="3">
+      <c r="S3">
         <v>0.08333333333333333</v>
       </c>
       <c r="T3" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="U3" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:23">
+    <row r="4" spans="1:24">
       <c r="A4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" t="s">
-        <v>28</v>
+        <v>26</v>
+      </c>
+      <c r="B4">
+        <v>2023</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" t="s">
-        <v>32</v>
+        <v>39</v>
+      </c>
+      <c r="D4">
+        <v>1291</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H4" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="I4" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="J4" s="2">
         <v>45180.95467592592</v>
       </c>
       <c r="K4" t="s">
-        <v>44</v>
-      </c>
-      <c r="L4" s="3">
+        <v>56</v>
+      </c>
+      <c r="L4">
         <v>-0.0001157407407407407</v>
       </c>
       <c r="M4">
         <v>-10</v>
       </c>
-      <c r="N4" s="3">
+      <c r="N4">
         <v>1.454675925925926</v>
       </c>
       <c r="O4">
@@ -771,59 +819,59 @@
         <v>45181.33333333334</v>
       </c>
       <c r="Q4" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="R4" t="b">
         <v>0</v>
       </c>
-      <c r="S4" s="3">
+      <c r="S4">
         <v>0.08333333333333333</v>
       </c>
       <c r="T4" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="U4" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:23">
+    <row r="5" spans="1:24">
       <c r="A5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="B5">
+        <v>2023</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" t="s">
-        <v>33</v>
+        <v>39</v>
+      </c>
+      <c r="D5">
+        <v>423</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H5" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I5" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="J5" s="2">
         <v>45183.8446412037</v>
       </c>
       <c r="K5" t="s">
-        <v>44</v>
-      </c>
-      <c r="L5" s="3">
+        <v>56</v>
+      </c>
+      <c r="L5">
         <v>-0.02489583333333333</v>
       </c>
       <c r="M5">
         <v>-2151</v>
       </c>
-      <c r="N5" s="3">
+      <c r="N5">
         <v>4.427974537037037</v>
       </c>
       <c r="O5">
@@ -833,59 +881,59 @@
         <v>45184.79166666666</v>
       </c>
       <c r="Q5" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="R5" t="b">
         <v>0</v>
       </c>
-      <c r="S5" s="3">
+      <c r="S5">
         <v>0.08333333333333333</v>
       </c>
       <c r="T5" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23">
+    <row r="6" spans="1:24">
       <c r="A6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" t="s">
         <v>28</v>
       </c>
+      <c r="B6">
+        <v>2023</v>
+      </c>
       <c r="C6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" t="s">
-        <v>34</v>
+        <v>39</v>
+      </c>
+      <c r="D6">
+        <v>1334</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H6" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="I6" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="J6" s="2">
         <v>45180.98311342593</v>
       </c>
       <c r="K6" t="s">
-        <v>44</v>
-      </c>
-      <c r="L6" s="3">
+        <v>56</v>
+      </c>
+      <c r="L6">
         <v>-0.0002083333333333333</v>
       </c>
       <c r="M6">
         <v>-18</v>
       </c>
-      <c r="N6" s="3">
+      <c r="N6">
         <v>1.483113425925926</v>
       </c>
       <c r="O6">
@@ -895,18 +943,3667 @@
         <v>45181.33333333334</v>
       </c>
       <c r="Q6" t="s">
+        <v>61</v>
+      </c>
+      <c r="R6" t="b">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T6" t="s">
+        <v>64</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7">
+        <v>2023</v>
+      </c>
+      <c r="C7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7">
+        <v>334</v>
+      </c>
+      <c r="E7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" t="s">
+        <v>41</v>
+      </c>
+      <c r="H7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I7" t="s">
+        <v>49</v>
+      </c>
+      <c r="J7" s="2">
+        <v>45180.90565972222</v>
+      </c>
+      <c r="K7" t="s">
+        <v>54</v>
+      </c>
+      <c r="L7">
+        <v>-0.05702546296296297</v>
+      </c>
+      <c r="M7">
+        <v>-4927</v>
+      </c>
+      <c r="N7">
+        <v>1.488993055555556</v>
+      </c>
+      <c r="O7">
+        <v>128649</v>
+      </c>
+      <c r="P7" s="2">
+        <v>45182</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>59</v>
+      </c>
+      <c r="R7" t="b">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0.75</v>
+      </c>
+      <c r="T7" t="s">
+        <v>64</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24">
+      <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8">
+        <v>2023</v>
+      </c>
+      <c r="C8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8">
+        <v>343</v>
+      </c>
+      <c r="E8" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H8" t="s">
+        <v>46</v>
+      </c>
+      <c r="I8" t="s">
+        <v>50</v>
+      </c>
+      <c r="J8" s="2">
+        <v>45182.46465277778</v>
+      </c>
+      <c r="K8" t="s">
+        <v>55</v>
+      </c>
+      <c r="L8">
+        <v>-0.0003935185185185185</v>
+      </c>
+      <c r="M8">
+        <v>-34</v>
+      </c>
+      <c r="N8">
+        <v>3.047986111111111</v>
+      </c>
+      <c r="O8">
+        <v>263346</v>
+      </c>
+      <c r="P8" s="2">
+        <v>45183.04166666666</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>60</v>
+      </c>
+      <c r="R8" t="b">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T8" t="s">
+        <v>64</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24">
+      <c r="A9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9">
+        <v>2023</v>
+      </c>
+      <c r="C9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9">
+        <v>1291</v>
+      </c>
+      <c r="E9" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" t="s">
+        <v>41</v>
+      </c>
+      <c r="H9" t="s">
         <v>47</v>
       </c>
-      <c r="R6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S6" s="3">
-        <v>0.08333333333333333</v>
-      </c>
-      <c r="T6" t="s">
+      <c r="I9" t="s">
+        <v>51</v>
+      </c>
+      <c r="J9" s="2">
+        <v>45180.95467592592</v>
+      </c>
+      <c r="K9" t="s">
+        <v>56</v>
+      </c>
+      <c r="L9">
+        <v>-0.0001157407407407407</v>
+      </c>
+      <c r="M9">
+        <v>-10</v>
+      </c>
+      <c r="N9">
+        <v>1.454675925925926</v>
+      </c>
+      <c r="O9">
+        <v>125684</v>
+      </c>
+      <c r="P9" s="2">
+        <v>45181.33333333334</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>61</v>
+      </c>
+      <c r="R9" t="b">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T9" t="s">
+        <v>64</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24">
+      <c r="A10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10">
+        <v>2023</v>
+      </c>
+      <c r="C10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10">
+        <v>423</v>
+      </c>
+      <c r="E10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" t="s">
+        <v>41</v>
+      </c>
+      <c r="H10" t="s">
+        <v>46</v>
+      </c>
+      <c r="I10" t="s">
+        <v>52</v>
+      </c>
+      <c r="J10" s="2">
+        <v>45183.8446412037</v>
+      </c>
+      <c r="K10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L10">
+        <v>-0.02489583333333333</v>
+      </c>
+      <c r="M10">
+        <v>-2151</v>
+      </c>
+      <c r="N10">
+        <v>4.427974537037037</v>
+      </c>
+      <c r="O10">
+        <v>382577</v>
+      </c>
+      <c r="P10" s="2">
+        <v>45184.79166666666</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>62</v>
+      </c>
+      <c r="R10" t="b">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T10" t="s">
+        <v>64</v>
+      </c>
+      <c r="U10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24">
+      <c r="A11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11">
+        <v>2023</v>
+      </c>
+      <c r="C11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11">
+        <v>1334</v>
+      </c>
+      <c r="E11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11" t="s">
+        <v>41</v>
+      </c>
+      <c r="H11" t="s">
+        <v>47</v>
+      </c>
+      <c r="I11" t="s">
+        <v>51</v>
+      </c>
+      <c r="J11" s="2">
+        <v>45180.98311342593</v>
+      </c>
+      <c r="K11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L11">
+        <v>-0.0002083333333333333</v>
+      </c>
+      <c r="M11">
+        <v>-18</v>
+      </c>
+      <c r="N11">
+        <v>1.483113425925926</v>
+      </c>
+      <c r="O11">
+        <v>128141</v>
+      </c>
+      <c r="P11" s="2">
+        <v>45181.33333333334</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>61</v>
+      </c>
+      <c r="R11" t="b">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T11" t="s">
+        <v>64</v>
+      </c>
+      <c r="U11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24">
+      <c r="A12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12">
+        <v>2023</v>
+      </c>
+      <c r="C12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12">
+        <v>334</v>
+      </c>
+      <c r="E12" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" t="s">
+        <v>41</v>
+      </c>
+      <c r="H12" t="s">
+        <v>46</v>
+      </c>
+      <c r="I12" t="s">
         <v>49</v>
       </c>
-      <c r="U6" t="b">
+      <c r="J12" s="2">
+        <v>45180.90565972222</v>
+      </c>
+      <c r="K12" t="s">
+        <v>54</v>
+      </c>
+      <c r="L12">
+        <v>-0.05702546296296297</v>
+      </c>
+      <c r="M12">
+        <v>-4927</v>
+      </c>
+      <c r="N12">
+        <v>1.488993055555556</v>
+      </c>
+      <c r="O12">
+        <v>128649</v>
+      </c>
+      <c r="P12" s="2">
+        <v>45182</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>59</v>
+      </c>
+      <c r="R12" t="b">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0.75</v>
+      </c>
+      <c r="T12" t="s">
+        <v>64</v>
+      </c>
+      <c r="U12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24">
+      <c r="A13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13">
+        <v>2023</v>
+      </c>
+      <c r="C13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13">
+        <v>343</v>
+      </c>
+      <c r="E13" t="b">
+        <v>1</v>
+      </c>
+      <c r="F13" t="s">
+        <v>41</v>
+      </c>
+      <c r="H13" t="s">
+        <v>46</v>
+      </c>
+      <c r="I13" t="s">
+        <v>50</v>
+      </c>
+      <c r="J13" s="2">
+        <v>45182.46465277778</v>
+      </c>
+      <c r="K13" t="s">
+        <v>55</v>
+      </c>
+      <c r="L13">
+        <v>-0.0003935185185185185</v>
+      </c>
+      <c r="M13">
+        <v>-34</v>
+      </c>
+      <c r="N13">
+        <v>3.047986111111111</v>
+      </c>
+      <c r="O13">
+        <v>263346</v>
+      </c>
+      <c r="P13" s="2">
+        <v>45183.04166666666</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>60</v>
+      </c>
+      <c r="R13" t="b">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T13" t="s">
+        <v>64</v>
+      </c>
+      <c r="U13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24">
+      <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14">
+        <v>2023</v>
+      </c>
+      <c r="C14" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14">
+        <v>1291</v>
+      </c>
+      <c r="E14" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" t="s">
+        <v>41</v>
+      </c>
+      <c r="H14" t="s">
+        <v>47</v>
+      </c>
+      <c r="I14" t="s">
+        <v>51</v>
+      </c>
+      <c r="J14" s="2">
+        <v>45180.95467592592</v>
+      </c>
+      <c r="K14" t="s">
+        <v>56</v>
+      </c>
+      <c r="L14">
+        <v>-0.0001157407407407407</v>
+      </c>
+      <c r="M14">
+        <v>-10</v>
+      </c>
+      <c r="N14">
+        <v>1.454675925925926</v>
+      </c>
+      <c r="O14">
+        <v>125684</v>
+      </c>
+      <c r="P14" s="2">
+        <v>45181.33333333334</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>61</v>
+      </c>
+      <c r="R14" t="b">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T14" t="s">
+        <v>64</v>
+      </c>
+      <c r="U14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24">
+      <c r="A15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15">
+        <v>2023</v>
+      </c>
+      <c r="C15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15">
+        <v>423</v>
+      </c>
+      <c r="E15" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" t="s">
+        <v>41</v>
+      </c>
+      <c r="H15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I15" t="s">
+        <v>52</v>
+      </c>
+      <c r="J15" s="2">
+        <v>45183.8446412037</v>
+      </c>
+      <c r="K15" t="s">
+        <v>56</v>
+      </c>
+      <c r="L15">
+        <v>-0.02489583333333333</v>
+      </c>
+      <c r="M15">
+        <v>-2151</v>
+      </c>
+      <c r="N15">
+        <v>4.427974537037037</v>
+      </c>
+      <c r="O15">
+        <v>382577</v>
+      </c>
+      <c r="P15" s="2">
+        <v>45184.79166666666</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>62</v>
+      </c>
+      <c r="R15" t="b">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T15" t="s">
+        <v>64</v>
+      </c>
+      <c r="U15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24">
+      <c r="A16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16">
+        <v>2023</v>
+      </c>
+      <c r="C16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16">
+        <v>1334</v>
+      </c>
+      <c r="E16" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" t="s">
+        <v>41</v>
+      </c>
+      <c r="H16" t="s">
+        <v>47</v>
+      </c>
+      <c r="I16" t="s">
+        <v>51</v>
+      </c>
+      <c r="J16" s="2">
+        <v>45180.98311342593</v>
+      </c>
+      <c r="K16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L16">
+        <v>-0.0002083333333333333</v>
+      </c>
+      <c r="M16">
+        <v>-18</v>
+      </c>
+      <c r="N16">
+        <v>1.483113425925926</v>
+      </c>
+      <c r="O16">
+        <v>128141</v>
+      </c>
+      <c r="P16" s="2">
+        <v>45181.33333333334</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>61</v>
+      </c>
+      <c r="R16" t="b">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T16" t="s">
+        <v>64</v>
+      </c>
+      <c r="U16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24">
+      <c r="A17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17">
+        <v>2023</v>
+      </c>
+      <c r="C17" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17">
+        <v>334</v>
+      </c>
+      <c r="E17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" t="s">
+        <v>41</v>
+      </c>
+      <c r="H17" t="s">
+        <v>46</v>
+      </c>
+      <c r="I17" t="s">
+        <v>49</v>
+      </c>
+      <c r="J17" s="2">
+        <v>45180.90565972222</v>
+      </c>
+      <c r="K17" t="s">
+        <v>54</v>
+      </c>
+      <c r="L17">
+        <v>-0.05702546296296297</v>
+      </c>
+      <c r="M17">
+        <v>-4927</v>
+      </c>
+      <c r="N17">
+        <v>1.488993055555556</v>
+      </c>
+      <c r="O17">
+        <v>128649</v>
+      </c>
+      <c r="P17" s="2">
+        <v>45182</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>59</v>
+      </c>
+      <c r="R17" t="b">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0.75</v>
+      </c>
+      <c r="T17" t="s">
+        <v>64</v>
+      </c>
+      <c r="U17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24">
+      <c r="A18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18">
+        <v>2023</v>
+      </c>
+      <c r="C18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18">
+        <v>343</v>
+      </c>
+      <c r="E18" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" t="s">
+        <v>41</v>
+      </c>
+      <c r="H18" t="s">
+        <v>46</v>
+      </c>
+      <c r="I18" t="s">
+        <v>50</v>
+      </c>
+      <c r="J18" s="2">
+        <v>45182.46465277778</v>
+      </c>
+      <c r="K18" t="s">
+        <v>55</v>
+      </c>
+      <c r="L18">
+        <v>-0.0003935185185185185</v>
+      </c>
+      <c r="M18">
+        <v>-34</v>
+      </c>
+      <c r="N18">
+        <v>3.047986111111111</v>
+      </c>
+      <c r="O18">
+        <v>263346</v>
+      </c>
+      <c r="P18" s="2">
+        <v>45183.04166666666</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>60</v>
+      </c>
+      <c r="R18" t="b">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T18" t="s">
+        <v>64</v>
+      </c>
+      <c r="U18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24">
+      <c r="A19" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19">
+        <v>2023</v>
+      </c>
+      <c r="C19" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19">
+        <v>1291</v>
+      </c>
+      <c r="E19" t="b">
+        <v>1</v>
+      </c>
+      <c r="F19" t="s">
+        <v>41</v>
+      </c>
+      <c r="H19" t="s">
+        <v>47</v>
+      </c>
+      <c r="I19" t="s">
+        <v>51</v>
+      </c>
+      <c r="J19" s="2">
+        <v>45180.95467592592</v>
+      </c>
+      <c r="K19" t="s">
+        <v>56</v>
+      </c>
+      <c r="L19">
+        <v>-0.0001157407407407407</v>
+      </c>
+      <c r="M19">
+        <v>-10</v>
+      </c>
+      <c r="N19">
+        <v>1.454675925925926</v>
+      </c>
+      <c r="O19">
+        <v>125684</v>
+      </c>
+      <c r="P19" s="2">
+        <v>45181.33333333334</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>61</v>
+      </c>
+      <c r="R19" t="b">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T19" t="s">
+        <v>64</v>
+      </c>
+      <c r="U19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24">
+      <c r="A20" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20">
+        <v>2023</v>
+      </c>
+      <c r="C20" t="s">
+        <v>39</v>
+      </c>
+      <c r="D20">
+        <v>423</v>
+      </c>
+      <c r="E20" t="b">
+        <v>1</v>
+      </c>
+      <c r="F20" t="s">
+        <v>41</v>
+      </c>
+      <c r="H20" t="s">
+        <v>46</v>
+      </c>
+      <c r="I20" t="s">
+        <v>52</v>
+      </c>
+      <c r="J20" s="2">
+        <v>45183.8446412037</v>
+      </c>
+      <c r="K20" t="s">
+        <v>56</v>
+      </c>
+      <c r="L20">
+        <v>-0.02489583333333333</v>
+      </c>
+      <c r="M20">
+        <v>-2151</v>
+      </c>
+      <c r="N20">
+        <v>4.427974537037037</v>
+      </c>
+      <c r="O20">
+        <v>382577</v>
+      </c>
+      <c r="P20" s="2">
+        <v>45184.79166666666</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>62</v>
+      </c>
+      <c r="R20" t="b">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T20" t="s">
+        <v>64</v>
+      </c>
+      <c r="U20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24">
+      <c r="A21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21">
+        <v>2023</v>
+      </c>
+      <c r="C21" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21">
+        <v>1334</v>
+      </c>
+      <c r="E21" t="b">
+        <v>1</v>
+      </c>
+      <c r="F21" t="s">
+        <v>41</v>
+      </c>
+      <c r="H21" t="s">
+        <v>47</v>
+      </c>
+      <c r="I21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J21" s="2">
+        <v>45180.98311342593</v>
+      </c>
+      <c r="K21" t="s">
+        <v>56</v>
+      </c>
+      <c r="L21">
+        <v>-0.0002083333333333333</v>
+      </c>
+      <c r="M21">
+        <v>-18</v>
+      </c>
+      <c r="N21">
+        <v>1.483113425925926</v>
+      </c>
+      <c r="O21">
+        <v>128141</v>
+      </c>
+      <c r="P21" s="2">
+        <v>45181.33333333334</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>61</v>
+      </c>
+      <c r="R21" t="b">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T21" t="s">
+        <v>64</v>
+      </c>
+      <c r="U21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24">
+      <c r="A22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22">
+        <v>2024</v>
+      </c>
+      <c r="C22" t="s">
+        <v>39</v>
+      </c>
+      <c r="D22">
+        <v>404</v>
+      </c>
+      <c r="E22" t="b">
+        <v>1</v>
+      </c>
+      <c r="F22" t="s">
+        <v>41</v>
+      </c>
+      <c r="H22" t="s">
+        <v>46</v>
+      </c>
+      <c r="I22" t="s">
+        <v>53</v>
+      </c>
+      <c r="J22" s="2">
+        <v>45546.77756944444</v>
+      </c>
+      <c r="K22" t="s">
+        <v>54</v>
+      </c>
+      <c r="L22">
+        <v>-0.007534722222222222</v>
+      </c>
+      <c r="M22">
+        <v>-651</v>
+      </c>
+      <c r="N22">
+        <v>3.360902777777778</v>
+      </c>
+      <c r="O22">
+        <v>290382</v>
+      </c>
+      <c r="P22" s="2">
+        <v>45547.875</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>63</v>
+      </c>
+      <c r="R22" t="b">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T22" t="s">
+        <v>64</v>
+      </c>
+      <c r="U22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24">
+      <c r="A23" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23">
+        <v>2024</v>
+      </c>
+      <c r="C23" t="s">
+        <v>39</v>
+      </c>
+      <c r="D23">
+        <v>1367</v>
+      </c>
+      <c r="E23" t="b">
+        <v>0</v>
+      </c>
+      <c r="F23" t="s">
+        <v>42</v>
+      </c>
+      <c r="G23" t="s">
+        <v>45</v>
+      </c>
+      <c r="H23" t="s">
+        <v>47</v>
+      </c>
+      <c r="I23" t="s">
+        <v>51</v>
+      </c>
+      <c r="J23" s="2">
+        <v>45545.14299768519</v>
+      </c>
+      <c r="K23" t="s">
+        <v>42</v>
+      </c>
+      <c r="L23">
+        <v>-0.0003587962962962963</v>
+      </c>
+      <c r="M23">
+        <v>-31</v>
+      </c>
+      <c r="N23">
+        <v>1.642997685185185</v>
+      </c>
+      <c r="O23">
+        <v>141955</v>
+      </c>
+      <c r="P23" s="2">
+        <v>45545.33333333334</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>61</v>
+      </c>
+      <c r="R23" t="b">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T23" t="s">
+        <v>64</v>
+      </c>
+      <c r="U23" t="b">
+        <v>0</v>
+      </c>
+      <c r="X23" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24">
+      <c r="A24" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24">
+        <v>2022</v>
+      </c>
+      <c r="C24" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24">
+        <v>275</v>
+      </c>
+      <c r="E24" t="b">
+        <v>1</v>
+      </c>
+      <c r="F24" t="s">
+        <v>41</v>
+      </c>
+      <c r="H24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I24" t="s">
+        <v>50</v>
+      </c>
+      <c r="J24" s="2">
+        <v>44817.39240740741</v>
+      </c>
+      <c r="K24" t="s">
+        <v>57</v>
+      </c>
+      <c r="L24">
+        <v>-0.003252314814814815</v>
+      </c>
+      <c r="M24">
+        <v>-281</v>
+      </c>
+      <c r="N24">
+        <v>1.975740740740741</v>
+      </c>
+      <c r="O24">
+        <v>170704</v>
+      </c>
+      <c r="P24" s="2">
+        <v>44819.04166666666</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>60</v>
+      </c>
+      <c r="R24" t="b">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T24" t="s">
+        <v>64</v>
+      </c>
+      <c r="U24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24">
+      <c r="A25" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25">
+        <v>2022</v>
+      </c>
+      <c r="C25" t="s">
+        <v>39</v>
+      </c>
+      <c r="D25">
+        <v>127</v>
+      </c>
+      <c r="E25" t="b">
+        <v>1</v>
+      </c>
+      <c r="F25" t="s">
+        <v>41</v>
+      </c>
+      <c r="H25" t="s">
+        <v>46</v>
+      </c>
+      <c r="I25" t="s">
+        <v>53</v>
+      </c>
+      <c r="J25" s="2">
+        <v>44818.26855324074</v>
+      </c>
+      <c r="K25" t="s">
+        <v>58</v>
+      </c>
+      <c r="L25">
+        <v>-0.0005439814814814814</v>
+      </c>
+      <c r="M25">
+        <v>-47</v>
+      </c>
+      <c r="N25">
+        <v>2.851886574074074</v>
+      </c>
+      <c r="O25">
+        <v>246403</v>
+      </c>
+      <c r="P25" s="2">
+        <v>44819.875</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>63</v>
+      </c>
+      <c r="R25" t="b">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T25" t="s">
+        <v>64</v>
+      </c>
+      <c r="U25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24">
+      <c r="A26" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26">
+        <v>2022</v>
+      </c>
+      <c r="C26" t="s">
+        <v>39</v>
+      </c>
+      <c r="D26">
+        <v>549</v>
+      </c>
+      <c r="E26" t="b">
+        <v>1</v>
+      </c>
+      <c r="F26" t="s">
+        <v>41</v>
+      </c>
+      <c r="H26" t="s">
+        <v>46</v>
+      </c>
+      <c r="I26" t="s">
+        <v>52</v>
+      </c>
+      <c r="J26" s="2">
+        <v>44820.2553125</v>
+      </c>
+      <c r="K26" t="s">
+        <v>55</v>
+      </c>
+      <c r="L26">
+        <v>-0.0003587962962962963</v>
+      </c>
+      <c r="M26">
+        <v>-31</v>
+      </c>
+      <c r="N26">
+        <v>4.838645833333334</v>
+      </c>
+      <c r="O26">
+        <v>418059</v>
+      </c>
+      <c r="P26" s="2">
+        <v>44820.79166666666</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>62</v>
+      </c>
+      <c r="R26" t="b">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T26" t="s">
+        <v>64</v>
+      </c>
+      <c r="U26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24">
+      <c r="A27" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27">
+        <v>2022</v>
+      </c>
+      <c r="C27" t="s">
+        <v>39</v>
+      </c>
+      <c r="D27">
+        <v>1005</v>
+      </c>
+      <c r="E27" t="b">
+        <v>0</v>
+      </c>
+      <c r="F27" t="s">
+        <v>43</v>
+      </c>
+      <c r="H27" t="s">
+        <v>47</v>
+      </c>
+      <c r="I27" t="s">
+        <v>53</v>
+      </c>
+      <c r="J27" s="2">
+        <v>44819.50680555555</v>
+      </c>
+      <c r="L27">
+        <v>-0.0002777777777777778</v>
+      </c>
+      <c r="M27">
+        <v>-24</v>
+      </c>
+      <c r="N27">
+        <v>4.006805555555555</v>
+      </c>
+      <c r="O27">
+        <v>346188</v>
+      </c>
+      <c r="P27" s="2">
+        <v>44819.95833333334</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>63</v>
+      </c>
+      <c r="R27" t="b">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T27" t="s">
+        <v>64</v>
+      </c>
+      <c r="U27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24">
+      <c r="A28" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28">
+        <v>2022</v>
+      </c>
+      <c r="C28" t="s">
+        <v>39</v>
+      </c>
+      <c r="D28">
+        <v>1205</v>
+      </c>
+      <c r="E28" t="b">
+        <v>0</v>
+      </c>
+      <c r="F28" t="s">
+        <v>44</v>
+      </c>
+      <c r="H28" t="s">
+        <v>47</v>
+      </c>
+      <c r="I28" t="s">
+        <v>50</v>
+      </c>
+      <c r="J28" s="2">
+        <v>44818.92413194444</v>
+      </c>
+      <c r="L28">
+        <v>-0.0002199074074074074</v>
+      </c>
+      <c r="M28">
+        <v>-19</v>
+      </c>
+      <c r="N28">
+        <v>3.424131944444444</v>
+      </c>
+      <c r="O28">
+        <v>295845</v>
+      </c>
+      <c r="P28" s="2">
+        <v>44819.125</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>60</v>
+      </c>
+      <c r="R28" t="b">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T28" t="s">
+        <v>64</v>
+      </c>
+      <c r="U28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24">
+      <c r="A29" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29">
+        <v>2022</v>
+      </c>
+      <c r="C29" t="s">
+        <v>39</v>
+      </c>
+      <c r="D29">
+        <v>1268</v>
+      </c>
+      <c r="E29" t="b">
+        <v>0</v>
+      </c>
+      <c r="F29" t="s">
+        <v>44</v>
+      </c>
+      <c r="H29" t="s">
+        <v>47</v>
+      </c>
+      <c r="I29" t="s">
+        <v>50</v>
+      </c>
+      <c r="J29" s="2">
+        <v>44818.92489583333</v>
+      </c>
+      <c r="L29">
+        <v>-0.0008333333333333334</v>
+      </c>
+      <c r="M29">
+        <v>-72</v>
+      </c>
+      <c r="N29">
+        <v>3.424895833333333</v>
+      </c>
+      <c r="O29">
+        <v>295911</v>
+      </c>
+      <c r="P29" s="2">
+        <v>44819.125</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>60</v>
+      </c>
+      <c r="R29" t="b">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T29" t="s">
+        <v>64</v>
+      </c>
+      <c r="U29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24">
+      <c r="A30" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30">
+        <v>2021</v>
+      </c>
+      <c r="C30" t="s">
+        <v>39</v>
+      </c>
+      <c r="D30">
+        <v>162</v>
+      </c>
+      <c r="E30" t="b">
+        <v>1</v>
+      </c>
+      <c r="F30" t="s">
+        <v>41</v>
+      </c>
+      <c r="H30" t="s">
+        <v>48</v>
+      </c>
+      <c r="I30" t="s">
+        <v>52</v>
+      </c>
+      <c r="J30" s="2">
+        <v>44456.22016203704</v>
+      </c>
+      <c r="K30" t="s">
+        <v>55</v>
+      </c>
+      <c r="L30">
+        <v>-0.001018518518518518</v>
+      </c>
+      <c r="M30">
+        <v>-88</v>
+      </c>
+      <c r="N30">
+        <v>4.803495370370371</v>
+      </c>
+      <c r="O30">
+        <v>415022</v>
+      </c>
+      <c r="P30" s="2">
+        <v>44456.79166666666</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>62</v>
+      </c>
+      <c r="R30" t="b">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T30" t="s">
+        <v>64</v>
+      </c>
+      <c r="U30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24">
+      <c r="A31" t="s">
+        <v>24</v>
+      </c>
+      <c r="B31">
+        <v>2023</v>
+      </c>
+      <c r="C31" t="s">
+        <v>39</v>
+      </c>
+      <c r="D31">
+        <v>334</v>
+      </c>
+      <c r="E31" t="b">
+        <v>1</v>
+      </c>
+      <c r="F31" t="s">
+        <v>41</v>
+      </c>
+      <c r="H31" t="s">
+        <v>46</v>
+      </c>
+      <c r="I31" t="s">
+        <v>49</v>
+      </c>
+      <c r="J31" s="2">
+        <v>45180.90565972222</v>
+      </c>
+      <c r="K31" t="s">
+        <v>54</v>
+      </c>
+      <c r="L31">
+        <v>-0.05702546296296297</v>
+      </c>
+      <c r="M31">
+        <v>-4927</v>
+      </c>
+      <c r="N31">
+        <v>1.488993055555556</v>
+      </c>
+      <c r="O31">
+        <v>128649</v>
+      </c>
+      <c r="P31" s="2">
+        <v>45182</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>59</v>
+      </c>
+      <c r="R31" t="b">
+        <v>0</v>
+      </c>
+      <c r="S31">
+        <v>0.75</v>
+      </c>
+      <c r="T31" t="s">
+        <v>64</v>
+      </c>
+      <c r="U31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24">
+      <c r="A32" t="s">
+        <v>25</v>
+      </c>
+      <c r="B32">
+        <v>2023</v>
+      </c>
+      <c r="C32" t="s">
+        <v>39</v>
+      </c>
+      <c r="D32">
+        <v>343</v>
+      </c>
+      <c r="E32" t="b">
+        <v>1</v>
+      </c>
+      <c r="F32" t="s">
+        <v>41</v>
+      </c>
+      <c r="H32" t="s">
+        <v>46</v>
+      </c>
+      <c r="I32" t="s">
+        <v>50</v>
+      </c>
+      <c r="J32" s="2">
+        <v>45182.46465277778</v>
+      </c>
+      <c r="K32" t="s">
+        <v>55</v>
+      </c>
+      <c r="L32">
+        <v>-0.0003935185185185185</v>
+      </c>
+      <c r="M32">
+        <v>-34</v>
+      </c>
+      <c r="N32">
+        <v>3.047986111111111</v>
+      </c>
+      <c r="O32">
+        <v>263346</v>
+      </c>
+      <c r="P32" s="2">
+        <v>45183.04166666666</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>60</v>
+      </c>
+      <c r="R32" t="b">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T32" t="s">
+        <v>64</v>
+      </c>
+      <c r="U32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21">
+      <c r="A33" t="s">
+        <v>26</v>
+      </c>
+      <c r="B33">
+        <v>2023</v>
+      </c>
+      <c r="C33" t="s">
+        <v>39</v>
+      </c>
+      <c r="D33">
+        <v>1291</v>
+      </c>
+      <c r="E33" t="b">
+        <v>1</v>
+      </c>
+      <c r="F33" t="s">
+        <v>41</v>
+      </c>
+      <c r="H33" t="s">
+        <v>47</v>
+      </c>
+      <c r="I33" t="s">
+        <v>51</v>
+      </c>
+      <c r="J33" s="2">
+        <v>45180.95467592592</v>
+      </c>
+      <c r="K33" t="s">
+        <v>56</v>
+      </c>
+      <c r="L33">
+        <v>-0.0001157407407407407</v>
+      </c>
+      <c r="M33">
+        <v>-10</v>
+      </c>
+      <c r="N33">
+        <v>1.454675925925926</v>
+      </c>
+      <c r="O33">
+        <v>125684</v>
+      </c>
+      <c r="P33" s="2">
+        <v>45181.33333333334</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>61</v>
+      </c>
+      <c r="R33" t="b">
+        <v>0</v>
+      </c>
+      <c r="S33">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T33" t="s">
+        <v>64</v>
+      </c>
+      <c r="U33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21">
+      <c r="A34" t="s">
+        <v>27</v>
+      </c>
+      <c r="B34">
+        <v>2023</v>
+      </c>
+      <c r="C34" t="s">
+        <v>39</v>
+      </c>
+      <c r="D34">
+        <v>423</v>
+      </c>
+      <c r="E34" t="b">
+        <v>1</v>
+      </c>
+      <c r="F34" t="s">
+        <v>41</v>
+      </c>
+      <c r="H34" t="s">
+        <v>46</v>
+      </c>
+      <c r="I34" t="s">
+        <v>52</v>
+      </c>
+      <c r="J34" s="2">
+        <v>45183.8446412037</v>
+      </c>
+      <c r="K34" t="s">
+        <v>56</v>
+      </c>
+      <c r="L34">
+        <v>-0.02489583333333333</v>
+      </c>
+      <c r="M34">
+        <v>-2151</v>
+      </c>
+      <c r="N34">
+        <v>4.427974537037037</v>
+      </c>
+      <c r="O34">
+        <v>382577</v>
+      </c>
+      <c r="P34" s="2">
+        <v>45184.79166666666</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>62</v>
+      </c>
+      <c r="R34" t="b">
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T34" t="s">
+        <v>64</v>
+      </c>
+      <c r="U34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21">
+      <c r="A35" t="s">
+        <v>28</v>
+      </c>
+      <c r="B35">
+        <v>2023</v>
+      </c>
+      <c r="C35" t="s">
+        <v>39</v>
+      </c>
+      <c r="D35">
+        <v>1334</v>
+      </c>
+      <c r="E35" t="b">
+        <v>1</v>
+      </c>
+      <c r="F35" t="s">
+        <v>41</v>
+      </c>
+      <c r="H35" t="s">
+        <v>47</v>
+      </c>
+      <c r="I35" t="s">
+        <v>51</v>
+      </c>
+      <c r="J35" s="2">
+        <v>45180.98311342593</v>
+      </c>
+      <c r="K35" t="s">
+        <v>56</v>
+      </c>
+      <c r="L35">
+        <v>-0.0002083333333333333</v>
+      </c>
+      <c r="M35">
+        <v>-18</v>
+      </c>
+      <c r="N35">
+        <v>1.483113425925926</v>
+      </c>
+      <c r="O35">
+        <v>128141</v>
+      </c>
+      <c r="P35" s="2">
+        <v>45181.33333333334</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>61</v>
+      </c>
+      <c r="R35" t="b">
+        <v>0</v>
+      </c>
+      <c r="S35">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T35" t="s">
+        <v>64</v>
+      </c>
+      <c r="U35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21">
+      <c r="A36" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36">
+        <v>2021</v>
+      </c>
+      <c r="C36" t="s">
+        <v>39</v>
+      </c>
+      <c r="D36">
+        <v>162</v>
+      </c>
+      <c r="E36" t="b">
+        <v>1</v>
+      </c>
+      <c r="F36" t="s">
+        <v>41</v>
+      </c>
+      <c r="H36" t="s">
+        <v>48</v>
+      </c>
+      <c r="I36" t="s">
+        <v>52</v>
+      </c>
+      <c r="J36" s="2">
+        <v>44456.22016203704</v>
+      </c>
+      <c r="K36" t="s">
+        <v>55</v>
+      </c>
+      <c r="L36">
+        <v>-0.001018518518518518</v>
+      </c>
+      <c r="M36">
+        <v>-88</v>
+      </c>
+      <c r="N36">
+        <v>4.803495370370371</v>
+      </c>
+      <c r="O36">
+        <v>415022</v>
+      </c>
+      <c r="P36" s="2">
+        <v>44456.79166666666</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>62</v>
+      </c>
+      <c r="R36" t="b">
+        <v>0</v>
+      </c>
+      <c r="S36">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T36" t="s">
+        <v>64</v>
+      </c>
+      <c r="U36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21">
+      <c r="A37" t="s">
+        <v>31</v>
+      </c>
+      <c r="B37">
+        <v>2022</v>
+      </c>
+      <c r="C37" t="s">
+        <v>39</v>
+      </c>
+      <c r="D37">
+        <v>275</v>
+      </c>
+      <c r="E37" t="b">
+        <v>1</v>
+      </c>
+      <c r="F37" t="s">
+        <v>41</v>
+      </c>
+      <c r="H37" t="s">
+        <v>46</v>
+      </c>
+      <c r="I37" t="s">
+        <v>50</v>
+      </c>
+      <c r="J37" s="2">
+        <v>44817.39240740741</v>
+      </c>
+      <c r="K37" t="s">
+        <v>57</v>
+      </c>
+      <c r="L37">
+        <v>-0.003252314814814815</v>
+      </c>
+      <c r="M37">
+        <v>-281</v>
+      </c>
+      <c r="N37">
+        <v>1.975740740740741</v>
+      </c>
+      <c r="O37">
+        <v>170704</v>
+      </c>
+      <c r="P37" s="2">
+        <v>44819.04166666666</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>60</v>
+      </c>
+      <c r="R37" t="b">
+        <v>0</v>
+      </c>
+      <c r="S37">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T37" t="s">
+        <v>64</v>
+      </c>
+      <c r="U37" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21">
+      <c r="A38" t="s">
+        <v>32</v>
+      </c>
+      <c r="B38">
+        <v>2022</v>
+      </c>
+      <c r="C38" t="s">
+        <v>39</v>
+      </c>
+      <c r="D38">
+        <v>127</v>
+      </c>
+      <c r="E38" t="b">
+        <v>1</v>
+      </c>
+      <c r="F38" t="s">
+        <v>41</v>
+      </c>
+      <c r="H38" t="s">
+        <v>46</v>
+      </c>
+      <c r="I38" t="s">
+        <v>53</v>
+      </c>
+      <c r="J38" s="2">
+        <v>44818.26855324074</v>
+      </c>
+      <c r="K38" t="s">
+        <v>58</v>
+      </c>
+      <c r="L38">
+        <v>-0.0005439814814814814</v>
+      </c>
+      <c r="M38">
+        <v>-47</v>
+      </c>
+      <c r="N38">
+        <v>2.851886574074074</v>
+      </c>
+      <c r="O38">
+        <v>246403</v>
+      </c>
+      <c r="P38" s="2">
+        <v>44819.875</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>63</v>
+      </c>
+      <c r="R38" t="b">
+        <v>0</v>
+      </c>
+      <c r="S38">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T38" t="s">
+        <v>64</v>
+      </c>
+      <c r="U38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21">
+      <c r="A39" t="s">
+        <v>33</v>
+      </c>
+      <c r="B39">
+        <v>2022</v>
+      </c>
+      <c r="C39" t="s">
+        <v>39</v>
+      </c>
+      <c r="D39">
+        <v>549</v>
+      </c>
+      <c r="E39" t="b">
+        <v>1</v>
+      </c>
+      <c r="F39" t="s">
+        <v>41</v>
+      </c>
+      <c r="H39" t="s">
+        <v>46</v>
+      </c>
+      <c r="I39" t="s">
+        <v>52</v>
+      </c>
+      <c r="J39" s="2">
+        <v>44820.2553125</v>
+      </c>
+      <c r="K39" t="s">
+        <v>55</v>
+      </c>
+      <c r="L39">
+        <v>-0.0003587962962962963</v>
+      </c>
+      <c r="M39">
+        <v>-31</v>
+      </c>
+      <c r="N39">
+        <v>4.838645833333334</v>
+      </c>
+      <c r="O39">
+        <v>418059</v>
+      </c>
+      <c r="P39" s="2">
+        <v>44820.79166666666</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>62</v>
+      </c>
+      <c r="R39" t="b">
+        <v>0</v>
+      </c>
+      <c r="S39">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T39" t="s">
+        <v>64</v>
+      </c>
+      <c r="U39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21">
+      <c r="A40" t="s">
+        <v>34</v>
+      </c>
+      <c r="B40">
+        <v>2022</v>
+      </c>
+      <c r="C40" t="s">
+        <v>39</v>
+      </c>
+      <c r="D40">
+        <v>1005</v>
+      </c>
+      <c r="E40" t="b">
+        <v>0</v>
+      </c>
+      <c r="F40" t="s">
+        <v>43</v>
+      </c>
+      <c r="H40" t="s">
+        <v>47</v>
+      </c>
+      <c r="I40" t="s">
+        <v>53</v>
+      </c>
+      <c r="J40" s="2">
+        <v>44819.50680555555</v>
+      </c>
+      <c r="L40">
+        <v>-0.0002777777777777778</v>
+      </c>
+      <c r="M40">
+        <v>-24</v>
+      </c>
+      <c r="N40">
+        <v>4.006805555555555</v>
+      </c>
+      <c r="O40">
+        <v>346188</v>
+      </c>
+      <c r="P40" s="2">
+        <v>44819.95833333334</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>63</v>
+      </c>
+      <c r="R40" t="b">
+        <v>0</v>
+      </c>
+      <c r="S40">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T40" t="s">
+        <v>64</v>
+      </c>
+      <c r="U40" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21">
+      <c r="A41" t="s">
+        <v>35</v>
+      </c>
+      <c r="B41">
+        <v>2022</v>
+      </c>
+      <c r="C41" t="s">
+        <v>39</v>
+      </c>
+      <c r="D41">
+        <v>1205</v>
+      </c>
+      <c r="E41" t="b">
+        <v>0</v>
+      </c>
+      <c r="F41" t="s">
+        <v>44</v>
+      </c>
+      <c r="H41" t="s">
+        <v>47</v>
+      </c>
+      <c r="I41" t="s">
+        <v>50</v>
+      </c>
+      <c r="J41" s="2">
+        <v>44818.92413194444</v>
+      </c>
+      <c r="L41">
+        <v>-0.0002199074074074074</v>
+      </c>
+      <c r="M41">
+        <v>-19</v>
+      </c>
+      <c r="N41">
+        <v>3.424131944444444</v>
+      </c>
+      <c r="O41">
+        <v>295845</v>
+      </c>
+      <c r="P41" s="2">
+        <v>44819.125</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>60</v>
+      </c>
+      <c r="R41" t="b">
+        <v>0</v>
+      </c>
+      <c r="S41">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T41" t="s">
+        <v>64</v>
+      </c>
+      <c r="U41" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21">
+      <c r="A42" t="s">
+        <v>36</v>
+      </c>
+      <c r="B42">
+        <v>2022</v>
+      </c>
+      <c r="C42" t="s">
+        <v>39</v>
+      </c>
+      <c r="D42">
+        <v>1268</v>
+      </c>
+      <c r="E42" t="b">
+        <v>0</v>
+      </c>
+      <c r="F42" t="s">
+        <v>44</v>
+      </c>
+      <c r="H42" t="s">
+        <v>47</v>
+      </c>
+      <c r="I42" t="s">
+        <v>50</v>
+      </c>
+      <c r="J42" s="2">
+        <v>44818.92489583333</v>
+      </c>
+      <c r="L42">
+        <v>-0.0008333333333333334</v>
+      </c>
+      <c r="M42">
+        <v>-72</v>
+      </c>
+      <c r="N42">
+        <v>3.424895833333333</v>
+      </c>
+      <c r="O42">
+        <v>295911</v>
+      </c>
+      <c r="P42" s="2">
+        <v>44819.125</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>60</v>
+      </c>
+      <c r="R42" t="b">
+        <v>0</v>
+      </c>
+      <c r="S42">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T42" t="s">
+        <v>64</v>
+      </c>
+      <c r="U42" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21">
+      <c r="A43" t="s">
+        <v>24</v>
+      </c>
+      <c r="B43">
+        <v>2023</v>
+      </c>
+      <c r="C43" t="s">
+        <v>39</v>
+      </c>
+      <c r="D43">
+        <v>334</v>
+      </c>
+      <c r="E43" t="b">
+        <v>1</v>
+      </c>
+      <c r="F43" t="s">
+        <v>41</v>
+      </c>
+      <c r="H43" t="s">
+        <v>46</v>
+      </c>
+      <c r="I43" t="s">
+        <v>49</v>
+      </c>
+      <c r="J43" s="2">
+        <v>45180.90565972222</v>
+      </c>
+      <c r="K43" t="s">
+        <v>54</v>
+      </c>
+      <c r="L43">
+        <v>-0.05702546296296297</v>
+      </c>
+      <c r="M43">
+        <v>-4927</v>
+      </c>
+      <c r="N43">
+        <v>1.488993055555556</v>
+      </c>
+      <c r="O43">
+        <v>128649</v>
+      </c>
+      <c r="P43" s="2">
+        <v>45182</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>59</v>
+      </c>
+      <c r="R43" t="b">
+        <v>0</v>
+      </c>
+      <c r="S43">
+        <v>0.75</v>
+      </c>
+      <c r="T43" t="s">
+        <v>64</v>
+      </c>
+      <c r="U43" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21">
+      <c r="A44" t="s">
+        <v>25</v>
+      </c>
+      <c r="B44">
+        <v>2023</v>
+      </c>
+      <c r="C44" t="s">
+        <v>39</v>
+      </c>
+      <c r="D44">
+        <v>343</v>
+      </c>
+      <c r="E44" t="b">
+        <v>1</v>
+      </c>
+      <c r="F44" t="s">
+        <v>41</v>
+      </c>
+      <c r="H44" t="s">
+        <v>46</v>
+      </c>
+      <c r="I44" t="s">
+        <v>50</v>
+      </c>
+      <c r="J44" s="2">
+        <v>45182.46465277778</v>
+      </c>
+      <c r="K44" t="s">
+        <v>55</v>
+      </c>
+      <c r="L44">
+        <v>-0.0003935185185185185</v>
+      </c>
+      <c r="M44">
+        <v>-34</v>
+      </c>
+      <c r="N44">
+        <v>3.047986111111111</v>
+      </c>
+      <c r="O44">
+        <v>263346</v>
+      </c>
+      <c r="P44" s="2">
+        <v>45183.04166666666</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>60</v>
+      </c>
+      <c r="R44" t="b">
+        <v>0</v>
+      </c>
+      <c r="S44">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T44" t="s">
+        <v>64</v>
+      </c>
+      <c r="U44" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21">
+      <c r="A45" t="s">
+        <v>26</v>
+      </c>
+      <c r="B45">
+        <v>2023</v>
+      </c>
+      <c r="C45" t="s">
+        <v>39</v>
+      </c>
+      <c r="D45">
+        <v>1291</v>
+      </c>
+      <c r="E45" t="b">
+        <v>1</v>
+      </c>
+      <c r="F45" t="s">
+        <v>41</v>
+      </c>
+      <c r="H45" t="s">
+        <v>47</v>
+      </c>
+      <c r="I45" t="s">
+        <v>51</v>
+      </c>
+      <c r="J45" s="2">
+        <v>45180.95467592592</v>
+      </c>
+      <c r="K45" t="s">
+        <v>56</v>
+      </c>
+      <c r="L45">
+        <v>-0.0001157407407407407</v>
+      </c>
+      <c r="M45">
+        <v>-10</v>
+      </c>
+      <c r="N45">
+        <v>1.454675925925926</v>
+      </c>
+      <c r="O45">
+        <v>125684</v>
+      </c>
+      <c r="P45" s="2">
+        <v>45181.33333333334</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>61</v>
+      </c>
+      <c r="R45" t="b">
+        <v>0</v>
+      </c>
+      <c r="S45">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T45" t="s">
+        <v>64</v>
+      </c>
+      <c r="U45" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21">
+      <c r="A46" t="s">
+        <v>27</v>
+      </c>
+      <c r="B46">
+        <v>2023</v>
+      </c>
+      <c r="C46" t="s">
+        <v>39</v>
+      </c>
+      <c r="D46">
+        <v>423</v>
+      </c>
+      <c r="E46" t="b">
+        <v>1</v>
+      </c>
+      <c r="F46" t="s">
+        <v>41</v>
+      </c>
+      <c r="H46" t="s">
+        <v>46</v>
+      </c>
+      <c r="I46" t="s">
+        <v>52</v>
+      </c>
+      <c r="J46" s="2">
+        <v>45183.8446412037</v>
+      </c>
+      <c r="K46" t="s">
+        <v>56</v>
+      </c>
+      <c r="L46">
+        <v>-0.02489583333333333</v>
+      </c>
+      <c r="M46">
+        <v>-2151</v>
+      </c>
+      <c r="N46">
+        <v>4.427974537037037</v>
+      </c>
+      <c r="O46">
+        <v>382577</v>
+      </c>
+      <c r="P46" s="2">
+        <v>45184.79166666666</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>62</v>
+      </c>
+      <c r="R46" t="b">
+        <v>0</v>
+      </c>
+      <c r="S46">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T46" t="s">
+        <v>64</v>
+      </c>
+      <c r="U46" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21">
+      <c r="A47" t="s">
+        <v>28</v>
+      </c>
+      <c r="B47">
+        <v>2023</v>
+      </c>
+      <c r="C47" t="s">
+        <v>39</v>
+      </c>
+      <c r="D47">
+        <v>1334</v>
+      </c>
+      <c r="E47" t="b">
+        <v>1</v>
+      </c>
+      <c r="F47" t="s">
+        <v>41</v>
+      </c>
+      <c r="H47" t="s">
+        <v>47</v>
+      </c>
+      <c r="I47" t="s">
+        <v>51</v>
+      </c>
+      <c r="J47" s="2">
+        <v>45180.98311342593</v>
+      </c>
+      <c r="K47" t="s">
+        <v>56</v>
+      </c>
+      <c r="L47">
+        <v>-0.0002083333333333333</v>
+      </c>
+      <c r="M47">
+        <v>-18</v>
+      </c>
+      <c r="N47">
+        <v>1.483113425925926</v>
+      </c>
+      <c r="O47">
+        <v>128141</v>
+      </c>
+      <c r="P47" s="2">
+        <v>45181.33333333334</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>61</v>
+      </c>
+      <c r="R47" t="b">
+        <v>0</v>
+      </c>
+      <c r="S47">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T47" t="s">
+        <v>64</v>
+      </c>
+      <c r="U47" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21">
+      <c r="A48" t="s">
+        <v>29</v>
+      </c>
+      <c r="B48">
+        <v>2024</v>
+      </c>
+      <c r="C48" t="s">
+        <v>39</v>
+      </c>
+      <c r="D48">
+        <v>404</v>
+      </c>
+      <c r="E48" t="b">
+        <v>1</v>
+      </c>
+      <c r="F48" t="s">
+        <v>41</v>
+      </c>
+      <c r="H48" t="s">
+        <v>46</v>
+      </c>
+      <c r="I48" t="s">
+        <v>53</v>
+      </c>
+      <c r="J48" s="2">
+        <v>45546.77756944444</v>
+      </c>
+      <c r="K48" t="s">
+        <v>54</v>
+      </c>
+      <c r="L48">
+        <v>-0.007534722222222222</v>
+      </c>
+      <c r="M48">
+        <v>-651</v>
+      </c>
+      <c r="N48">
+        <v>3.360902777777778</v>
+      </c>
+      <c r="O48">
+        <v>290382</v>
+      </c>
+      <c r="P48" s="2">
+        <v>45547.875</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>63</v>
+      </c>
+      <c r="R48" t="b">
+        <v>0</v>
+      </c>
+      <c r="S48">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T48" t="s">
+        <v>64</v>
+      </c>
+      <c r="U48" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:24">
+      <c r="A49" t="s">
+        <v>30</v>
+      </c>
+      <c r="B49">
+        <v>2024</v>
+      </c>
+      <c r="C49" t="s">
+        <v>39</v>
+      </c>
+      <c r="D49">
+        <v>1367</v>
+      </c>
+      <c r="E49" t="b">
+        <v>0</v>
+      </c>
+      <c r="F49" t="s">
+        <v>42</v>
+      </c>
+      <c r="G49" t="s">
+        <v>45</v>
+      </c>
+      <c r="H49" t="s">
+        <v>47</v>
+      </c>
+      <c r="I49" t="s">
+        <v>51</v>
+      </c>
+      <c r="J49" s="2">
+        <v>45545.14299768519</v>
+      </c>
+      <c r="K49" t="s">
+        <v>42</v>
+      </c>
+      <c r="L49">
+        <v>-0.0003587962962962963</v>
+      </c>
+      <c r="M49">
+        <v>-31</v>
+      </c>
+      <c r="N49">
+        <v>1.642997685185185</v>
+      </c>
+      <c r="O49">
+        <v>141955</v>
+      </c>
+      <c r="P49" s="2">
+        <v>45545.33333333334</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>61</v>
+      </c>
+      <c r="R49" t="b">
+        <v>0</v>
+      </c>
+      <c r="S49">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T49" t="s">
+        <v>64</v>
+      </c>
+      <c r="U49" t="b">
+        <v>0</v>
+      </c>
+      <c r="X49" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="50" spans="1:24">
+      <c r="A50" t="s">
+        <v>29</v>
+      </c>
+      <c r="B50">
+        <v>2024</v>
+      </c>
+      <c r="C50" t="s">
+        <v>39</v>
+      </c>
+      <c r="D50">
+        <v>404</v>
+      </c>
+      <c r="E50" t="b">
+        <v>1</v>
+      </c>
+      <c r="F50" t="s">
+        <v>41</v>
+      </c>
+      <c r="H50" t="s">
+        <v>46</v>
+      </c>
+      <c r="I50" t="s">
+        <v>53</v>
+      </c>
+      <c r="J50" s="2">
+        <v>45546.77756944444</v>
+      </c>
+      <c r="K50" t="s">
+        <v>54</v>
+      </c>
+      <c r="L50">
+        <v>-0.007534722222222222</v>
+      </c>
+      <c r="M50">
+        <v>-651</v>
+      </c>
+      <c r="N50">
+        <v>3.360902777777778</v>
+      </c>
+      <c r="O50">
+        <v>290382</v>
+      </c>
+      <c r="P50" s="2">
+        <v>45547.875</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>63</v>
+      </c>
+      <c r="R50" t="b">
+        <v>0</v>
+      </c>
+      <c r="S50">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T50" t="s">
+        <v>64</v>
+      </c>
+      <c r="U50" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:24">
+      <c r="A51" t="s">
+        <v>30</v>
+      </c>
+      <c r="B51">
+        <v>2024</v>
+      </c>
+      <c r="C51" t="s">
+        <v>39</v>
+      </c>
+      <c r="D51">
+        <v>1367</v>
+      </c>
+      <c r="E51" t="b">
+        <v>0</v>
+      </c>
+      <c r="F51" t="s">
+        <v>42</v>
+      </c>
+      <c r="G51" t="s">
+        <v>45</v>
+      </c>
+      <c r="H51" t="s">
+        <v>47</v>
+      </c>
+      <c r="I51" t="s">
+        <v>51</v>
+      </c>
+      <c r="J51" s="2">
+        <v>45545.14299768519</v>
+      </c>
+      <c r="K51" t="s">
+        <v>42</v>
+      </c>
+      <c r="L51">
+        <v>-0.0003587962962962963</v>
+      </c>
+      <c r="M51">
+        <v>-31</v>
+      </c>
+      <c r="N51">
+        <v>1.642997685185185</v>
+      </c>
+      <c r="O51">
+        <v>141955</v>
+      </c>
+      <c r="P51" s="2">
+        <v>45545.33333333334</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>61</v>
+      </c>
+      <c r="R51" t="b">
+        <v>0</v>
+      </c>
+      <c r="S51">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T51" t="s">
+        <v>64</v>
+      </c>
+      <c r="U51" t="b">
+        <v>0</v>
+      </c>
+      <c r="X51" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="52" spans="1:24">
+      <c r="A52" t="s">
+        <v>24</v>
+      </c>
+      <c r="B52">
+        <v>2023</v>
+      </c>
+      <c r="C52" t="s">
+        <v>39</v>
+      </c>
+      <c r="D52">
+        <v>334</v>
+      </c>
+      <c r="E52" t="b">
+        <v>1</v>
+      </c>
+      <c r="F52" t="s">
+        <v>41</v>
+      </c>
+      <c r="H52" t="s">
+        <v>46</v>
+      </c>
+      <c r="I52" t="s">
+        <v>49</v>
+      </c>
+      <c r="J52" s="2">
+        <v>45180.90565972222</v>
+      </c>
+      <c r="K52" t="s">
+        <v>54</v>
+      </c>
+      <c r="L52">
+        <v>-0.05702546296296297</v>
+      </c>
+      <c r="M52">
+        <v>-4927</v>
+      </c>
+      <c r="N52">
+        <v>1.488993055555556</v>
+      </c>
+      <c r="O52">
+        <v>128649</v>
+      </c>
+      <c r="P52" s="2">
+        <v>45182</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>59</v>
+      </c>
+      <c r="R52" t="b">
+        <v>0</v>
+      </c>
+      <c r="S52">
+        <v>0.75</v>
+      </c>
+      <c r="T52" t="s">
+        <v>64</v>
+      </c>
+      <c r="U52" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:24">
+      <c r="A53" t="s">
+        <v>25</v>
+      </c>
+      <c r="B53">
+        <v>2023</v>
+      </c>
+      <c r="C53" t="s">
+        <v>39</v>
+      </c>
+      <c r="D53">
+        <v>343</v>
+      </c>
+      <c r="E53" t="b">
+        <v>1</v>
+      </c>
+      <c r="F53" t="s">
+        <v>41</v>
+      </c>
+      <c r="H53" t="s">
+        <v>46</v>
+      </c>
+      <c r="I53" t="s">
+        <v>50</v>
+      </c>
+      <c r="J53" s="2">
+        <v>45182.46465277778</v>
+      </c>
+      <c r="K53" t="s">
+        <v>55</v>
+      </c>
+      <c r="L53">
+        <v>-0.0003935185185185185</v>
+      </c>
+      <c r="M53">
+        <v>-34</v>
+      </c>
+      <c r="N53">
+        <v>3.047986111111111</v>
+      </c>
+      <c r="O53">
+        <v>263346</v>
+      </c>
+      <c r="P53" s="2">
+        <v>45183.04166666666</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>60</v>
+      </c>
+      <c r="R53" t="b">
+        <v>0</v>
+      </c>
+      <c r="S53">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T53" t="s">
+        <v>64</v>
+      </c>
+      <c r="U53" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:24">
+      <c r="A54" t="s">
+        <v>26</v>
+      </c>
+      <c r="B54">
+        <v>2023</v>
+      </c>
+      <c r="C54" t="s">
+        <v>39</v>
+      </c>
+      <c r="D54">
+        <v>1291</v>
+      </c>
+      <c r="E54" t="b">
+        <v>1</v>
+      </c>
+      <c r="F54" t="s">
+        <v>41</v>
+      </c>
+      <c r="H54" t="s">
+        <v>47</v>
+      </c>
+      <c r="I54" t="s">
+        <v>51</v>
+      </c>
+      <c r="J54" s="2">
+        <v>45180.95467592592</v>
+      </c>
+      <c r="K54" t="s">
+        <v>56</v>
+      </c>
+      <c r="L54">
+        <v>-0.0001157407407407407</v>
+      </c>
+      <c r="M54">
+        <v>-10</v>
+      </c>
+      <c r="N54">
+        <v>1.454675925925926</v>
+      </c>
+      <c r="O54">
+        <v>125684</v>
+      </c>
+      <c r="P54" s="2">
+        <v>45181.33333333334</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>61</v>
+      </c>
+      <c r="R54" t="b">
+        <v>0</v>
+      </c>
+      <c r="S54">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T54" t="s">
+        <v>64</v>
+      </c>
+      <c r="U54" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:24">
+      <c r="A55" t="s">
+        <v>27</v>
+      </c>
+      <c r="B55">
+        <v>2023</v>
+      </c>
+      <c r="C55" t="s">
+        <v>39</v>
+      </c>
+      <c r="D55">
+        <v>423</v>
+      </c>
+      <c r="E55" t="b">
+        <v>1</v>
+      </c>
+      <c r="F55" t="s">
+        <v>41</v>
+      </c>
+      <c r="H55" t="s">
+        <v>46</v>
+      </c>
+      <c r="I55" t="s">
+        <v>52</v>
+      </c>
+      <c r="J55" s="2">
+        <v>45183.8446412037</v>
+      </c>
+      <c r="K55" t="s">
+        <v>56</v>
+      </c>
+      <c r="L55">
+        <v>-0.02489583333333333</v>
+      </c>
+      <c r="M55">
+        <v>-2151</v>
+      </c>
+      <c r="N55">
+        <v>4.427974537037037</v>
+      </c>
+      <c r="O55">
+        <v>382577</v>
+      </c>
+      <c r="P55" s="2">
+        <v>45184.79166666666</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>62</v>
+      </c>
+      <c r="R55" t="b">
+        <v>0</v>
+      </c>
+      <c r="S55">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T55" t="s">
+        <v>64</v>
+      </c>
+      <c r="U55" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:24">
+      <c r="A56" t="s">
+        <v>28</v>
+      </c>
+      <c r="B56">
+        <v>2023</v>
+      </c>
+      <c r="C56" t="s">
+        <v>39</v>
+      </c>
+      <c r="D56">
+        <v>1334</v>
+      </c>
+      <c r="E56" t="b">
+        <v>1</v>
+      </c>
+      <c r="F56" t="s">
+        <v>41</v>
+      </c>
+      <c r="H56" t="s">
+        <v>47</v>
+      </c>
+      <c r="I56" t="s">
+        <v>51</v>
+      </c>
+      <c r="J56" s="2">
+        <v>45180.98311342593</v>
+      </c>
+      <c r="K56" t="s">
+        <v>56</v>
+      </c>
+      <c r="L56">
+        <v>-0.0002083333333333333</v>
+      </c>
+      <c r="M56">
+        <v>-18</v>
+      </c>
+      <c r="N56">
+        <v>1.483113425925926</v>
+      </c>
+      <c r="O56">
+        <v>128141</v>
+      </c>
+      <c r="P56" s="2">
+        <v>45181.33333333334</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>61</v>
+      </c>
+      <c r="R56" t="b">
+        <v>0</v>
+      </c>
+      <c r="S56">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T56" t="s">
+        <v>64</v>
+      </c>
+      <c r="U56" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:24">
+      <c r="A57" t="s">
+        <v>31</v>
+      </c>
+      <c r="B57">
+        <v>2022</v>
+      </c>
+      <c r="C57" t="s">
+        <v>39</v>
+      </c>
+      <c r="D57">
+        <v>275</v>
+      </c>
+      <c r="E57" t="b">
+        <v>1</v>
+      </c>
+      <c r="F57" t="s">
+        <v>41</v>
+      </c>
+      <c r="H57" t="s">
+        <v>46</v>
+      </c>
+      <c r="I57" t="s">
+        <v>50</v>
+      </c>
+      <c r="J57" s="2">
+        <v>44817.39240740741</v>
+      </c>
+      <c r="K57" t="s">
+        <v>57</v>
+      </c>
+      <c r="L57">
+        <v>-0.003252314814814815</v>
+      </c>
+      <c r="M57">
+        <v>-281</v>
+      </c>
+      <c r="N57">
+        <v>1.975740740740741</v>
+      </c>
+      <c r="O57">
+        <v>170704</v>
+      </c>
+      <c r="P57" s="2">
+        <v>44819.04166666666</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>60</v>
+      </c>
+      <c r="R57" t="b">
+        <v>0</v>
+      </c>
+      <c r="S57">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T57" t="s">
+        <v>64</v>
+      </c>
+      <c r="U57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:24">
+      <c r="A58" t="s">
+        <v>32</v>
+      </c>
+      <c r="B58">
+        <v>2022</v>
+      </c>
+      <c r="C58" t="s">
+        <v>39</v>
+      </c>
+      <c r="D58">
+        <v>127</v>
+      </c>
+      <c r="E58" t="b">
+        <v>1</v>
+      </c>
+      <c r="F58" t="s">
+        <v>41</v>
+      </c>
+      <c r="H58" t="s">
+        <v>46</v>
+      </c>
+      <c r="I58" t="s">
+        <v>53</v>
+      </c>
+      <c r="J58" s="2">
+        <v>44818.26855324074</v>
+      </c>
+      <c r="K58" t="s">
+        <v>58</v>
+      </c>
+      <c r="L58">
+        <v>-0.0005439814814814814</v>
+      </c>
+      <c r="M58">
+        <v>-47</v>
+      </c>
+      <c r="N58">
+        <v>2.851886574074074</v>
+      </c>
+      <c r="O58">
+        <v>246403</v>
+      </c>
+      <c r="P58" s="2">
+        <v>44819.875</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>63</v>
+      </c>
+      <c r="R58" t="b">
+        <v>0</v>
+      </c>
+      <c r="S58">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T58" t="s">
+        <v>64</v>
+      </c>
+      <c r="U58" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:24">
+      <c r="A59" t="s">
+        <v>33</v>
+      </c>
+      <c r="B59">
+        <v>2022</v>
+      </c>
+      <c r="C59" t="s">
+        <v>39</v>
+      </c>
+      <c r="D59">
+        <v>549</v>
+      </c>
+      <c r="E59" t="b">
+        <v>1</v>
+      </c>
+      <c r="F59" t="s">
+        <v>41</v>
+      </c>
+      <c r="H59" t="s">
+        <v>46</v>
+      </c>
+      <c r="I59" t="s">
+        <v>52</v>
+      </c>
+      <c r="J59" s="2">
+        <v>44820.2553125</v>
+      </c>
+      <c r="K59" t="s">
+        <v>55</v>
+      </c>
+      <c r="L59">
+        <v>-0.0003587962962962963</v>
+      </c>
+      <c r="M59">
+        <v>-31</v>
+      </c>
+      <c r="N59">
+        <v>4.838645833333334</v>
+      </c>
+      <c r="O59">
+        <v>418059</v>
+      </c>
+      <c r="P59" s="2">
+        <v>44820.79166666666</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>62</v>
+      </c>
+      <c r="R59" t="b">
+        <v>0</v>
+      </c>
+      <c r="S59">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T59" t="s">
+        <v>64</v>
+      </c>
+      <c r="U59" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:24">
+      <c r="A60" t="s">
+        <v>34</v>
+      </c>
+      <c r="B60">
+        <v>2022</v>
+      </c>
+      <c r="C60" t="s">
+        <v>39</v>
+      </c>
+      <c r="D60">
+        <v>1005</v>
+      </c>
+      <c r="E60" t="b">
+        <v>0</v>
+      </c>
+      <c r="F60" t="s">
+        <v>43</v>
+      </c>
+      <c r="H60" t="s">
+        <v>47</v>
+      </c>
+      <c r="I60" t="s">
+        <v>53</v>
+      </c>
+      <c r="J60" s="2">
+        <v>44819.50680555555</v>
+      </c>
+      <c r="L60">
+        <v>-0.0002777777777777778</v>
+      </c>
+      <c r="M60">
+        <v>-24</v>
+      </c>
+      <c r="N60">
+        <v>4.006805555555555</v>
+      </c>
+      <c r="O60">
+        <v>346188</v>
+      </c>
+      <c r="P60" s="2">
+        <v>44819.95833333334</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>63</v>
+      </c>
+      <c r="R60" t="b">
+        <v>0</v>
+      </c>
+      <c r="S60">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T60" t="s">
+        <v>64</v>
+      </c>
+      <c r="U60" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:24">
+      <c r="A61" t="s">
+        <v>35</v>
+      </c>
+      <c r="B61">
+        <v>2022</v>
+      </c>
+      <c r="C61" t="s">
+        <v>39</v>
+      </c>
+      <c r="D61">
+        <v>1205</v>
+      </c>
+      <c r="E61" t="b">
+        <v>0</v>
+      </c>
+      <c r="F61" t="s">
+        <v>44</v>
+      </c>
+      <c r="H61" t="s">
+        <v>47</v>
+      </c>
+      <c r="I61" t="s">
+        <v>50</v>
+      </c>
+      <c r="J61" s="2">
+        <v>44818.92413194444</v>
+      </c>
+      <c r="L61">
+        <v>-0.0002199074074074074</v>
+      </c>
+      <c r="M61">
+        <v>-19</v>
+      </c>
+      <c r="N61">
+        <v>3.424131944444444</v>
+      </c>
+      <c r="O61">
+        <v>295845</v>
+      </c>
+      <c r="P61" s="2">
+        <v>44819.125</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>60</v>
+      </c>
+      <c r="R61" t="b">
+        <v>0</v>
+      </c>
+      <c r="S61">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T61" t="s">
+        <v>64</v>
+      </c>
+      <c r="U61" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:24">
+      <c r="A62" t="s">
+        <v>36</v>
+      </c>
+      <c r="B62">
+        <v>2022</v>
+      </c>
+      <c r="C62" t="s">
+        <v>39</v>
+      </c>
+      <c r="D62">
+        <v>1268</v>
+      </c>
+      <c r="E62" t="b">
+        <v>0</v>
+      </c>
+      <c r="F62" t="s">
+        <v>44</v>
+      </c>
+      <c r="H62" t="s">
+        <v>47</v>
+      </c>
+      <c r="I62" t="s">
+        <v>50</v>
+      </c>
+      <c r="J62" s="2">
+        <v>44818.92489583333</v>
+      </c>
+      <c r="L62">
+        <v>-0.0008333333333333334</v>
+      </c>
+      <c r="M62">
+        <v>-72</v>
+      </c>
+      <c r="N62">
+        <v>3.424895833333333</v>
+      </c>
+      <c r="O62">
+        <v>295911</v>
+      </c>
+      <c r="P62" s="2">
+        <v>44819.125</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>60</v>
+      </c>
+      <c r="R62" t="b">
+        <v>0</v>
+      </c>
+      <c r="S62">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T62" t="s">
+        <v>64</v>
+      </c>
+      <c r="U62" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:24">
+      <c r="A63" t="s">
+        <v>37</v>
+      </c>
+      <c r="B63">
+        <v>2021</v>
+      </c>
+      <c r="C63" t="s">
+        <v>39</v>
+      </c>
+      <c r="D63">
+        <v>162</v>
+      </c>
+      <c r="E63" t="b">
+        <v>1</v>
+      </c>
+      <c r="F63" t="s">
+        <v>41</v>
+      </c>
+      <c r="H63" t="s">
+        <v>48</v>
+      </c>
+      <c r="I63" t="s">
+        <v>52</v>
+      </c>
+      <c r="J63" s="2">
+        <v>44456.22016203704</v>
+      </c>
+      <c r="K63" t="s">
+        <v>55</v>
+      </c>
+      <c r="L63">
+        <v>-0.001018518518518518</v>
+      </c>
+      <c r="M63">
+        <v>-88</v>
+      </c>
+      <c r="N63">
+        <v>4.803495370370371</v>
+      </c>
+      <c r="O63">
+        <v>415022</v>
+      </c>
+      <c r="P63" s="2">
+        <v>44456.79166666666</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>62</v>
+      </c>
+      <c r="R63" t="b">
+        <v>0</v>
+      </c>
+      <c r="S63">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T63" t="s">
+        <v>64</v>
+      </c>
+      <c r="U63" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:24">
+      <c r="A64" t="s">
+        <v>37</v>
+      </c>
+      <c r="B64">
+        <v>2021</v>
+      </c>
+      <c r="C64" t="s">
+        <v>39</v>
+      </c>
+      <c r="D64">
+        <v>162</v>
+      </c>
+      <c r="E64" t="b">
+        <v>1</v>
+      </c>
+      <c r="F64" t="s">
+        <v>41</v>
+      </c>
+      <c r="H64" t="s">
+        <v>48</v>
+      </c>
+      <c r="I64" t="s">
+        <v>52</v>
+      </c>
+      <c r="J64" s="2">
+        <v>44456.22016203704</v>
+      </c>
+      <c r="K64" t="s">
+        <v>55</v>
+      </c>
+      <c r="L64">
+        <v>-0.001018518518518518</v>
+      </c>
+      <c r="M64">
+        <v>-88</v>
+      </c>
+      <c r="N64">
+        <v>4.803495370370371</v>
+      </c>
+      <c r="O64">
+        <v>415022</v>
+      </c>
+      <c r="P64" s="2">
+        <v>44456.79166666666</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>62</v>
+      </c>
+      <c r="R64" t="b">
+        <v>0</v>
+      </c>
+      <c r="S64">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T64" t="s">
+        <v>64</v>
+      </c>
+      <c r="U64" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21">
+      <c r="A65" t="s">
+        <v>37</v>
+      </c>
+      <c r="B65" t="s">
+        <v>38</v>
+      </c>
+      <c r="C65" t="s">
+        <v>39</v>
+      </c>
+      <c r="D65" t="s">
+        <v>40</v>
+      </c>
+      <c r="E65" t="b">
+        <v>1</v>
+      </c>
+      <c r="F65" t="s">
+        <v>41</v>
+      </c>
+      <c r="H65" t="s">
+        <v>48</v>
+      </c>
+      <c r="I65" t="s">
+        <v>52</v>
+      </c>
+      <c r="J65" s="2">
+        <v>44456.22016203704</v>
+      </c>
+      <c r="K65" t="s">
+        <v>55</v>
+      </c>
+      <c r="L65" s="3">
+        <v>-0.001018518518518518</v>
+      </c>
+      <c r="M65">
+        <v>-88</v>
+      </c>
+      <c r="N65" s="3">
+        <v>4.803495370370371</v>
+      </c>
+      <c r="O65">
+        <v>415022</v>
+      </c>
+      <c r="P65" s="2">
+        <v>44456.79166666666</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>62</v>
+      </c>
+      <c r="R65" t="b">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T65" t="s">
+        <v>64</v>
+      </c>
+      <c r="U65" t="b">
         <v>0</v>
       </c>
     </row>

--- a/TOR330 Data/5. Clean Data for Data Visualisation/TOR330_negative_duration_checkpoints_bib_df.xlsx
+++ b/TOR330 Data/5. Clean Data for Data Visualisation/TOR330_negative_duration_checkpoints_bib_df.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="65">
   <si>
     <t>PK</t>
   </si>
@@ -571,7 +571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X65"/>
+  <dimension ref="A1:X119"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:24">
@@ -4545,18 +4545,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:21">
+    <row r="65" spans="1:24">
       <c r="A65" t="s">
         <v>37</v>
       </c>
-      <c r="B65" t="s">
-        <v>38</v>
+      <c r="B65">
+        <v>2021</v>
       </c>
       <c r="C65" t="s">
         <v>39</v>
       </c>
-      <c r="D65" t="s">
-        <v>40</v>
+      <c r="D65">
+        <v>162</v>
       </c>
       <c r="E65" t="b">
         <v>1</v>
@@ -4576,13 +4576,13 @@
       <c r="K65" t="s">
         <v>55</v>
       </c>
-      <c r="L65" s="3">
+      <c r="L65">
         <v>-0.001018518518518518</v>
       </c>
       <c r="M65">
         <v>-88</v>
       </c>
-      <c r="N65" s="3">
+      <c r="N65">
         <v>4.803495370370371</v>
       </c>
       <c r="O65">
@@ -4597,13 +4597,3343 @@
       <c r="R65" t="b">
         <v>0</v>
       </c>
-      <c r="S65" s="3">
+      <c r="S65">
         <v>0.08333333333333333</v>
       </c>
       <c r="T65" t="s">
         <v>64</v>
       </c>
       <c r="U65" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:24">
+      <c r="A66" t="s">
+        <v>37</v>
+      </c>
+      <c r="B66">
+        <v>2021</v>
+      </c>
+      <c r="C66" t="s">
+        <v>39</v>
+      </c>
+      <c r="D66">
+        <v>162</v>
+      </c>
+      <c r="E66" t="b">
+        <v>1</v>
+      </c>
+      <c r="F66" t="s">
+        <v>41</v>
+      </c>
+      <c r="H66" t="s">
+        <v>48</v>
+      </c>
+      <c r="I66" t="s">
+        <v>52</v>
+      </c>
+      <c r="J66" s="2">
+        <v>44456.22016203704</v>
+      </c>
+      <c r="K66" t="s">
+        <v>55</v>
+      </c>
+      <c r="L66">
+        <v>-0.001018518518518518</v>
+      </c>
+      <c r="M66">
+        <v>-88</v>
+      </c>
+      <c r="N66">
+        <v>4.803495370370371</v>
+      </c>
+      <c r="O66">
+        <v>415022</v>
+      </c>
+      <c r="P66" s="2">
+        <v>44456.79166666666</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>62</v>
+      </c>
+      <c r="R66" t="b">
+        <v>0</v>
+      </c>
+      <c r="S66">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T66" t="s">
+        <v>64</v>
+      </c>
+      <c r="U66" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:24">
+      <c r="A67" t="s">
+        <v>31</v>
+      </c>
+      <c r="B67">
+        <v>2022</v>
+      </c>
+      <c r="C67" t="s">
+        <v>39</v>
+      </c>
+      <c r="D67">
+        <v>275</v>
+      </c>
+      <c r="E67" t="b">
+        <v>1</v>
+      </c>
+      <c r="F67" t="s">
+        <v>41</v>
+      </c>
+      <c r="H67" t="s">
+        <v>46</v>
+      </c>
+      <c r="I67" t="s">
+        <v>50</v>
+      </c>
+      <c r="J67" s="2">
+        <v>44817.39240740741</v>
+      </c>
+      <c r="K67" t="s">
+        <v>57</v>
+      </c>
+      <c r="L67">
+        <v>-0.003252314814814815</v>
+      </c>
+      <c r="M67">
+        <v>-281</v>
+      </c>
+      <c r="N67">
+        <v>1.975740740740741</v>
+      </c>
+      <c r="O67">
+        <v>170704</v>
+      </c>
+      <c r="P67" s="2">
+        <v>44819.04166666666</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>60</v>
+      </c>
+      <c r="R67" t="b">
+        <v>0</v>
+      </c>
+      <c r="S67">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T67" t="s">
+        <v>64</v>
+      </c>
+      <c r="U67" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:24">
+      <c r="A68" t="s">
+        <v>32</v>
+      </c>
+      <c r="B68">
+        <v>2022</v>
+      </c>
+      <c r="C68" t="s">
+        <v>39</v>
+      </c>
+      <c r="D68">
+        <v>127</v>
+      </c>
+      <c r="E68" t="b">
+        <v>1</v>
+      </c>
+      <c r="F68" t="s">
+        <v>41</v>
+      </c>
+      <c r="H68" t="s">
+        <v>46</v>
+      </c>
+      <c r="I68" t="s">
+        <v>53</v>
+      </c>
+      <c r="J68" s="2">
+        <v>44818.26855324074</v>
+      </c>
+      <c r="K68" t="s">
+        <v>58</v>
+      </c>
+      <c r="L68">
+        <v>-0.0005439814814814814</v>
+      </c>
+      <c r="M68">
+        <v>-47</v>
+      </c>
+      <c r="N68">
+        <v>2.851886574074074</v>
+      </c>
+      <c r="O68">
+        <v>246403</v>
+      </c>
+      <c r="P68" s="2">
+        <v>44819.875</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>63</v>
+      </c>
+      <c r="R68" t="b">
+        <v>0</v>
+      </c>
+      <c r="S68">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T68" t="s">
+        <v>64</v>
+      </c>
+      <c r="U68" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:24">
+      <c r="A69" t="s">
+        <v>33</v>
+      </c>
+      <c r="B69">
+        <v>2022</v>
+      </c>
+      <c r="C69" t="s">
+        <v>39</v>
+      </c>
+      <c r="D69">
+        <v>549</v>
+      </c>
+      <c r="E69" t="b">
+        <v>1</v>
+      </c>
+      <c r="F69" t="s">
+        <v>41</v>
+      </c>
+      <c r="H69" t="s">
+        <v>46</v>
+      </c>
+      <c r="I69" t="s">
+        <v>52</v>
+      </c>
+      <c r="J69" s="2">
+        <v>44820.2553125</v>
+      </c>
+      <c r="K69" t="s">
+        <v>55</v>
+      </c>
+      <c r="L69">
+        <v>-0.0003587962962962963</v>
+      </c>
+      <c r="M69">
+        <v>-31</v>
+      </c>
+      <c r="N69">
+        <v>4.838645833333334</v>
+      </c>
+      <c r="O69">
+        <v>418059</v>
+      </c>
+      <c r="P69" s="2">
+        <v>44820.79166666666</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>62</v>
+      </c>
+      <c r="R69" t="b">
+        <v>0</v>
+      </c>
+      <c r="S69">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T69" t="s">
+        <v>64</v>
+      </c>
+      <c r="U69" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:24">
+      <c r="A70" t="s">
+        <v>34</v>
+      </c>
+      <c r="B70">
+        <v>2022</v>
+      </c>
+      <c r="C70" t="s">
+        <v>39</v>
+      </c>
+      <c r="D70">
+        <v>1005</v>
+      </c>
+      <c r="E70" t="b">
+        <v>0</v>
+      </c>
+      <c r="F70" t="s">
+        <v>43</v>
+      </c>
+      <c r="H70" t="s">
+        <v>47</v>
+      </c>
+      <c r="I70" t="s">
+        <v>53</v>
+      </c>
+      <c r="J70" s="2">
+        <v>44819.50680555555</v>
+      </c>
+      <c r="L70">
+        <v>-0.0002777777777777778</v>
+      </c>
+      <c r="M70">
+        <v>-24</v>
+      </c>
+      <c r="N70">
+        <v>4.006805555555555</v>
+      </c>
+      <c r="O70">
+        <v>346188</v>
+      </c>
+      <c r="P70" s="2">
+        <v>44819.95833333334</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>63</v>
+      </c>
+      <c r="R70" t="b">
+        <v>0</v>
+      </c>
+      <c r="S70">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T70" t="s">
+        <v>64</v>
+      </c>
+      <c r="U70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:24">
+      <c r="A71" t="s">
+        <v>35</v>
+      </c>
+      <c r="B71">
+        <v>2022</v>
+      </c>
+      <c r="C71" t="s">
+        <v>39</v>
+      </c>
+      <c r="D71">
+        <v>1205</v>
+      </c>
+      <c r="E71" t="b">
+        <v>0</v>
+      </c>
+      <c r="F71" t="s">
+        <v>44</v>
+      </c>
+      <c r="H71" t="s">
+        <v>47</v>
+      </c>
+      <c r="I71" t="s">
+        <v>50</v>
+      </c>
+      <c r="J71" s="2">
+        <v>44818.92413194444</v>
+      </c>
+      <c r="L71">
+        <v>-0.0002199074074074074</v>
+      </c>
+      <c r="M71">
+        <v>-19</v>
+      </c>
+      <c r="N71">
+        <v>3.424131944444444</v>
+      </c>
+      <c r="O71">
+        <v>295845</v>
+      </c>
+      <c r="P71" s="2">
+        <v>44819.125</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>60</v>
+      </c>
+      <c r="R71" t="b">
+        <v>0</v>
+      </c>
+      <c r="S71">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T71" t="s">
+        <v>64</v>
+      </c>
+      <c r="U71" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:24">
+      <c r="A72" t="s">
+        <v>36</v>
+      </c>
+      <c r="B72">
+        <v>2022</v>
+      </c>
+      <c r="C72" t="s">
+        <v>39</v>
+      </c>
+      <c r="D72">
+        <v>1268</v>
+      </c>
+      <c r="E72" t="b">
+        <v>0</v>
+      </c>
+      <c r="F72" t="s">
+        <v>44</v>
+      </c>
+      <c r="H72" t="s">
+        <v>47</v>
+      </c>
+      <c r="I72" t="s">
+        <v>50</v>
+      </c>
+      <c r="J72" s="2">
+        <v>44818.92489583333</v>
+      </c>
+      <c r="L72">
+        <v>-0.0008333333333333334</v>
+      </c>
+      <c r="M72">
+        <v>-72</v>
+      </c>
+      <c r="N72">
+        <v>3.424895833333333</v>
+      </c>
+      <c r="O72">
+        <v>295911</v>
+      </c>
+      <c r="P72" s="2">
+        <v>44819.125</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>60</v>
+      </c>
+      <c r="R72" t="b">
+        <v>0</v>
+      </c>
+      <c r="S72">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T72" t="s">
+        <v>64</v>
+      </c>
+      <c r="U72" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:24">
+      <c r="A73" t="s">
+        <v>24</v>
+      </c>
+      <c r="B73">
+        <v>2023</v>
+      </c>
+      <c r="C73" t="s">
+        <v>39</v>
+      </c>
+      <c r="D73">
+        <v>334</v>
+      </c>
+      <c r="E73" t="b">
+        <v>1</v>
+      </c>
+      <c r="F73" t="s">
+        <v>41</v>
+      </c>
+      <c r="H73" t="s">
+        <v>46</v>
+      </c>
+      <c r="I73" t="s">
+        <v>49</v>
+      </c>
+      <c r="J73" s="2">
+        <v>45180.90565972222</v>
+      </c>
+      <c r="K73" t="s">
+        <v>54</v>
+      </c>
+      <c r="L73">
+        <v>-0.05702546296296297</v>
+      </c>
+      <c r="M73">
+        <v>-4927</v>
+      </c>
+      <c r="N73">
+        <v>1.488993055555556</v>
+      </c>
+      <c r="O73">
+        <v>128649</v>
+      </c>
+      <c r="P73" s="2">
+        <v>45182</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>59</v>
+      </c>
+      <c r="R73" t="b">
+        <v>0</v>
+      </c>
+      <c r="S73">
+        <v>0.75</v>
+      </c>
+      <c r="T73" t="s">
+        <v>64</v>
+      </c>
+      <c r="U73" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:24">
+      <c r="A74" t="s">
+        <v>25</v>
+      </c>
+      <c r="B74">
+        <v>2023</v>
+      </c>
+      <c r="C74" t="s">
+        <v>39</v>
+      </c>
+      <c r="D74">
+        <v>343</v>
+      </c>
+      <c r="E74" t="b">
+        <v>1</v>
+      </c>
+      <c r="F74" t="s">
+        <v>41</v>
+      </c>
+      <c r="H74" t="s">
+        <v>46</v>
+      </c>
+      <c r="I74" t="s">
+        <v>50</v>
+      </c>
+      <c r="J74" s="2">
+        <v>45182.46465277778</v>
+      </c>
+      <c r="K74" t="s">
+        <v>55</v>
+      </c>
+      <c r="L74">
+        <v>-0.0003935185185185185</v>
+      </c>
+      <c r="M74">
+        <v>-34</v>
+      </c>
+      <c r="N74">
+        <v>3.047986111111111</v>
+      </c>
+      <c r="O74">
+        <v>263346</v>
+      </c>
+      <c r="P74" s="2">
+        <v>45183.04166666666</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>60</v>
+      </c>
+      <c r="R74" t="b">
+        <v>0</v>
+      </c>
+      <c r="S74">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T74" t="s">
+        <v>64</v>
+      </c>
+      <c r="U74" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:24">
+      <c r="A75" t="s">
+        <v>26</v>
+      </c>
+      <c r="B75">
+        <v>2023</v>
+      </c>
+      <c r="C75" t="s">
+        <v>39</v>
+      </c>
+      <c r="D75">
+        <v>1291</v>
+      </c>
+      <c r="E75" t="b">
+        <v>1</v>
+      </c>
+      <c r="F75" t="s">
+        <v>41</v>
+      </c>
+      <c r="H75" t="s">
+        <v>47</v>
+      </c>
+      <c r="I75" t="s">
+        <v>51</v>
+      </c>
+      <c r="J75" s="2">
+        <v>45180.95467592592</v>
+      </c>
+      <c r="K75" t="s">
+        <v>56</v>
+      </c>
+      <c r="L75">
+        <v>-0.0001157407407407407</v>
+      </c>
+      <c r="M75">
+        <v>-10</v>
+      </c>
+      <c r="N75">
+        <v>1.454675925925926</v>
+      </c>
+      <c r="O75">
+        <v>125684</v>
+      </c>
+      <c r="P75" s="2">
+        <v>45181.33333333334</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>61</v>
+      </c>
+      <c r="R75" t="b">
+        <v>0</v>
+      </c>
+      <c r="S75">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T75" t="s">
+        <v>64</v>
+      </c>
+      <c r="U75" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:24">
+      <c r="A76" t="s">
+        <v>27</v>
+      </c>
+      <c r="B76">
+        <v>2023</v>
+      </c>
+      <c r="C76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D76">
+        <v>423</v>
+      </c>
+      <c r="E76" t="b">
+        <v>1</v>
+      </c>
+      <c r="F76" t="s">
+        <v>41</v>
+      </c>
+      <c r="H76" t="s">
+        <v>46</v>
+      </c>
+      <c r="I76" t="s">
+        <v>52</v>
+      </c>
+      <c r="J76" s="2">
+        <v>45183.8446412037</v>
+      </c>
+      <c r="K76" t="s">
+        <v>56</v>
+      </c>
+      <c r="L76">
+        <v>-0.02489583333333333</v>
+      </c>
+      <c r="M76">
+        <v>-2151</v>
+      </c>
+      <c r="N76">
+        <v>4.427974537037037</v>
+      </c>
+      <c r="O76">
+        <v>382577</v>
+      </c>
+      <c r="P76" s="2">
+        <v>45184.79166666666</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>62</v>
+      </c>
+      <c r="R76" t="b">
+        <v>0</v>
+      </c>
+      <c r="S76">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T76" t="s">
+        <v>64</v>
+      </c>
+      <c r="U76" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:24">
+      <c r="A77" t="s">
+        <v>28</v>
+      </c>
+      <c r="B77">
+        <v>2023</v>
+      </c>
+      <c r="C77" t="s">
+        <v>39</v>
+      </c>
+      <c r="D77">
+        <v>1334</v>
+      </c>
+      <c r="E77" t="b">
+        <v>1</v>
+      </c>
+      <c r="F77" t="s">
+        <v>41</v>
+      </c>
+      <c r="H77" t="s">
+        <v>47</v>
+      </c>
+      <c r="I77" t="s">
+        <v>51</v>
+      </c>
+      <c r="J77" s="2">
+        <v>45180.98311342593</v>
+      </c>
+      <c r="K77" t="s">
+        <v>56</v>
+      </c>
+      <c r="L77">
+        <v>-0.0002083333333333333</v>
+      </c>
+      <c r="M77">
+        <v>-18</v>
+      </c>
+      <c r="N77">
+        <v>1.483113425925926</v>
+      </c>
+      <c r="O77">
+        <v>128141</v>
+      </c>
+      <c r="P77" s="2">
+        <v>45181.33333333334</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>61</v>
+      </c>
+      <c r="R77" t="b">
+        <v>0</v>
+      </c>
+      <c r="S77">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T77" t="s">
+        <v>64</v>
+      </c>
+      <c r="U77" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:24">
+      <c r="A78" t="s">
+        <v>29</v>
+      </c>
+      <c r="B78">
+        <v>2024</v>
+      </c>
+      <c r="C78" t="s">
+        <v>39</v>
+      </c>
+      <c r="D78">
+        <v>404</v>
+      </c>
+      <c r="E78" t="b">
+        <v>1</v>
+      </c>
+      <c r="F78" t="s">
+        <v>41</v>
+      </c>
+      <c r="H78" t="s">
+        <v>46</v>
+      </c>
+      <c r="I78" t="s">
+        <v>53</v>
+      </c>
+      <c r="J78" s="2">
+        <v>45546.77756944444</v>
+      </c>
+      <c r="K78" t="s">
+        <v>54</v>
+      </c>
+      <c r="L78">
+        <v>-0.007534722222222222</v>
+      </c>
+      <c r="M78">
+        <v>-651</v>
+      </c>
+      <c r="N78">
+        <v>3.360902777777778</v>
+      </c>
+      <c r="O78">
+        <v>290382</v>
+      </c>
+      <c r="P78" s="2">
+        <v>45547.875</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>63</v>
+      </c>
+      <c r="R78" t="b">
+        <v>0</v>
+      </c>
+      <c r="S78">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T78" t="s">
+        <v>64</v>
+      </c>
+      <c r="U78" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:24">
+      <c r="A79" t="s">
+        <v>30</v>
+      </c>
+      <c r="B79">
+        <v>2024</v>
+      </c>
+      <c r="C79" t="s">
+        <v>39</v>
+      </c>
+      <c r="D79">
+        <v>1367</v>
+      </c>
+      <c r="E79" t="b">
+        <v>0</v>
+      </c>
+      <c r="F79" t="s">
+        <v>42</v>
+      </c>
+      <c r="G79" t="s">
+        <v>45</v>
+      </c>
+      <c r="H79" t="s">
+        <v>47</v>
+      </c>
+      <c r="I79" t="s">
+        <v>51</v>
+      </c>
+      <c r="J79" s="2">
+        <v>45545.14299768519</v>
+      </c>
+      <c r="K79" t="s">
+        <v>42</v>
+      </c>
+      <c r="L79">
+        <v>-0.0003587962962962963</v>
+      </c>
+      <c r="M79">
+        <v>-31</v>
+      </c>
+      <c r="N79">
+        <v>1.642997685185185</v>
+      </c>
+      <c r="O79">
+        <v>141955</v>
+      </c>
+      <c r="P79" s="2">
+        <v>45545.33333333334</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>61</v>
+      </c>
+      <c r="R79" t="b">
+        <v>0</v>
+      </c>
+      <c r="S79">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T79" t="s">
+        <v>64</v>
+      </c>
+      <c r="U79" t="b">
+        <v>0</v>
+      </c>
+      <c r="X79" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="80" spans="1:24">
+      <c r="A80" t="s">
+        <v>29</v>
+      </c>
+      <c r="B80">
+        <v>2024</v>
+      </c>
+      <c r="C80" t="s">
+        <v>39</v>
+      </c>
+      <c r="D80">
+        <v>404</v>
+      </c>
+      <c r="E80" t="b">
+        <v>1</v>
+      </c>
+      <c r="F80" t="s">
+        <v>41</v>
+      </c>
+      <c r="H80" t="s">
+        <v>46</v>
+      </c>
+      <c r="I80" t="s">
+        <v>53</v>
+      </c>
+      <c r="J80" s="2">
+        <v>45546.77756944444</v>
+      </c>
+      <c r="K80" t="s">
+        <v>54</v>
+      </c>
+      <c r="L80">
+        <v>-0.007534722222222222</v>
+      </c>
+      <c r="M80">
+        <v>-651</v>
+      </c>
+      <c r="N80">
+        <v>3.360902777777778</v>
+      </c>
+      <c r="O80">
+        <v>290382</v>
+      </c>
+      <c r="P80" s="2">
+        <v>45547.875</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>63</v>
+      </c>
+      <c r="R80" t="b">
+        <v>0</v>
+      </c>
+      <c r="S80">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T80" t="s">
+        <v>64</v>
+      </c>
+      <c r="U80" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:24">
+      <c r="A81" t="s">
+        <v>30</v>
+      </c>
+      <c r="B81">
+        <v>2024</v>
+      </c>
+      <c r="C81" t="s">
+        <v>39</v>
+      </c>
+      <c r="D81">
+        <v>1367</v>
+      </c>
+      <c r="E81" t="b">
+        <v>0</v>
+      </c>
+      <c r="F81" t="s">
+        <v>42</v>
+      </c>
+      <c r="G81" t="s">
+        <v>45</v>
+      </c>
+      <c r="H81" t="s">
+        <v>47</v>
+      </c>
+      <c r="I81" t="s">
+        <v>51</v>
+      </c>
+      <c r="J81" s="2">
+        <v>45545.14299768519</v>
+      </c>
+      <c r="K81" t="s">
+        <v>42</v>
+      </c>
+      <c r="L81">
+        <v>-0.0003587962962962963</v>
+      </c>
+      <c r="M81">
+        <v>-31</v>
+      </c>
+      <c r="N81">
+        <v>1.642997685185185</v>
+      </c>
+      <c r="O81">
+        <v>141955</v>
+      </c>
+      <c r="P81" s="2">
+        <v>45545.33333333334</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>61</v>
+      </c>
+      <c r="R81" t="b">
+        <v>0</v>
+      </c>
+      <c r="S81">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T81" t="s">
+        <v>64</v>
+      </c>
+      <c r="U81" t="b">
+        <v>0</v>
+      </c>
+      <c r="X81" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="82" spans="1:24">
+      <c r="A82" t="s">
+        <v>24</v>
+      </c>
+      <c r="B82">
+        <v>2023</v>
+      </c>
+      <c r="C82" t="s">
+        <v>39</v>
+      </c>
+      <c r="D82">
+        <v>334</v>
+      </c>
+      <c r="E82" t="b">
+        <v>1</v>
+      </c>
+      <c r="F82" t="s">
+        <v>41</v>
+      </c>
+      <c r="H82" t="s">
+        <v>46</v>
+      </c>
+      <c r="I82" t="s">
+        <v>49</v>
+      </c>
+      <c r="J82" s="2">
+        <v>45180.90565972222</v>
+      </c>
+      <c r="K82" t="s">
+        <v>54</v>
+      </c>
+      <c r="L82">
+        <v>-0.05702546296296297</v>
+      </c>
+      <c r="M82">
+        <v>-4927</v>
+      </c>
+      <c r="N82">
+        <v>1.488993055555556</v>
+      </c>
+      <c r="O82">
+        <v>128649</v>
+      </c>
+      <c r="P82" s="2">
+        <v>45182</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>59</v>
+      </c>
+      <c r="R82" t="b">
+        <v>0</v>
+      </c>
+      <c r="S82">
+        <v>0.75</v>
+      </c>
+      <c r="T82" t="s">
+        <v>64</v>
+      </c>
+      <c r="U82" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:24">
+      <c r="A83" t="s">
+        <v>25</v>
+      </c>
+      <c r="B83">
+        <v>2023</v>
+      </c>
+      <c r="C83" t="s">
+        <v>39</v>
+      </c>
+      <c r="D83">
+        <v>343</v>
+      </c>
+      <c r="E83" t="b">
+        <v>1</v>
+      </c>
+      <c r="F83" t="s">
+        <v>41</v>
+      </c>
+      <c r="H83" t="s">
+        <v>46</v>
+      </c>
+      <c r="I83" t="s">
+        <v>50</v>
+      </c>
+      <c r="J83" s="2">
+        <v>45182.46465277778</v>
+      </c>
+      <c r="K83" t="s">
+        <v>55</v>
+      </c>
+      <c r="L83">
+        <v>-0.0003935185185185185</v>
+      </c>
+      <c r="M83">
+        <v>-34</v>
+      </c>
+      <c r="N83">
+        <v>3.047986111111111</v>
+      </c>
+      <c r="O83">
+        <v>263346</v>
+      </c>
+      <c r="P83" s="2">
+        <v>45183.04166666666</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>60</v>
+      </c>
+      <c r="R83" t="b">
+        <v>0</v>
+      </c>
+      <c r="S83">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T83" t="s">
+        <v>64</v>
+      </c>
+      <c r="U83" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:24">
+      <c r="A84" t="s">
+        <v>26</v>
+      </c>
+      <c r="B84">
+        <v>2023</v>
+      </c>
+      <c r="C84" t="s">
+        <v>39</v>
+      </c>
+      <c r="D84">
+        <v>1291</v>
+      </c>
+      <c r="E84" t="b">
+        <v>1</v>
+      </c>
+      <c r="F84" t="s">
+        <v>41</v>
+      </c>
+      <c r="H84" t="s">
+        <v>47</v>
+      </c>
+      <c r="I84" t="s">
+        <v>51</v>
+      </c>
+      <c r="J84" s="2">
+        <v>45180.95467592592</v>
+      </c>
+      <c r="K84" t="s">
+        <v>56</v>
+      </c>
+      <c r="L84">
+        <v>-0.0001157407407407407</v>
+      </c>
+      <c r="M84">
+        <v>-10</v>
+      </c>
+      <c r="N84">
+        <v>1.454675925925926</v>
+      </c>
+      <c r="O84">
+        <v>125684</v>
+      </c>
+      <c r="P84" s="2">
+        <v>45181.33333333334</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>61</v>
+      </c>
+      <c r="R84" t="b">
+        <v>0</v>
+      </c>
+      <c r="S84">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T84" t="s">
+        <v>64</v>
+      </c>
+      <c r="U84" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:24">
+      <c r="A85" t="s">
+        <v>27</v>
+      </c>
+      <c r="B85">
+        <v>2023</v>
+      </c>
+      <c r="C85" t="s">
+        <v>39</v>
+      </c>
+      <c r="D85">
+        <v>423</v>
+      </c>
+      <c r="E85" t="b">
+        <v>1</v>
+      </c>
+      <c r="F85" t="s">
+        <v>41</v>
+      </c>
+      <c r="H85" t="s">
+        <v>46</v>
+      </c>
+      <c r="I85" t="s">
+        <v>52</v>
+      </c>
+      <c r="J85" s="2">
+        <v>45183.8446412037</v>
+      </c>
+      <c r="K85" t="s">
+        <v>56</v>
+      </c>
+      <c r="L85">
+        <v>-0.02489583333333333</v>
+      </c>
+      <c r="M85">
+        <v>-2151</v>
+      </c>
+      <c r="N85">
+        <v>4.427974537037037</v>
+      </c>
+      <c r="O85">
+        <v>382577</v>
+      </c>
+      <c r="P85" s="2">
+        <v>45184.79166666666</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>62</v>
+      </c>
+      <c r="R85" t="b">
+        <v>0</v>
+      </c>
+      <c r="S85">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T85" t="s">
+        <v>64</v>
+      </c>
+      <c r="U85" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:24">
+      <c r="A86" t="s">
+        <v>28</v>
+      </c>
+      <c r="B86">
+        <v>2023</v>
+      </c>
+      <c r="C86" t="s">
+        <v>39</v>
+      </c>
+      <c r="D86">
+        <v>1334</v>
+      </c>
+      <c r="E86" t="b">
+        <v>1</v>
+      </c>
+      <c r="F86" t="s">
+        <v>41</v>
+      </c>
+      <c r="H86" t="s">
+        <v>47</v>
+      </c>
+      <c r="I86" t="s">
+        <v>51</v>
+      </c>
+      <c r="J86" s="2">
+        <v>45180.98311342593</v>
+      </c>
+      <c r="K86" t="s">
+        <v>56</v>
+      </c>
+      <c r="L86">
+        <v>-0.0002083333333333333</v>
+      </c>
+      <c r="M86">
+        <v>-18</v>
+      </c>
+      <c r="N86">
+        <v>1.483113425925926</v>
+      </c>
+      <c r="O86">
+        <v>128141</v>
+      </c>
+      <c r="P86" s="2">
+        <v>45181.33333333334</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>61</v>
+      </c>
+      <c r="R86" t="b">
+        <v>0</v>
+      </c>
+      <c r="S86">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T86" t="s">
+        <v>64</v>
+      </c>
+      <c r="U86" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:24">
+      <c r="A87" t="s">
+        <v>31</v>
+      </c>
+      <c r="B87">
+        <v>2022</v>
+      </c>
+      <c r="C87" t="s">
+        <v>39</v>
+      </c>
+      <c r="D87">
+        <v>275</v>
+      </c>
+      <c r="E87" t="b">
+        <v>1</v>
+      </c>
+      <c r="F87" t="s">
+        <v>41</v>
+      </c>
+      <c r="H87" t="s">
+        <v>46</v>
+      </c>
+      <c r="I87" t="s">
+        <v>50</v>
+      </c>
+      <c r="J87" s="2">
+        <v>44817.39240740741</v>
+      </c>
+      <c r="K87" t="s">
+        <v>57</v>
+      </c>
+      <c r="L87">
+        <v>-0.003252314814814815</v>
+      </c>
+      <c r="M87">
+        <v>-281</v>
+      </c>
+      <c r="N87">
+        <v>1.975740740740741</v>
+      </c>
+      <c r="O87">
+        <v>170704</v>
+      </c>
+      <c r="P87" s="2">
+        <v>44819.04166666666</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>60</v>
+      </c>
+      <c r="R87" t="b">
+        <v>0</v>
+      </c>
+      <c r="S87">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T87" t="s">
+        <v>64</v>
+      </c>
+      <c r="U87" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:24">
+      <c r="A88" t="s">
+        <v>32</v>
+      </c>
+      <c r="B88">
+        <v>2022</v>
+      </c>
+      <c r="C88" t="s">
+        <v>39</v>
+      </c>
+      <c r="D88">
+        <v>127</v>
+      </c>
+      <c r="E88" t="b">
+        <v>1</v>
+      </c>
+      <c r="F88" t="s">
+        <v>41</v>
+      </c>
+      <c r="H88" t="s">
+        <v>46</v>
+      </c>
+      <c r="I88" t="s">
+        <v>53</v>
+      </c>
+      <c r="J88" s="2">
+        <v>44818.26855324074</v>
+      </c>
+      <c r="K88" t="s">
+        <v>58</v>
+      </c>
+      <c r="L88">
+        <v>-0.0005439814814814814</v>
+      </c>
+      <c r="M88">
+        <v>-47</v>
+      </c>
+      <c r="N88">
+        <v>2.851886574074074</v>
+      </c>
+      <c r="O88">
+        <v>246403</v>
+      </c>
+      <c r="P88" s="2">
+        <v>44819.875</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>63</v>
+      </c>
+      <c r="R88" t="b">
+        <v>0</v>
+      </c>
+      <c r="S88">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T88" t="s">
+        <v>64</v>
+      </c>
+      <c r="U88" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:24">
+      <c r="A89" t="s">
+        <v>33</v>
+      </c>
+      <c r="B89">
+        <v>2022</v>
+      </c>
+      <c r="C89" t="s">
+        <v>39</v>
+      </c>
+      <c r="D89">
+        <v>549</v>
+      </c>
+      <c r="E89" t="b">
+        <v>1</v>
+      </c>
+      <c r="F89" t="s">
+        <v>41</v>
+      </c>
+      <c r="H89" t="s">
+        <v>46</v>
+      </c>
+      <c r="I89" t="s">
+        <v>52</v>
+      </c>
+      <c r="J89" s="2">
+        <v>44820.2553125</v>
+      </c>
+      <c r="K89" t="s">
+        <v>55</v>
+      </c>
+      <c r="L89">
+        <v>-0.0003587962962962963</v>
+      </c>
+      <c r="M89">
+        <v>-31</v>
+      </c>
+      <c r="N89">
+        <v>4.838645833333334</v>
+      </c>
+      <c r="O89">
+        <v>418059</v>
+      </c>
+      <c r="P89" s="2">
+        <v>44820.79166666666</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>62</v>
+      </c>
+      <c r="R89" t="b">
+        <v>0</v>
+      </c>
+      <c r="S89">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T89" t="s">
+        <v>64</v>
+      </c>
+      <c r="U89" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:24">
+      <c r="A90" t="s">
+        <v>34</v>
+      </c>
+      <c r="B90">
+        <v>2022</v>
+      </c>
+      <c r="C90" t="s">
+        <v>39</v>
+      </c>
+      <c r="D90">
+        <v>1005</v>
+      </c>
+      <c r="E90" t="b">
+        <v>0</v>
+      </c>
+      <c r="F90" t="s">
+        <v>43</v>
+      </c>
+      <c r="H90" t="s">
+        <v>47</v>
+      </c>
+      <c r="I90" t="s">
+        <v>53</v>
+      </c>
+      <c r="J90" s="2">
+        <v>44819.50680555555</v>
+      </c>
+      <c r="L90">
+        <v>-0.0002777777777777778</v>
+      </c>
+      <c r="M90">
+        <v>-24</v>
+      </c>
+      <c r="N90">
+        <v>4.006805555555555</v>
+      </c>
+      <c r="O90">
+        <v>346188</v>
+      </c>
+      <c r="P90" s="2">
+        <v>44819.95833333334</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>63</v>
+      </c>
+      <c r="R90" t="b">
+        <v>0</v>
+      </c>
+      <c r="S90">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T90" t="s">
+        <v>64</v>
+      </c>
+      <c r="U90" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:24">
+      <c r="A91" t="s">
+        <v>35</v>
+      </c>
+      <c r="B91">
+        <v>2022</v>
+      </c>
+      <c r="C91" t="s">
+        <v>39</v>
+      </c>
+      <c r="D91">
+        <v>1205</v>
+      </c>
+      <c r="E91" t="b">
+        <v>0</v>
+      </c>
+      <c r="F91" t="s">
+        <v>44</v>
+      </c>
+      <c r="H91" t="s">
+        <v>47</v>
+      </c>
+      <c r="I91" t="s">
+        <v>50</v>
+      </c>
+      <c r="J91" s="2">
+        <v>44818.92413194444</v>
+      </c>
+      <c r="L91">
+        <v>-0.0002199074074074074</v>
+      </c>
+      <c r="M91">
+        <v>-19</v>
+      </c>
+      <c r="N91">
+        <v>3.424131944444444</v>
+      </c>
+      <c r="O91">
+        <v>295845</v>
+      </c>
+      <c r="P91" s="2">
+        <v>44819.125</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>60</v>
+      </c>
+      <c r="R91" t="b">
+        <v>0</v>
+      </c>
+      <c r="S91">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T91" t="s">
+        <v>64</v>
+      </c>
+      <c r="U91" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:24">
+      <c r="A92" t="s">
+        <v>36</v>
+      </c>
+      <c r="B92">
+        <v>2022</v>
+      </c>
+      <c r="C92" t="s">
+        <v>39</v>
+      </c>
+      <c r="D92">
+        <v>1268</v>
+      </c>
+      <c r="E92" t="b">
+        <v>0</v>
+      </c>
+      <c r="F92" t="s">
+        <v>44</v>
+      </c>
+      <c r="H92" t="s">
+        <v>47</v>
+      </c>
+      <c r="I92" t="s">
+        <v>50</v>
+      </c>
+      <c r="J92" s="2">
+        <v>44818.92489583333</v>
+      </c>
+      <c r="L92">
+        <v>-0.0008333333333333334</v>
+      </c>
+      <c r="M92">
+        <v>-72</v>
+      </c>
+      <c r="N92">
+        <v>3.424895833333333</v>
+      </c>
+      <c r="O92">
+        <v>295911</v>
+      </c>
+      <c r="P92" s="2">
+        <v>44819.125</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>60</v>
+      </c>
+      <c r="R92" t="b">
+        <v>0</v>
+      </c>
+      <c r="S92">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T92" t="s">
+        <v>64</v>
+      </c>
+      <c r="U92" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:24">
+      <c r="A93" t="s">
+        <v>37</v>
+      </c>
+      <c r="B93">
+        <v>2021</v>
+      </c>
+      <c r="C93" t="s">
+        <v>39</v>
+      </c>
+      <c r="D93">
+        <v>162</v>
+      </c>
+      <c r="E93" t="b">
+        <v>1</v>
+      </c>
+      <c r="F93" t="s">
+        <v>41</v>
+      </c>
+      <c r="H93" t="s">
+        <v>48</v>
+      </c>
+      <c r="I93" t="s">
+        <v>52</v>
+      </c>
+      <c r="J93" s="2">
+        <v>44456.22016203704</v>
+      </c>
+      <c r="K93" t="s">
+        <v>55</v>
+      </c>
+      <c r="L93">
+        <v>-0.001018518518518518</v>
+      </c>
+      <c r="M93">
+        <v>-88</v>
+      </c>
+      <c r="N93">
+        <v>4.803495370370371</v>
+      </c>
+      <c r="O93">
+        <v>415022</v>
+      </c>
+      <c r="P93" s="2">
+        <v>44456.79166666666</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>62</v>
+      </c>
+      <c r="R93" t="b">
+        <v>0</v>
+      </c>
+      <c r="S93">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T93" t="s">
+        <v>64</v>
+      </c>
+      <c r="U93" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:24">
+      <c r="A94" t="s">
+        <v>37</v>
+      </c>
+      <c r="B94">
+        <v>2021</v>
+      </c>
+      <c r="C94" t="s">
+        <v>39</v>
+      </c>
+      <c r="D94">
+        <v>162</v>
+      </c>
+      <c r="E94" t="b">
+        <v>1</v>
+      </c>
+      <c r="F94" t="s">
+        <v>41</v>
+      </c>
+      <c r="H94" t="s">
+        <v>48</v>
+      </c>
+      <c r="I94" t="s">
+        <v>52</v>
+      </c>
+      <c r="J94" s="2">
+        <v>44456.22016203704</v>
+      </c>
+      <c r="K94" t="s">
+        <v>55</v>
+      </c>
+      <c r="L94">
+        <v>-0.001018518518518518</v>
+      </c>
+      <c r="M94">
+        <v>-88</v>
+      </c>
+      <c r="N94">
+        <v>4.803495370370371</v>
+      </c>
+      <c r="O94">
+        <v>415022</v>
+      </c>
+      <c r="P94" s="2">
+        <v>44456.79166666666</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>62</v>
+      </c>
+      <c r="R94" t="b">
+        <v>0</v>
+      </c>
+      <c r="S94">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T94" t="s">
+        <v>64</v>
+      </c>
+      <c r="U94" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:24">
+      <c r="A95" t="s">
+        <v>31</v>
+      </c>
+      <c r="B95">
+        <v>2022</v>
+      </c>
+      <c r="C95" t="s">
+        <v>39</v>
+      </c>
+      <c r="D95">
+        <v>275</v>
+      </c>
+      <c r="E95" t="b">
+        <v>1</v>
+      </c>
+      <c r="F95" t="s">
+        <v>41</v>
+      </c>
+      <c r="H95" t="s">
+        <v>46</v>
+      </c>
+      <c r="I95" t="s">
+        <v>50</v>
+      </c>
+      <c r="J95" s="2">
+        <v>44817.39240740741</v>
+      </c>
+      <c r="K95" t="s">
+        <v>57</v>
+      </c>
+      <c r="L95">
+        <v>-0.003252314814814815</v>
+      </c>
+      <c r="M95">
+        <v>-281</v>
+      </c>
+      <c r="N95">
+        <v>1.975740740740741</v>
+      </c>
+      <c r="O95">
+        <v>170704</v>
+      </c>
+      <c r="P95" s="2">
+        <v>44819.04166666666</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>60</v>
+      </c>
+      <c r="R95" t="b">
+        <v>0</v>
+      </c>
+      <c r="S95">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T95" t="s">
+        <v>64</v>
+      </c>
+      <c r="U95" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:24">
+      <c r="A96" t="s">
+        <v>32</v>
+      </c>
+      <c r="B96">
+        <v>2022</v>
+      </c>
+      <c r="C96" t="s">
+        <v>39</v>
+      </c>
+      <c r="D96">
+        <v>127</v>
+      </c>
+      <c r="E96" t="b">
+        <v>1</v>
+      </c>
+      <c r="F96" t="s">
+        <v>41</v>
+      </c>
+      <c r="H96" t="s">
+        <v>46</v>
+      </c>
+      <c r="I96" t="s">
+        <v>53</v>
+      </c>
+      <c r="J96" s="2">
+        <v>44818.26855324074</v>
+      </c>
+      <c r="K96" t="s">
+        <v>58</v>
+      </c>
+      <c r="L96">
+        <v>-0.0005439814814814814</v>
+      </c>
+      <c r="M96">
+        <v>-47</v>
+      </c>
+      <c r="N96">
+        <v>2.851886574074074</v>
+      </c>
+      <c r="O96">
+        <v>246403</v>
+      </c>
+      <c r="P96" s="2">
+        <v>44819.875</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>63</v>
+      </c>
+      <c r="R96" t="b">
+        <v>0</v>
+      </c>
+      <c r="S96">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T96" t="s">
+        <v>64</v>
+      </c>
+      <c r="U96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:24">
+      <c r="A97" t="s">
+        <v>33</v>
+      </c>
+      <c r="B97">
+        <v>2022</v>
+      </c>
+      <c r="C97" t="s">
+        <v>39</v>
+      </c>
+      <c r="D97">
+        <v>549</v>
+      </c>
+      <c r="E97" t="b">
+        <v>1</v>
+      </c>
+      <c r="F97" t="s">
+        <v>41</v>
+      </c>
+      <c r="H97" t="s">
+        <v>46</v>
+      </c>
+      <c r="I97" t="s">
+        <v>52</v>
+      </c>
+      <c r="J97" s="2">
+        <v>44820.2553125</v>
+      </c>
+      <c r="K97" t="s">
+        <v>55</v>
+      </c>
+      <c r="L97">
+        <v>-0.0003587962962962963</v>
+      </c>
+      <c r="M97">
+        <v>-31</v>
+      </c>
+      <c r="N97">
+        <v>4.838645833333334</v>
+      </c>
+      <c r="O97">
+        <v>418059</v>
+      </c>
+      <c r="P97" s="2">
+        <v>44820.79166666666</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>62</v>
+      </c>
+      <c r="R97" t="b">
+        <v>0</v>
+      </c>
+      <c r="S97">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T97" t="s">
+        <v>64</v>
+      </c>
+      <c r="U97" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:24">
+      <c r="A98" t="s">
+        <v>34</v>
+      </c>
+      <c r="B98">
+        <v>2022</v>
+      </c>
+      <c r="C98" t="s">
+        <v>39</v>
+      </c>
+      <c r="D98">
+        <v>1005</v>
+      </c>
+      <c r="E98" t="b">
+        <v>0</v>
+      </c>
+      <c r="F98" t="s">
+        <v>43</v>
+      </c>
+      <c r="H98" t="s">
+        <v>47</v>
+      </c>
+      <c r="I98" t="s">
+        <v>53</v>
+      </c>
+      <c r="J98" s="2">
+        <v>44819.50680555555</v>
+      </c>
+      <c r="L98">
+        <v>-0.0002777777777777778</v>
+      </c>
+      <c r="M98">
+        <v>-24</v>
+      </c>
+      <c r="N98">
+        <v>4.006805555555555</v>
+      </c>
+      <c r="O98">
+        <v>346188</v>
+      </c>
+      <c r="P98" s="2">
+        <v>44819.95833333334</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>63</v>
+      </c>
+      <c r="R98" t="b">
+        <v>0</v>
+      </c>
+      <c r="S98">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T98" t="s">
+        <v>64</v>
+      </c>
+      <c r="U98" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:24">
+      <c r="A99" t="s">
+        <v>35</v>
+      </c>
+      <c r="B99">
+        <v>2022</v>
+      </c>
+      <c r="C99" t="s">
+        <v>39</v>
+      </c>
+      <c r="D99">
+        <v>1205</v>
+      </c>
+      <c r="E99" t="b">
+        <v>0</v>
+      </c>
+      <c r="F99" t="s">
+        <v>44</v>
+      </c>
+      <c r="H99" t="s">
+        <v>47</v>
+      </c>
+      <c r="I99" t="s">
+        <v>50</v>
+      </c>
+      <c r="J99" s="2">
+        <v>44818.92413194444</v>
+      </c>
+      <c r="L99">
+        <v>-0.0002199074074074074</v>
+      </c>
+      <c r="M99">
+        <v>-19</v>
+      </c>
+      <c r="N99">
+        <v>3.424131944444444</v>
+      </c>
+      <c r="O99">
+        <v>295845</v>
+      </c>
+      <c r="P99" s="2">
+        <v>44819.125</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>60</v>
+      </c>
+      <c r="R99" t="b">
+        <v>0</v>
+      </c>
+      <c r="S99">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T99" t="s">
+        <v>64</v>
+      </c>
+      <c r="U99" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:24">
+      <c r="A100" t="s">
+        <v>36</v>
+      </c>
+      <c r="B100">
+        <v>2022</v>
+      </c>
+      <c r="C100" t="s">
+        <v>39</v>
+      </c>
+      <c r="D100">
+        <v>1268</v>
+      </c>
+      <c r="E100" t="b">
+        <v>0</v>
+      </c>
+      <c r="F100" t="s">
+        <v>44</v>
+      </c>
+      <c r="H100" t="s">
+        <v>47</v>
+      </c>
+      <c r="I100" t="s">
+        <v>50</v>
+      </c>
+      <c r="J100" s="2">
+        <v>44818.92489583333</v>
+      </c>
+      <c r="L100">
+        <v>-0.0008333333333333334</v>
+      </c>
+      <c r="M100">
+        <v>-72</v>
+      </c>
+      <c r="N100">
+        <v>3.424895833333333</v>
+      </c>
+      <c r="O100">
+        <v>295911</v>
+      </c>
+      <c r="P100" s="2">
+        <v>44819.125</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>60</v>
+      </c>
+      <c r="R100" t="b">
+        <v>0</v>
+      </c>
+      <c r="S100">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T100" t="s">
+        <v>64</v>
+      </c>
+      <c r="U100" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:24">
+      <c r="A101" t="s">
+        <v>24</v>
+      </c>
+      <c r="B101">
+        <v>2023</v>
+      </c>
+      <c r="C101" t="s">
+        <v>39</v>
+      </c>
+      <c r="D101">
+        <v>334</v>
+      </c>
+      <c r="E101" t="b">
+        <v>1</v>
+      </c>
+      <c r="F101" t="s">
+        <v>41</v>
+      </c>
+      <c r="H101" t="s">
+        <v>46</v>
+      </c>
+      <c r="I101" t="s">
+        <v>49</v>
+      </c>
+      <c r="J101" s="2">
+        <v>45180.90565972222</v>
+      </c>
+      <c r="K101" t="s">
+        <v>54</v>
+      </c>
+      <c r="L101">
+        <v>-0.05702546296296297</v>
+      </c>
+      <c r="M101">
+        <v>-4927</v>
+      </c>
+      <c r="N101">
+        <v>1.488993055555556</v>
+      </c>
+      <c r="O101">
+        <v>128649</v>
+      </c>
+      <c r="P101" s="2">
+        <v>45182</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>59</v>
+      </c>
+      <c r="R101" t="b">
+        <v>0</v>
+      </c>
+      <c r="S101">
+        <v>0.75</v>
+      </c>
+      <c r="T101" t="s">
+        <v>64</v>
+      </c>
+      <c r="U101" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:24">
+      <c r="A102" t="s">
+        <v>25</v>
+      </c>
+      <c r="B102">
+        <v>2023</v>
+      </c>
+      <c r="C102" t="s">
+        <v>39</v>
+      </c>
+      <c r="D102">
+        <v>343</v>
+      </c>
+      <c r="E102" t="b">
+        <v>1</v>
+      </c>
+      <c r="F102" t="s">
+        <v>41</v>
+      </c>
+      <c r="H102" t="s">
+        <v>46</v>
+      </c>
+      <c r="I102" t="s">
+        <v>50</v>
+      </c>
+      <c r="J102" s="2">
+        <v>45182.46465277778</v>
+      </c>
+      <c r="K102" t="s">
+        <v>55</v>
+      </c>
+      <c r="L102">
+        <v>-0.0003935185185185185</v>
+      </c>
+      <c r="M102">
+        <v>-34</v>
+      </c>
+      <c r="N102">
+        <v>3.047986111111111</v>
+      </c>
+      <c r="O102">
+        <v>263346</v>
+      </c>
+      <c r="P102" s="2">
+        <v>45183.04166666666</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>60</v>
+      </c>
+      <c r="R102" t="b">
+        <v>0</v>
+      </c>
+      <c r="S102">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T102" t="s">
+        <v>64</v>
+      </c>
+      <c r="U102" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:24">
+      <c r="A103" t="s">
+        <v>26</v>
+      </c>
+      <c r="B103">
+        <v>2023</v>
+      </c>
+      <c r="C103" t="s">
+        <v>39</v>
+      </c>
+      <c r="D103">
+        <v>1291</v>
+      </c>
+      <c r="E103" t="b">
+        <v>1</v>
+      </c>
+      <c r="F103" t="s">
+        <v>41</v>
+      </c>
+      <c r="H103" t="s">
+        <v>47</v>
+      </c>
+      <c r="I103" t="s">
+        <v>51</v>
+      </c>
+      <c r="J103" s="2">
+        <v>45180.95467592592</v>
+      </c>
+      <c r="K103" t="s">
+        <v>56</v>
+      </c>
+      <c r="L103">
+        <v>-0.0001157407407407407</v>
+      </c>
+      <c r="M103">
+        <v>-10</v>
+      </c>
+      <c r="N103">
+        <v>1.454675925925926</v>
+      </c>
+      <c r="O103">
+        <v>125684</v>
+      </c>
+      <c r="P103" s="2">
+        <v>45181.33333333334</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>61</v>
+      </c>
+      <c r="R103" t="b">
+        <v>0</v>
+      </c>
+      <c r="S103">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T103" t="s">
+        <v>64</v>
+      </c>
+      <c r="U103" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:24">
+      <c r="A104" t="s">
+        <v>27</v>
+      </c>
+      <c r="B104">
+        <v>2023</v>
+      </c>
+      <c r="C104" t="s">
+        <v>39</v>
+      </c>
+      <c r="D104">
+        <v>423</v>
+      </c>
+      <c r="E104" t="b">
+        <v>1</v>
+      </c>
+      <c r="F104" t="s">
+        <v>41</v>
+      </c>
+      <c r="H104" t="s">
+        <v>46</v>
+      </c>
+      <c r="I104" t="s">
+        <v>52</v>
+      </c>
+      <c r="J104" s="2">
+        <v>45183.8446412037</v>
+      </c>
+      <c r="K104" t="s">
+        <v>56</v>
+      </c>
+      <c r="L104">
+        <v>-0.02489583333333333</v>
+      </c>
+      <c r="M104">
+        <v>-2151</v>
+      </c>
+      <c r="N104">
+        <v>4.427974537037037</v>
+      </c>
+      <c r="O104">
+        <v>382577</v>
+      </c>
+      <c r="P104" s="2">
+        <v>45184.79166666666</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>62</v>
+      </c>
+      <c r="R104" t="b">
+        <v>0</v>
+      </c>
+      <c r="S104">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T104" t="s">
+        <v>64</v>
+      </c>
+      <c r="U104" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:24">
+      <c r="A105" t="s">
+        <v>28</v>
+      </c>
+      <c r="B105">
+        <v>2023</v>
+      </c>
+      <c r="C105" t="s">
+        <v>39</v>
+      </c>
+      <c r="D105">
+        <v>1334</v>
+      </c>
+      <c r="E105" t="b">
+        <v>1</v>
+      </c>
+      <c r="F105" t="s">
+        <v>41</v>
+      </c>
+      <c r="H105" t="s">
+        <v>47</v>
+      </c>
+      <c r="I105" t="s">
+        <v>51</v>
+      </c>
+      <c r="J105" s="2">
+        <v>45180.98311342593</v>
+      </c>
+      <c r="K105" t="s">
+        <v>56</v>
+      </c>
+      <c r="L105">
+        <v>-0.0002083333333333333</v>
+      </c>
+      <c r="M105">
+        <v>-18</v>
+      </c>
+      <c r="N105">
+        <v>1.483113425925926</v>
+      </c>
+      <c r="O105">
+        <v>128141</v>
+      </c>
+      <c r="P105" s="2">
+        <v>45181.33333333334</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>61</v>
+      </c>
+      <c r="R105" t="b">
+        <v>0</v>
+      </c>
+      <c r="S105">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T105" t="s">
+        <v>64</v>
+      </c>
+      <c r="U105" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:24">
+      <c r="A106" t="s">
+        <v>29</v>
+      </c>
+      <c r="B106">
+        <v>2024</v>
+      </c>
+      <c r="C106" t="s">
+        <v>39</v>
+      </c>
+      <c r="D106">
+        <v>404</v>
+      </c>
+      <c r="E106" t="b">
+        <v>1</v>
+      </c>
+      <c r="F106" t="s">
+        <v>41</v>
+      </c>
+      <c r="H106" t="s">
+        <v>46</v>
+      </c>
+      <c r="I106" t="s">
+        <v>53</v>
+      </c>
+      <c r="J106" s="2">
+        <v>45546.77756944444</v>
+      </c>
+      <c r="K106" t="s">
+        <v>54</v>
+      </c>
+      <c r="L106">
+        <v>-0.007534722222222222</v>
+      </c>
+      <c r="M106">
+        <v>-651</v>
+      </c>
+      <c r="N106">
+        <v>3.360902777777778</v>
+      </c>
+      <c r="O106">
+        <v>290382</v>
+      </c>
+      <c r="P106" s="2">
+        <v>45547.875</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>63</v>
+      </c>
+      <c r="R106" t="b">
+        <v>0</v>
+      </c>
+      <c r="S106">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T106" t="s">
+        <v>64</v>
+      </c>
+      <c r="U106" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:24">
+      <c r="A107" t="s">
+        <v>30</v>
+      </c>
+      <c r="B107">
+        <v>2024</v>
+      </c>
+      <c r="C107" t="s">
+        <v>39</v>
+      </c>
+      <c r="D107">
+        <v>1367</v>
+      </c>
+      <c r="E107" t="b">
+        <v>0</v>
+      </c>
+      <c r="F107" t="s">
+        <v>42</v>
+      </c>
+      <c r="G107" t="s">
+        <v>45</v>
+      </c>
+      <c r="H107" t="s">
+        <v>47</v>
+      </c>
+      <c r="I107" t="s">
+        <v>51</v>
+      </c>
+      <c r="J107" s="2">
+        <v>45545.14299768519</v>
+      </c>
+      <c r="K107" t="s">
+        <v>42</v>
+      </c>
+      <c r="L107">
+        <v>-0.0003587962962962963</v>
+      </c>
+      <c r="M107">
+        <v>-31</v>
+      </c>
+      <c r="N107">
+        <v>1.642997685185185</v>
+      </c>
+      <c r="O107">
+        <v>141955</v>
+      </c>
+      <c r="P107" s="2">
+        <v>45545.33333333334</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>61</v>
+      </c>
+      <c r="R107" t="b">
+        <v>0</v>
+      </c>
+      <c r="S107">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T107" t="s">
+        <v>64</v>
+      </c>
+      <c r="U107" t="b">
+        <v>0</v>
+      </c>
+      <c r="X107" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="108" spans="1:24">
+      <c r="A108" t="s">
+        <v>24</v>
+      </c>
+      <c r="B108">
+        <v>2023</v>
+      </c>
+      <c r="C108" t="s">
+        <v>39</v>
+      </c>
+      <c r="D108">
+        <v>334</v>
+      </c>
+      <c r="E108" t="b">
+        <v>1</v>
+      </c>
+      <c r="F108" t="s">
+        <v>41</v>
+      </c>
+      <c r="H108" t="s">
+        <v>46</v>
+      </c>
+      <c r="I108" t="s">
+        <v>49</v>
+      </c>
+      <c r="J108" s="2">
+        <v>45180.90565972222</v>
+      </c>
+      <c r="K108" t="s">
+        <v>54</v>
+      </c>
+      <c r="L108">
+        <v>-0.05702546296296297</v>
+      </c>
+      <c r="M108">
+        <v>-4927</v>
+      </c>
+      <c r="N108">
+        <v>1.488993055555556</v>
+      </c>
+      <c r="O108">
+        <v>128649</v>
+      </c>
+      <c r="P108" s="2">
+        <v>45182</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>59</v>
+      </c>
+      <c r="R108" t="b">
+        <v>0</v>
+      </c>
+      <c r="S108">
+        <v>0.75</v>
+      </c>
+      <c r="T108" t="s">
+        <v>64</v>
+      </c>
+      <c r="U108" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:24">
+      <c r="A109" t="s">
+        <v>25</v>
+      </c>
+      <c r="B109">
+        <v>2023</v>
+      </c>
+      <c r="C109" t="s">
+        <v>39</v>
+      </c>
+      <c r="D109">
+        <v>343</v>
+      </c>
+      <c r="E109" t="b">
+        <v>1</v>
+      </c>
+      <c r="F109" t="s">
+        <v>41</v>
+      </c>
+      <c r="H109" t="s">
+        <v>46</v>
+      </c>
+      <c r="I109" t="s">
+        <v>50</v>
+      </c>
+      <c r="J109" s="2">
+        <v>45182.46465277778</v>
+      </c>
+      <c r="K109" t="s">
+        <v>55</v>
+      </c>
+      <c r="L109">
+        <v>-0.0003935185185185185</v>
+      </c>
+      <c r="M109">
+        <v>-34</v>
+      </c>
+      <c r="N109">
+        <v>3.047986111111111</v>
+      </c>
+      <c r="O109">
+        <v>263346</v>
+      </c>
+      <c r="P109" s="2">
+        <v>45183.04166666666</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>60</v>
+      </c>
+      <c r="R109" t="b">
+        <v>0</v>
+      </c>
+      <c r="S109">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T109" t="s">
+        <v>64</v>
+      </c>
+      <c r="U109" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:24">
+      <c r="A110" t="s">
+        <v>26</v>
+      </c>
+      <c r="B110">
+        <v>2023</v>
+      </c>
+      <c r="C110" t="s">
+        <v>39</v>
+      </c>
+      <c r="D110">
+        <v>1291</v>
+      </c>
+      <c r="E110" t="b">
+        <v>1</v>
+      </c>
+      <c r="F110" t="s">
+        <v>41</v>
+      </c>
+      <c r="H110" t="s">
+        <v>47</v>
+      </c>
+      <c r="I110" t="s">
+        <v>51</v>
+      </c>
+      <c r="J110" s="2">
+        <v>45180.95467592592</v>
+      </c>
+      <c r="K110" t="s">
+        <v>56</v>
+      </c>
+      <c r="L110">
+        <v>-0.0001157407407407407</v>
+      </c>
+      <c r="M110">
+        <v>-10</v>
+      </c>
+      <c r="N110">
+        <v>1.454675925925926</v>
+      </c>
+      <c r="O110">
+        <v>125684</v>
+      </c>
+      <c r="P110" s="2">
+        <v>45181.33333333334</v>
+      </c>
+      <c r="Q110" t="s">
+        <v>61</v>
+      </c>
+      <c r="R110" t="b">
+        <v>0</v>
+      </c>
+      <c r="S110">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T110" t="s">
+        <v>64</v>
+      </c>
+      <c r="U110" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:24">
+      <c r="A111" t="s">
+        <v>27</v>
+      </c>
+      <c r="B111">
+        <v>2023</v>
+      </c>
+      <c r="C111" t="s">
+        <v>39</v>
+      </c>
+      <c r="D111">
+        <v>423</v>
+      </c>
+      <c r="E111" t="b">
+        <v>1</v>
+      </c>
+      <c r="F111" t="s">
+        <v>41</v>
+      </c>
+      <c r="H111" t="s">
+        <v>46</v>
+      </c>
+      <c r="I111" t="s">
+        <v>52</v>
+      </c>
+      <c r="J111" s="2">
+        <v>45183.8446412037</v>
+      </c>
+      <c r="K111" t="s">
+        <v>56</v>
+      </c>
+      <c r="L111">
+        <v>-0.02489583333333333</v>
+      </c>
+      <c r="M111">
+        <v>-2151</v>
+      </c>
+      <c r="N111">
+        <v>4.427974537037037</v>
+      </c>
+      <c r="O111">
+        <v>382577</v>
+      </c>
+      <c r="P111" s="2">
+        <v>45184.79166666666</v>
+      </c>
+      <c r="Q111" t="s">
+        <v>62</v>
+      </c>
+      <c r="R111" t="b">
+        <v>0</v>
+      </c>
+      <c r="S111">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T111" t="s">
+        <v>64</v>
+      </c>
+      <c r="U111" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:24">
+      <c r="A112" t="s">
+        <v>28</v>
+      </c>
+      <c r="B112">
+        <v>2023</v>
+      </c>
+      <c r="C112" t="s">
+        <v>39</v>
+      </c>
+      <c r="D112">
+        <v>1334</v>
+      </c>
+      <c r="E112" t="b">
+        <v>1</v>
+      </c>
+      <c r="F112" t="s">
+        <v>41</v>
+      </c>
+      <c r="H112" t="s">
+        <v>47</v>
+      </c>
+      <c r="I112" t="s">
+        <v>51</v>
+      </c>
+      <c r="J112" s="2">
+        <v>45180.98311342593</v>
+      </c>
+      <c r="K112" t="s">
+        <v>56</v>
+      </c>
+      <c r="L112">
+        <v>-0.0002083333333333333</v>
+      </c>
+      <c r="M112">
+        <v>-18</v>
+      </c>
+      <c r="N112">
+        <v>1.483113425925926</v>
+      </c>
+      <c r="O112">
+        <v>128141</v>
+      </c>
+      <c r="P112" s="2">
+        <v>45181.33333333334</v>
+      </c>
+      <c r="Q112" t="s">
+        <v>61</v>
+      </c>
+      <c r="R112" t="b">
+        <v>0</v>
+      </c>
+      <c r="S112">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T112" t="s">
+        <v>64</v>
+      </c>
+      <c r="U112" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:21">
+      <c r="A113" t="s">
+        <v>31</v>
+      </c>
+      <c r="B113">
+        <v>2022</v>
+      </c>
+      <c r="C113" t="s">
+        <v>39</v>
+      </c>
+      <c r="D113">
+        <v>275</v>
+      </c>
+      <c r="E113" t="b">
+        <v>1</v>
+      </c>
+      <c r="F113" t="s">
+        <v>41</v>
+      </c>
+      <c r="H113" t="s">
+        <v>46</v>
+      </c>
+      <c r="I113" t="s">
+        <v>50</v>
+      </c>
+      <c r="J113" s="2">
+        <v>44817.39240740741</v>
+      </c>
+      <c r="K113" t="s">
+        <v>57</v>
+      </c>
+      <c r="L113">
+        <v>-0.003252314814814815</v>
+      </c>
+      <c r="M113">
+        <v>-281</v>
+      </c>
+      <c r="N113">
+        <v>1.975740740740741</v>
+      </c>
+      <c r="O113">
+        <v>170704</v>
+      </c>
+      <c r="P113" s="2">
+        <v>44819.04166666666</v>
+      </c>
+      <c r="Q113" t="s">
+        <v>60</v>
+      </c>
+      <c r="R113" t="b">
+        <v>0</v>
+      </c>
+      <c r="S113">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T113" t="s">
+        <v>64</v>
+      </c>
+      <c r="U113" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:21">
+      <c r="A114" t="s">
+        <v>32</v>
+      </c>
+      <c r="B114">
+        <v>2022</v>
+      </c>
+      <c r="C114" t="s">
+        <v>39</v>
+      </c>
+      <c r="D114">
+        <v>127</v>
+      </c>
+      <c r="E114" t="b">
+        <v>1</v>
+      </c>
+      <c r="F114" t="s">
+        <v>41</v>
+      </c>
+      <c r="H114" t="s">
+        <v>46</v>
+      </c>
+      <c r="I114" t="s">
+        <v>53</v>
+      </c>
+      <c r="J114" s="2">
+        <v>44818.26855324074</v>
+      </c>
+      <c r="K114" t="s">
+        <v>58</v>
+      </c>
+      <c r="L114">
+        <v>-0.0005439814814814814</v>
+      </c>
+      <c r="M114">
+        <v>-47</v>
+      </c>
+      <c r="N114">
+        <v>2.851886574074074</v>
+      </c>
+      <c r="O114">
+        <v>246403</v>
+      </c>
+      <c r="P114" s="2">
+        <v>44819.875</v>
+      </c>
+      <c r="Q114" t="s">
+        <v>63</v>
+      </c>
+      <c r="R114" t="b">
+        <v>0</v>
+      </c>
+      <c r="S114">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T114" t="s">
+        <v>64</v>
+      </c>
+      <c r="U114" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:21">
+      <c r="A115" t="s">
+        <v>33</v>
+      </c>
+      <c r="B115">
+        <v>2022</v>
+      </c>
+      <c r="C115" t="s">
+        <v>39</v>
+      </c>
+      <c r="D115">
+        <v>549</v>
+      </c>
+      <c r="E115" t="b">
+        <v>1</v>
+      </c>
+      <c r="F115" t="s">
+        <v>41</v>
+      </c>
+      <c r="H115" t="s">
+        <v>46</v>
+      </c>
+      <c r="I115" t="s">
+        <v>52</v>
+      </c>
+      <c r="J115" s="2">
+        <v>44820.2553125</v>
+      </c>
+      <c r="K115" t="s">
+        <v>55</v>
+      </c>
+      <c r="L115">
+        <v>-0.0003587962962962963</v>
+      </c>
+      <c r="M115">
+        <v>-31</v>
+      </c>
+      <c r="N115">
+        <v>4.838645833333334</v>
+      </c>
+      <c r="O115">
+        <v>418059</v>
+      </c>
+      <c r="P115" s="2">
+        <v>44820.79166666666</v>
+      </c>
+      <c r="Q115" t="s">
+        <v>62</v>
+      </c>
+      <c r="R115" t="b">
+        <v>0</v>
+      </c>
+      <c r="S115">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T115" t="s">
+        <v>64</v>
+      </c>
+      <c r="U115" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:21">
+      <c r="A116" t="s">
+        <v>34</v>
+      </c>
+      <c r="B116">
+        <v>2022</v>
+      </c>
+      <c r="C116" t="s">
+        <v>39</v>
+      </c>
+      <c r="D116">
+        <v>1005</v>
+      </c>
+      <c r="E116" t="b">
+        <v>0</v>
+      </c>
+      <c r="F116" t="s">
+        <v>43</v>
+      </c>
+      <c r="H116" t="s">
+        <v>47</v>
+      </c>
+      <c r="I116" t="s">
+        <v>53</v>
+      </c>
+      <c r="J116" s="2">
+        <v>44819.50680555555</v>
+      </c>
+      <c r="L116">
+        <v>-0.0002777777777777778</v>
+      </c>
+      <c r="M116">
+        <v>-24</v>
+      </c>
+      <c r="N116">
+        <v>4.006805555555555</v>
+      </c>
+      <c r="O116">
+        <v>346188</v>
+      </c>
+      <c r="P116" s="2">
+        <v>44819.95833333334</v>
+      </c>
+      <c r="Q116" t="s">
+        <v>63</v>
+      </c>
+      <c r="R116" t="b">
+        <v>0</v>
+      </c>
+      <c r="S116">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T116" t="s">
+        <v>64</v>
+      </c>
+      <c r="U116" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:21">
+      <c r="A117" t="s">
+        <v>35</v>
+      </c>
+      <c r="B117">
+        <v>2022</v>
+      </c>
+      <c r="C117" t="s">
+        <v>39</v>
+      </c>
+      <c r="D117">
+        <v>1205</v>
+      </c>
+      <c r="E117" t="b">
+        <v>0</v>
+      </c>
+      <c r="F117" t="s">
+        <v>44</v>
+      </c>
+      <c r="H117" t="s">
+        <v>47</v>
+      </c>
+      <c r="I117" t="s">
+        <v>50</v>
+      </c>
+      <c r="J117" s="2">
+        <v>44818.92413194444</v>
+      </c>
+      <c r="L117">
+        <v>-0.0002199074074074074</v>
+      </c>
+      <c r="M117">
+        <v>-19</v>
+      </c>
+      <c r="N117">
+        <v>3.424131944444444</v>
+      </c>
+      <c r="O117">
+        <v>295845</v>
+      </c>
+      <c r="P117" s="2">
+        <v>44819.125</v>
+      </c>
+      <c r="Q117" t="s">
+        <v>60</v>
+      </c>
+      <c r="R117" t="b">
+        <v>0</v>
+      </c>
+      <c r="S117">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T117" t="s">
+        <v>64</v>
+      </c>
+      <c r="U117" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:21">
+      <c r="A118" t="s">
+        <v>36</v>
+      </c>
+      <c r="B118">
+        <v>2022</v>
+      </c>
+      <c r="C118" t="s">
+        <v>39</v>
+      </c>
+      <c r="D118">
+        <v>1268</v>
+      </c>
+      <c r="E118" t="b">
+        <v>0</v>
+      </c>
+      <c r="F118" t="s">
+        <v>44</v>
+      </c>
+      <c r="H118" t="s">
+        <v>47</v>
+      </c>
+      <c r="I118" t="s">
+        <v>50</v>
+      </c>
+      <c r="J118" s="2">
+        <v>44818.92489583333</v>
+      </c>
+      <c r="L118">
+        <v>-0.0008333333333333334</v>
+      </c>
+      <c r="M118">
+        <v>-72</v>
+      </c>
+      <c r="N118">
+        <v>3.424895833333333</v>
+      </c>
+      <c r="O118">
+        <v>295911</v>
+      </c>
+      <c r="P118" s="2">
+        <v>44819.125</v>
+      </c>
+      <c r="Q118" t="s">
+        <v>60</v>
+      </c>
+      <c r="R118" t="b">
+        <v>0</v>
+      </c>
+      <c r="S118">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T118" t="s">
+        <v>64</v>
+      </c>
+      <c r="U118" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:21">
+      <c r="A119" t="s">
+        <v>37</v>
+      </c>
+      <c r="B119" t="s">
+        <v>38</v>
+      </c>
+      <c r="C119" t="s">
+        <v>39</v>
+      </c>
+      <c r="D119" t="s">
+        <v>40</v>
+      </c>
+      <c r="E119" t="b">
+        <v>1</v>
+      </c>
+      <c r="F119" t="s">
+        <v>41</v>
+      </c>
+      <c r="H119" t="s">
+        <v>48</v>
+      </c>
+      <c r="I119" t="s">
+        <v>52</v>
+      </c>
+      <c r="J119" s="2">
+        <v>44456.22016203704</v>
+      </c>
+      <c r="K119" t="s">
+        <v>55</v>
+      </c>
+      <c r="L119" s="3">
+        <v>-0.001018518518518518</v>
+      </c>
+      <c r="M119">
+        <v>-88</v>
+      </c>
+      <c r="N119" s="3">
+        <v>4.803495370370371</v>
+      </c>
+      <c r="O119">
+        <v>415022</v>
+      </c>
+      <c r="P119" s="2">
+        <v>44456.79166666666</v>
+      </c>
+      <c r="Q119" t="s">
+        <v>62</v>
+      </c>
+      <c r="R119" t="b">
+        <v>0</v>
+      </c>
+      <c r="S119" s="3">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T119" t="s">
+        <v>64</v>
+      </c>
+      <c r="U119" t="b">
         <v>0</v>
       </c>
     </row>

--- a/TOR330 Data/5. Clean Data for Data Visualisation/TOR330_negative_duration_checkpoints_bib_df.xlsx
+++ b/TOR330 Data/5. Clean Data for Data Visualisation/TOR330_negative_duration_checkpoints_bib_df.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="66">
   <si>
     <t>PK</t>
   </si>
@@ -130,13 +130,16 @@
     <t>TOR330_2021_162</t>
   </si>
   <si>
-    <t>2021</t>
+    <t>2024</t>
   </si>
   <si>
     <t>TOR330</t>
   </si>
   <si>
-    <t>162</t>
+    <t>404</t>
+  </si>
+  <si>
+    <t>1367</t>
   </si>
   <si>
     <t>Finished at Courmayeur</t>
@@ -571,7 +574,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X119"/>
+  <dimension ref="A1:X134"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:24">
@@ -665,19 +668,19 @@
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J2" s="2">
         <v>45180.90565972222</v>
       </c>
       <c r="K2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L2">
         <v>-0.05702546296296297</v>
@@ -695,7 +698,7 @@
         <v>45182</v>
       </c>
       <c r="Q2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R2" t="b">
         <v>0</v>
@@ -704,7 +707,7 @@
         <v>0.75</v>
       </c>
       <c r="T2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U2" t="b">
         <v>0</v>
@@ -727,19 +730,19 @@
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J3" s="2">
         <v>45182.46465277778</v>
       </c>
       <c r="K3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L3">
         <v>-0.0003935185185185185</v>
@@ -757,7 +760,7 @@
         <v>45183.04166666666</v>
       </c>
       <c r="Q3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R3" t="b">
         <v>0</v>
@@ -766,7 +769,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U3" t="b">
         <v>0</v>
@@ -789,19 +792,19 @@
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J4" s="2">
         <v>45180.95467592592</v>
       </c>
       <c r="K4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L4">
         <v>-0.0001157407407407407</v>
@@ -819,7 +822,7 @@
         <v>45181.33333333334</v>
       </c>
       <c r="Q4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R4" t="b">
         <v>0</v>
@@ -828,7 +831,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U4" t="b">
         <v>0</v>
@@ -851,19 +854,19 @@
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J5" s="2">
         <v>45183.8446412037</v>
       </c>
       <c r="K5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L5">
         <v>-0.02489583333333333</v>
@@ -881,7 +884,7 @@
         <v>45184.79166666666</v>
       </c>
       <c r="Q5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R5" t="b">
         <v>0</v>
@@ -890,7 +893,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
@@ -913,19 +916,19 @@
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J6" s="2">
         <v>45180.98311342593</v>
       </c>
       <c r="K6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L6">
         <v>-0.0002083333333333333</v>
@@ -943,7 +946,7 @@
         <v>45181.33333333334</v>
       </c>
       <c r="Q6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R6" t="b">
         <v>0</v>
@@ -952,7 +955,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
@@ -975,19 +978,19 @@
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J7" s="2">
         <v>45180.90565972222</v>
       </c>
       <c r="K7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L7">
         <v>-0.05702546296296297</v>
@@ -1005,7 +1008,7 @@
         <v>45182</v>
       </c>
       <c r="Q7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R7" t="b">
         <v>0</v>
@@ -1014,7 +1017,7 @@
         <v>0.75</v>
       </c>
       <c r="T7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
@@ -1037,19 +1040,19 @@
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J8" s="2">
         <v>45182.46465277778</v>
       </c>
       <c r="K8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L8">
         <v>-0.0003935185185185185</v>
@@ -1067,7 +1070,7 @@
         <v>45183.04166666666</v>
       </c>
       <c r="Q8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R8" t="b">
         <v>0</v>
@@ -1076,7 +1079,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
@@ -1099,19 +1102,19 @@
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J9" s="2">
         <v>45180.95467592592</v>
       </c>
       <c r="K9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L9">
         <v>-0.0001157407407407407</v>
@@ -1129,7 +1132,7 @@
         <v>45181.33333333334</v>
       </c>
       <c r="Q9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R9" t="b">
         <v>0</v>
@@ -1138,7 +1141,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U9" t="b">
         <v>0</v>
@@ -1161,19 +1164,19 @@
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J10" s="2">
         <v>45183.8446412037</v>
       </c>
       <c r="K10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L10">
         <v>-0.02489583333333333</v>
@@ -1191,7 +1194,7 @@
         <v>45184.79166666666</v>
       </c>
       <c r="Q10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R10" t="b">
         <v>0</v>
@@ -1200,7 +1203,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U10" t="b">
         <v>0</v>
@@ -1223,19 +1226,19 @@
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J11" s="2">
         <v>45180.98311342593</v>
       </c>
       <c r="K11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L11">
         <v>-0.0002083333333333333</v>
@@ -1253,7 +1256,7 @@
         <v>45181.33333333334</v>
       </c>
       <c r="Q11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R11" t="b">
         <v>0</v>
@@ -1262,7 +1265,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U11" t="b">
         <v>0</v>
@@ -1285,19 +1288,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J12" s="2">
         <v>45180.90565972222</v>
       </c>
       <c r="K12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L12">
         <v>-0.05702546296296297</v>
@@ -1315,7 +1318,7 @@
         <v>45182</v>
       </c>
       <c r="Q12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R12" t="b">
         <v>0</v>
@@ -1324,7 +1327,7 @@
         <v>0.75</v>
       </c>
       <c r="T12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U12" t="b">
         <v>0</v>
@@ -1347,19 +1350,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J13" s="2">
         <v>45182.46465277778</v>
       </c>
       <c r="K13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L13">
         <v>-0.0003935185185185185</v>
@@ -1377,7 +1380,7 @@
         <v>45183.04166666666</v>
       </c>
       <c r="Q13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R13" t="b">
         <v>0</v>
@@ -1386,7 +1389,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U13" t="b">
         <v>0</v>
@@ -1409,19 +1412,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J14" s="2">
         <v>45180.95467592592</v>
       </c>
       <c r="K14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L14">
         <v>-0.0001157407407407407</v>
@@ -1439,7 +1442,7 @@
         <v>45181.33333333334</v>
       </c>
       <c r="Q14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R14" t="b">
         <v>0</v>
@@ -1448,7 +1451,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U14" t="b">
         <v>0</v>
@@ -1471,19 +1474,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J15" s="2">
         <v>45183.8446412037</v>
       </c>
       <c r="K15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L15">
         <v>-0.02489583333333333</v>
@@ -1501,7 +1504,7 @@
         <v>45184.79166666666</v>
       </c>
       <c r="Q15" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R15" t="b">
         <v>0</v>
@@ -1510,7 +1513,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U15" t="b">
         <v>0</v>
@@ -1533,19 +1536,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J16" s="2">
         <v>45180.98311342593</v>
       </c>
       <c r="K16" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L16">
         <v>-0.0002083333333333333</v>
@@ -1563,7 +1566,7 @@
         <v>45181.33333333334</v>
       </c>
       <c r="Q16" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R16" t="b">
         <v>0</v>
@@ -1572,7 +1575,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U16" t="b">
         <v>0</v>
@@ -1595,19 +1598,19 @@
         <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J17" s="2">
         <v>45180.90565972222</v>
       </c>
       <c r="K17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L17">
         <v>-0.05702546296296297</v>
@@ -1625,7 +1628,7 @@
         <v>45182</v>
       </c>
       <c r="Q17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R17" t="b">
         <v>0</v>
@@ -1634,7 +1637,7 @@
         <v>0.75</v>
       </c>
       <c r="T17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U17" t="b">
         <v>0</v>
@@ -1657,19 +1660,19 @@
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I18" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J18" s="2">
         <v>45182.46465277778</v>
       </c>
       <c r="K18" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L18">
         <v>-0.0003935185185185185</v>
@@ -1687,7 +1690,7 @@
         <v>45183.04166666666</v>
       </c>
       <c r="Q18" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R18" t="b">
         <v>0</v>
@@ -1696,7 +1699,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T18" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U18" t="b">
         <v>0</v>
@@ -1719,19 +1722,19 @@
         <v>1</v>
       </c>
       <c r="F19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H19" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I19" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J19" s="2">
         <v>45180.95467592592</v>
       </c>
       <c r="K19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L19">
         <v>-0.0001157407407407407</v>
@@ -1749,7 +1752,7 @@
         <v>45181.33333333334</v>
       </c>
       <c r="Q19" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R19" t="b">
         <v>0</v>
@@ -1758,7 +1761,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T19" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U19" t="b">
         <v>0</v>
@@ -1781,19 +1784,19 @@
         <v>1</v>
       </c>
       <c r="F20" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J20" s="2">
         <v>45183.8446412037</v>
       </c>
       <c r="K20" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L20">
         <v>-0.02489583333333333</v>
@@ -1811,7 +1814,7 @@
         <v>45184.79166666666</v>
       </c>
       <c r="Q20" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R20" t="b">
         <v>0</v>
@@ -1820,7 +1823,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T20" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U20" t="b">
         <v>0</v>
@@ -1843,19 +1846,19 @@
         <v>1</v>
       </c>
       <c r="F21" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I21" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J21" s="2">
         <v>45180.98311342593</v>
       </c>
       <c r="K21" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L21">
         <v>-0.0002083333333333333</v>
@@ -1873,7 +1876,7 @@
         <v>45181.33333333334</v>
       </c>
       <c r="Q21" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R21" t="b">
         <v>0</v>
@@ -1882,7 +1885,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T21" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U21" t="b">
         <v>0</v>
@@ -1905,19 +1908,19 @@
         <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H22" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J22" s="2">
         <v>45546.77756944444</v>
       </c>
       <c r="K22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L22">
         <v>-0.007534722222222222</v>
@@ -1935,7 +1938,7 @@
         <v>45547.875</v>
       </c>
       <c r="Q22" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="R22" t="b">
         <v>0</v>
@@ -1944,7 +1947,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T22" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U22" t="b">
         <v>0</v>
@@ -1967,22 +1970,22 @@
         <v>0</v>
       </c>
       <c r="F23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G23" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I23" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J23" s="2">
         <v>45545.14299768519</v>
       </c>
       <c r="K23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L23">
         <v>-0.0003587962962962963</v>
@@ -2000,7 +2003,7 @@
         <v>45545.33333333334</v>
       </c>
       <c r="Q23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R23" t="b">
         <v>0</v>
@@ -2009,13 +2012,13 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T23" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U23" t="b">
         <v>0</v>
       </c>
       <c r="X23" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:24">
@@ -2035,19 +2038,19 @@
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H24" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J24" s="2">
         <v>44817.39240740741</v>
       </c>
       <c r="K24" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L24">
         <v>-0.003252314814814815</v>
@@ -2065,7 +2068,7 @@
         <v>44819.04166666666</v>
       </c>
       <c r="Q24" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R24" t="b">
         <v>0</v>
@@ -2074,7 +2077,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T24" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U24" t="b">
         <v>0</v>
@@ -2097,19 +2100,19 @@
         <v>1</v>
       </c>
       <c r="F25" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I25" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J25" s="2">
         <v>44818.26855324074</v>
       </c>
       <c r="K25" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L25">
         <v>-0.0005439814814814814</v>
@@ -2127,7 +2130,7 @@
         <v>44819.875</v>
       </c>
       <c r="Q25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="R25" t="b">
         <v>0</v>
@@ -2136,7 +2139,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T25" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U25" t="b">
         <v>0</v>
@@ -2159,19 +2162,19 @@
         <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H26" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I26" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J26" s="2">
         <v>44820.2553125</v>
       </c>
       <c r="K26" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L26">
         <v>-0.0003587962962962963</v>
@@ -2189,7 +2192,7 @@
         <v>44820.79166666666</v>
       </c>
       <c r="Q26" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R26" t="b">
         <v>0</v>
@@ -2198,7 +2201,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T26" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U26" t="b">
         <v>0</v>
@@ -2221,13 +2224,13 @@
         <v>0</v>
       </c>
       <c r="F27" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H27" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I27" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J27" s="2">
         <v>44819.50680555555</v>
@@ -2248,7 +2251,7 @@
         <v>44819.95833333334</v>
       </c>
       <c r="Q27" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="R27" t="b">
         <v>0</v>
@@ -2257,7 +2260,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U27" t="b">
         <v>0</v>
@@ -2280,13 +2283,13 @@
         <v>0</v>
       </c>
       <c r="F28" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H28" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I28" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J28" s="2">
         <v>44818.92413194444</v>
@@ -2307,7 +2310,7 @@
         <v>44819.125</v>
       </c>
       <c r="Q28" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R28" t="b">
         <v>0</v>
@@ -2316,7 +2319,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T28" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U28" t="b">
         <v>0</v>
@@ -2339,13 +2342,13 @@
         <v>0</v>
       </c>
       <c r="F29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J29" s="2">
         <v>44818.92489583333</v>
@@ -2366,7 +2369,7 @@
         <v>44819.125</v>
       </c>
       <c r="Q29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R29" t="b">
         <v>0</v>
@@ -2375,7 +2378,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T29" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U29" t="b">
         <v>0</v>
@@ -2398,19 +2401,19 @@
         <v>1</v>
       </c>
       <c r="F30" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H30" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J30" s="2">
         <v>44456.22016203704</v>
       </c>
       <c r="K30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L30">
         <v>-0.001018518518518518</v>
@@ -2428,7 +2431,7 @@
         <v>44456.79166666666</v>
       </c>
       <c r="Q30" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R30" t="b">
         <v>0</v>
@@ -2437,7 +2440,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T30" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U30" t="b">
         <v>0</v>
@@ -2460,19 +2463,19 @@
         <v>1</v>
       </c>
       <c r="F31" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H31" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J31" s="2">
         <v>45180.90565972222</v>
       </c>
       <c r="K31" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L31">
         <v>-0.05702546296296297</v>
@@ -2490,7 +2493,7 @@
         <v>45182</v>
       </c>
       <c r="Q31" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R31" t="b">
         <v>0</v>
@@ -2499,7 +2502,7 @@
         <v>0.75</v>
       </c>
       <c r="T31" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U31" t="b">
         <v>0</v>
@@ -2522,19 +2525,19 @@
         <v>1</v>
       </c>
       <c r="F32" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H32" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I32" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J32" s="2">
         <v>45182.46465277778</v>
       </c>
       <c r="K32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L32">
         <v>-0.0003935185185185185</v>
@@ -2552,7 +2555,7 @@
         <v>45183.04166666666</v>
       </c>
       <c r="Q32" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R32" t="b">
         <v>0</v>
@@ -2561,7 +2564,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T32" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U32" t="b">
         <v>0</v>
@@ -2584,19 +2587,19 @@
         <v>1</v>
       </c>
       <c r="F33" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H33" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I33" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J33" s="2">
         <v>45180.95467592592</v>
       </c>
       <c r="K33" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L33">
         <v>-0.0001157407407407407</v>
@@ -2614,7 +2617,7 @@
         <v>45181.33333333334</v>
       </c>
       <c r="Q33" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R33" t="b">
         <v>0</v>
@@ -2623,7 +2626,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T33" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U33" t="b">
         <v>0</v>
@@ -2646,19 +2649,19 @@
         <v>1</v>
       </c>
       <c r="F34" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H34" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I34" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J34" s="2">
         <v>45183.8446412037</v>
       </c>
       <c r="K34" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L34">
         <v>-0.02489583333333333</v>
@@ -2676,7 +2679,7 @@
         <v>45184.79166666666</v>
       </c>
       <c r="Q34" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R34" t="b">
         <v>0</v>
@@ -2685,7 +2688,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T34" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U34" t="b">
         <v>0</v>
@@ -2708,19 +2711,19 @@
         <v>1</v>
       </c>
       <c r="F35" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H35" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I35" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J35" s="2">
         <v>45180.98311342593</v>
       </c>
       <c r="K35" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L35">
         <v>-0.0002083333333333333</v>
@@ -2738,7 +2741,7 @@
         <v>45181.33333333334</v>
       </c>
       <c r="Q35" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R35" t="b">
         <v>0</v>
@@ -2747,7 +2750,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T35" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U35" t="b">
         <v>0</v>
@@ -2770,19 +2773,19 @@
         <v>1</v>
       </c>
       <c r="F36" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H36" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I36" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J36" s="2">
         <v>44456.22016203704</v>
       </c>
       <c r="K36" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L36">
         <v>-0.001018518518518518</v>
@@ -2800,7 +2803,7 @@
         <v>44456.79166666666</v>
       </c>
       <c r="Q36" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R36" t="b">
         <v>0</v>
@@ -2809,7 +2812,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T36" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U36" t="b">
         <v>0</v>
@@ -2832,19 +2835,19 @@
         <v>1</v>
       </c>
       <c r="F37" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H37" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I37" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J37" s="2">
         <v>44817.39240740741</v>
       </c>
       <c r="K37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L37">
         <v>-0.003252314814814815</v>
@@ -2862,7 +2865,7 @@
         <v>44819.04166666666</v>
       </c>
       <c r="Q37" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R37" t="b">
         <v>0</v>
@@ -2871,7 +2874,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T37" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U37" t="b">
         <v>0</v>
@@ -2894,19 +2897,19 @@
         <v>1</v>
       </c>
       <c r="F38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H38" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I38" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J38" s="2">
         <v>44818.26855324074</v>
       </c>
       <c r="K38" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L38">
         <v>-0.0005439814814814814</v>
@@ -2924,7 +2927,7 @@
         <v>44819.875</v>
       </c>
       <c r="Q38" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="R38" t="b">
         <v>0</v>
@@ -2933,7 +2936,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T38" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U38" t="b">
         <v>0</v>
@@ -2956,19 +2959,19 @@
         <v>1</v>
       </c>
       <c r="F39" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H39" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I39" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J39" s="2">
         <v>44820.2553125</v>
       </c>
       <c r="K39" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L39">
         <v>-0.0003587962962962963</v>
@@ -2986,7 +2989,7 @@
         <v>44820.79166666666</v>
       </c>
       <c r="Q39" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R39" t="b">
         <v>0</v>
@@ -2995,7 +2998,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T39" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U39" t="b">
         <v>0</v>
@@ -3018,13 +3021,13 @@
         <v>0</v>
       </c>
       <c r="F40" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H40" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I40" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J40" s="2">
         <v>44819.50680555555</v>
@@ -3045,7 +3048,7 @@
         <v>44819.95833333334</v>
       </c>
       <c r="Q40" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="R40" t="b">
         <v>0</v>
@@ -3054,7 +3057,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T40" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U40" t="b">
         <v>0</v>
@@ -3077,13 +3080,13 @@
         <v>0</v>
       </c>
       <c r="F41" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H41" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I41" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J41" s="2">
         <v>44818.92413194444</v>
@@ -3104,7 +3107,7 @@
         <v>44819.125</v>
       </c>
       <c r="Q41" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R41" t="b">
         <v>0</v>
@@ -3113,7 +3116,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T41" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U41" t="b">
         <v>0</v>
@@ -3136,13 +3139,13 @@
         <v>0</v>
       </c>
       <c r="F42" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H42" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I42" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J42" s="2">
         <v>44818.92489583333</v>
@@ -3163,7 +3166,7 @@
         <v>44819.125</v>
       </c>
       <c r="Q42" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R42" t="b">
         <v>0</v>
@@ -3172,7 +3175,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T42" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U42" t="b">
         <v>0</v>
@@ -3195,19 +3198,19 @@
         <v>1</v>
       </c>
       <c r="F43" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H43" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I43" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J43" s="2">
         <v>45180.90565972222</v>
       </c>
       <c r="K43" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L43">
         <v>-0.05702546296296297</v>
@@ -3225,7 +3228,7 @@
         <v>45182</v>
       </c>
       <c r="Q43" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R43" t="b">
         <v>0</v>
@@ -3234,7 +3237,7 @@
         <v>0.75</v>
       </c>
       <c r="T43" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U43" t="b">
         <v>0</v>
@@ -3257,19 +3260,19 @@
         <v>1</v>
       </c>
       <c r="F44" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H44" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I44" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J44" s="2">
         <v>45182.46465277778</v>
       </c>
       <c r="K44" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L44">
         <v>-0.0003935185185185185</v>
@@ -3287,7 +3290,7 @@
         <v>45183.04166666666</v>
       </c>
       <c r="Q44" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R44" t="b">
         <v>0</v>
@@ -3296,7 +3299,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T44" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U44" t="b">
         <v>0</v>
@@ -3319,19 +3322,19 @@
         <v>1</v>
       </c>
       <c r="F45" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H45" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I45" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J45" s="2">
         <v>45180.95467592592</v>
       </c>
       <c r="K45" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L45">
         <v>-0.0001157407407407407</v>
@@ -3349,7 +3352,7 @@
         <v>45181.33333333334</v>
       </c>
       <c r="Q45" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R45" t="b">
         <v>0</v>
@@ -3358,7 +3361,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T45" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U45" t="b">
         <v>0</v>
@@ -3381,19 +3384,19 @@
         <v>1</v>
       </c>
       <c r="F46" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H46" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I46" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J46" s="2">
         <v>45183.8446412037</v>
       </c>
       <c r="K46" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L46">
         <v>-0.02489583333333333</v>
@@ -3411,7 +3414,7 @@
         <v>45184.79166666666</v>
       </c>
       <c r="Q46" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R46" t="b">
         <v>0</v>
@@ -3420,7 +3423,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T46" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U46" t="b">
         <v>0</v>
@@ -3443,19 +3446,19 @@
         <v>1</v>
       </c>
       <c r="F47" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H47" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I47" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J47" s="2">
         <v>45180.98311342593</v>
       </c>
       <c r="K47" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L47">
         <v>-0.0002083333333333333</v>
@@ -3473,7 +3476,7 @@
         <v>45181.33333333334</v>
       </c>
       <c r="Q47" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R47" t="b">
         <v>0</v>
@@ -3482,7 +3485,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T47" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U47" t="b">
         <v>0</v>
@@ -3505,19 +3508,19 @@
         <v>1</v>
       </c>
       <c r="F48" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H48" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I48" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J48" s="2">
         <v>45546.77756944444</v>
       </c>
       <c r="K48" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L48">
         <v>-0.007534722222222222</v>
@@ -3535,7 +3538,7 @@
         <v>45547.875</v>
       </c>
       <c r="Q48" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="R48" t="b">
         <v>0</v>
@@ -3544,7 +3547,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T48" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U48" t="b">
         <v>0</v>
@@ -3567,22 +3570,22 @@
         <v>0</v>
       </c>
       <c r="F49" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G49" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H49" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I49" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J49" s="2">
         <v>45545.14299768519</v>
       </c>
       <c r="K49" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L49">
         <v>-0.0003587962962962963</v>
@@ -3600,7 +3603,7 @@
         <v>45545.33333333334</v>
       </c>
       <c r="Q49" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R49" t="b">
         <v>0</v>
@@ -3609,13 +3612,13 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T49" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U49" t="b">
         <v>0</v>
       </c>
       <c r="X49" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="50" spans="1:24">
@@ -3635,19 +3638,19 @@
         <v>1</v>
       </c>
       <c r="F50" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H50" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I50" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J50" s="2">
         <v>45546.77756944444</v>
       </c>
       <c r="K50" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L50">
         <v>-0.007534722222222222</v>
@@ -3665,7 +3668,7 @@
         <v>45547.875</v>
       </c>
       <c r="Q50" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="R50" t="b">
         <v>0</v>
@@ -3674,7 +3677,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T50" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U50" t="b">
         <v>0</v>
@@ -3697,22 +3700,22 @@
         <v>0</v>
       </c>
       <c r="F51" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G51" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H51" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I51" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J51" s="2">
         <v>45545.14299768519</v>
       </c>
       <c r="K51" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L51">
         <v>-0.0003587962962962963</v>
@@ -3730,7 +3733,7 @@
         <v>45545.33333333334</v>
       </c>
       <c r="Q51" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R51" t="b">
         <v>0</v>
@@ -3739,13 +3742,13 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T51" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U51" t="b">
         <v>0</v>
       </c>
       <c r="X51" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="52" spans="1:24">
@@ -3765,19 +3768,19 @@
         <v>1</v>
       </c>
       <c r="F52" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H52" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I52" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J52" s="2">
         <v>45180.90565972222</v>
       </c>
       <c r="K52" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L52">
         <v>-0.05702546296296297</v>
@@ -3795,7 +3798,7 @@
         <v>45182</v>
       </c>
       <c r="Q52" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R52" t="b">
         <v>0</v>
@@ -3804,7 +3807,7 @@
         <v>0.75</v>
       </c>
       <c r="T52" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U52" t="b">
         <v>0</v>
@@ -3827,19 +3830,19 @@
         <v>1</v>
       </c>
       <c r="F53" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H53" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I53" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J53" s="2">
         <v>45182.46465277778</v>
       </c>
       <c r="K53" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L53">
         <v>-0.0003935185185185185</v>
@@ -3857,7 +3860,7 @@
         <v>45183.04166666666</v>
       </c>
       <c r="Q53" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R53" t="b">
         <v>0</v>
@@ -3866,7 +3869,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T53" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U53" t="b">
         <v>0</v>
@@ -3889,19 +3892,19 @@
         <v>1</v>
       </c>
       <c r="F54" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H54" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I54" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J54" s="2">
         <v>45180.95467592592</v>
       </c>
       <c r="K54" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L54">
         <v>-0.0001157407407407407</v>
@@ -3919,7 +3922,7 @@
         <v>45181.33333333334</v>
       </c>
       <c r="Q54" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R54" t="b">
         <v>0</v>
@@ -3928,7 +3931,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T54" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U54" t="b">
         <v>0</v>
@@ -3951,19 +3954,19 @@
         <v>1</v>
       </c>
       <c r="F55" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H55" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I55" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J55" s="2">
         <v>45183.8446412037</v>
       </c>
       <c r="K55" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L55">
         <v>-0.02489583333333333</v>
@@ -3981,7 +3984,7 @@
         <v>45184.79166666666</v>
       </c>
       <c r="Q55" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R55" t="b">
         <v>0</v>
@@ -3990,7 +3993,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T55" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U55" t="b">
         <v>0</v>
@@ -4013,19 +4016,19 @@
         <v>1</v>
       </c>
       <c r="F56" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H56" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I56" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J56" s="2">
         <v>45180.98311342593</v>
       </c>
       <c r="K56" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L56">
         <v>-0.0002083333333333333</v>
@@ -4043,7 +4046,7 @@
         <v>45181.33333333334</v>
       </c>
       <c r="Q56" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R56" t="b">
         <v>0</v>
@@ -4052,7 +4055,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T56" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U56" t="b">
         <v>0</v>
@@ -4075,19 +4078,19 @@
         <v>1</v>
       </c>
       <c r="F57" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H57" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I57" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J57" s="2">
         <v>44817.39240740741</v>
       </c>
       <c r="K57" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L57">
         <v>-0.003252314814814815</v>
@@ -4105,7 +4108,7 @@
         <v>44819.04166666666</v>
       </c>
       <c r="Q57" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R57" t="b">
         <v>0</v>
@@ -4114,7 +4117,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T57" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U57" t="b">
         <v>0</v>
@@ -4137,19 +4140,19 @@
         <v>1</v>
       </c>
       <c r="F58" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H58" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I58" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J58" s="2">
         <v>44818.26855324074</v>
       </c>
       <c r="K58" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L58">
         <v>-0.0005439814814814814</v>
@@ -4167,7 +4170,7 @@
         <v>44819.875</v>
       </c>
       <c r="Q58" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="R58" t="b">
         <v>0</v>
@@ -4176,7 +4179,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T58" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U58" t="b">
         <v>0</v>
@@ -4199,19 +4202,19 @@
         <v>1</v>
       </c>
       <c r="F59" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H59" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I59" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J59" s="2">
         <v>44820.2553125</v>
       </c>
       <c r="K59" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L59">
         <v>-0.0003587962962962963</v>
@@ -4229,7 +4232,7 @@
         <v>44820.79166666666</v>
       </c>
       <c r="Q59" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R59" t="b">
         <v>0</v>
@@ -4238,7 +4241,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T59" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U59" t="b">
         <v>0</v>
@@ -4261,13 +4264,13 @@
         <v>0</v>
       </c>
       <c r="F60" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H60" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I60" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J60" s="2">
         <v>44819.50680555555</v>
@@ -4288,7 +4291,7 @@
         <v>44819.95833333334</v>
       </c>
       <c r="Q60" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="R60" t="b">
         <v>0</v>
@@ -4297,7 +4300,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T60" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U60" t="b">
         <v>0</v>
@@ -4320,13 +4323,13 @@
         <v>0</v>
       </c>
       <c r="F61" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H61" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I61" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J61" s="2">
         <v>44818.92413194444</v>
@@ -4347,7 +4350,7 @@
         <v>44819.125</v>
       </c>
       <c r="Q61" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R61" t="b">
         <v>0</v>
@@ -4356,7 +4359,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T61" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U61" t="b">
         <v>0</v>
@@ -4379,13 +4382,13 @@
         <v>0</v>
       </c>
       <c r="F62" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H62" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I62" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J62" s="2">
         <v>44818.92489583333</v>
@@ -4406,7 +4409,7 @@
         <v>44819.125</v>
       </c>
       <c r="Q62" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R62" t="b">
         <v>0</v>
@@ -4415,7 +4418,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T62" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U62" t="b">
         <v>0</v>
@@ -4438,19 +4441,19 @@
         <v>1</v>
       </c>
       <c r="F63" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H63" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I63" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J63" s="2">
         <v>44456.22016203704</v>
       </c>
       <c r="K63" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L63">
         <v>-0.001018518518518518</v>
@@ -4468,7 +4471,7 @@
         <v>44456.79166666666</v>
       </c>
       <c r="Q63" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R63" t="b">
         <v>0</v>
@@ -4477,7 +4480,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T63" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U63" t="b">
         <v>0</v>
@@ -4500,19 +4503,19 @@
         <v>1</v>
       </c>
       <c r="F64" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H64" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I64" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J64" s="2">
         <v>44456.22016203704</v>
       </c>
       <c r="K64" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L64">
         <v>-0.001018518518518518</v>
@@ -4530,7 +4533,7 @@
         <v>44456.79166666666</v>
       </c>
       <c r="Q64" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R64" t="b">
         <v>0</v>
@@ -4539,7 +4542,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T64" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U64" t="b">
         <v>0</v>
@@ -4562,19 +4565,19 @@
         <v>1</v>
       </c>
       <c r="F65" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H65" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I65" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J65" s="2">
         <v>44456.22016203704</v>
       </c>
       <c r="K65" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L65">
         <v>-0.001018518518518518</v>
@@ -4592,7 +4595,7 @@
         <v>44456.79166666666</v>
       </c>
       <c r="Q65" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R65" t="b">
         <v>0</v>
@@ -4601,7 +4604,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T65" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U65" t="b">
         <v>0</v>
@@ -4624,19 +4627,19 @@
         <v>1</v>
       </c>
       <c r="F66" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H66" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I66" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J66" s="2">
         <v>44456.22016203704</v>
       </c>
       <c r="K66" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L66">
         <v>-0.001018518518518518</v>
@@ -4654,7 +4657,7 @@
         <v>44456.79166666666</v>
       </c>
       <c r="Q66" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R66" t="b">
         <v>0</v>
@@ -4663,7 +4666,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T66" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U66" t="b">
         <v>0</v>
@@ -4686,19 +4689,19 @@
         <v>1</v>
       </c>
       <c r="F67" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H67" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I67" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J67" s="2">
         <v>44817.39240740741</v>
       </c>
       <c r="K67" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L67">
         <v>-0.003252314814814815</v>
@@ -4716,7 +4719,7 @@
         <v>44819.04166666666</v>
       </c>
       <c r="Q67" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R67" t="b">
         <v>0</v>
@@ -4725,7 +4728,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T67" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U67" t="b">
         <v>0</v>
@@ -4748,19 +4751,19 @@
         <v>1</v>
       </c>
       <c r="F68" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H68" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I68" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J68" s="2">
         <v>44818.26855324074</v>
       </c>
       <c r="K68" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L68">
         <v>-0.0005439814814814814</v>
@@ -4778,7 +4781,7 @@
         <v>44819.875</v>
       </c>
       <c r="Q68" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="R68" t="b">
         <v>0</v>
@@ -4787,7 +4790,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T68" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U68" t="b">
         <v>0</v>
@@ -4810,19 +4813,19 @@
         <v>1</v>
       </c>
       <c r="F69" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H69" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I69" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J69" s="2">
         <v>44820.2553125</v>
       </c>
       <c r="K69" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L69">
         <v>-0.0003587962962962963</v>
@@ -4840,7 +4843,7 @@
         <v>44820.79166666666</v>
       </c>
       <c r="Q69" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R69" t="b">
         <v>0</v>
@@ -4849,7 +4852,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T69" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U69" t="b">
         <v>0</v>
@@ -4872,13 +4875,13 @@
         <v>0</v>
       </c>
       <c r="F70" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H70" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I70" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J70" s="2">
         <v>44819.50680555555</v>
@@ -4899,7 +4902,7 @@
         <v>44819.95833333334</v>
       </c>
       <c r="Q70" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="R70" t="b">
         <v>0</v>
@@ -4908,7 +4911,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T70" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U70" t="b">
         <v>0</v>
@@ -4931,13 +4934,13 @@
         <v>0</v>
       </c>
       <c r="F71" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H71" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I71" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J71" s="2">
         <v>44818.92413194444</v>
@@ -4958,7 +4961,7 @@
         <v>44819.125</v>
       </c>
       <c r="Q71" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R71" t="b">
         <v>0</v>
@@ -4967,7 +4970,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T71" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U71" t="b">
         <v>0</v>
@@ -4990,13 +4993,13 @@
         <v>0</v>
       </c>
       <c r="F72" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H72" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I72" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J72" s="2">
         <v>44818.92489583333</v>
@@ -5017,7 +5020,7 @@
         <v>44819.125</v>
       </c>
       <c r="Q72" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R72" t="b">
         <v>0</v>
@@ -5026,7 +5029,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T72" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U72" t="b">
         <v>0</v>
@@ -5049,19 +5052,19 @@
         <v>1</v>
       </c>
       <c r="F73" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H73" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I73" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J73" s="2">
         <v>45180.90565972222</v>
       </c>
       <c r="K73" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L73">
         <v>-0.05702546296296297</v>
@@ -5079,7 +5082,7 @@
         <v>45182</v>
       </c>
       <c r="Q73" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R73" t="b">
         <v>0</v>
@@ -5088,7 +5091,7 @@
         <v>0.75</v>
       </c>
       <c r="T73" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U73" t="b">
         <v>0</v>
@@ -5111,19 +5114,19 @@
         <v>1</v>
       </c>
       <c r="F74" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H74" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I74" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J74" s="2">
         <v>45182.46465277778</v>
       </c>
       <c r="K74" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L74">
         <v>-0.0003935185185185185</v>
@@ -5141,7 +5144,7 @@
         <v>45183.04166666666</v>
       </c>
       <c r="Q74" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R74" t="b">
         <v>0</v>
@@ -5150,7 +5153,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T74" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U74" t="b">
         <v>0</v>
@@ -5173,19 +5176,19 @@
         <v>1</v>
       </c>
       <c r="F75" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H75" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I75" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J75" s="2">
         <v>45180.95467592592</v>
       </c>
       <c r="K75" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L75">
         <v>-0.0001157407407407407</v>
@@ -5203,7 +5206,7 @@
         <v>45181.33333333334</v>
       </c>
       <c r="Q75" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R75" t="b">
         <v>0</v>
@@ -5212,7 +5215,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T75" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U75" t="b">
         <v>0</v>
@@ -5235,19 +5238,19 @@
         <v>1</v>
       </c>
       <c r="F76" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H76" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I76" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J76" s="2">
         <v>45183.8446412037</v>
       </c>
       <c r="K76" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L76">
         <v>-0.02489583333333333</v>
@@ -5265,7 +5268,7 @@
         <v>45184.79166666666</v>
       </c>
       <c r="Q76" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R76" t="b">
         <v>0</v>
@@ -5274,7 +5277,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T76" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U76" t="b">
         <v>0</v>
@@ -5297,19 +5300,19 @@
         <v>1</v>
       </c>
       <c r="F77" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H77" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I77" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J77" s="2">
         <v>45180.98311342593</v>
       </c>
       <c r="K77" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L77">
         <v>-0.0002083333333333333</v>
@@ -5327,7 +5330,7 @@
         <v>45181.33333333334</v>
       </c>
       <c r="Q77" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R77" t="b">
         <v>0</v>
@@ -5336,7 +5339,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T77" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U77" t="b">
         <v>0</v>
@@ -5359,19 +5362,19 @@
         <v>1</v>
       </c>
       <c r="F78" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H78" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I78" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J78" s="2">
         <v>45546.77756944444</v>
       </c>
       <c r="K78" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L78">
         <v>-0.007534722222222222</v>
@@ -5389,7 +5392,7 @@
         <v>45547.875</v>
       </c>
       <c r="Q78" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="R78" t="b">
         <v>0</v>
@@ -5398,7 +5401,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T78" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U78" t="b">
         <v>0</v>
@@ -5421,22 +5424,22 @@
         <v>0</v>
       </c>
       <c r="F79" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G79" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H79" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I79" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J79" s="2">
         <v>45545.14299768519</v>
       </c>
       <c r="K79" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L79">
         <v>-0.0003587962962962963</v>
@@ -5454,7 +5457,7 @@
         <v>45545.33333333334</v>
       </c>
       <c r="Q79" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R79" t="b">
         <v>0</v>
@@ -5463,13 +5466,13 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T79" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U79" t="b">
         <v>0</v>
       </c>
       <c r="X79" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="80" spans="1:24">
@@ -5489,19 +5492,19 @@
         <v>1</v>
       </c>
       <c r="F80" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H80" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I80" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J80" s="2">
         <v>45546.77756944444</v>
       </c>
       <c r="K80" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L80">
         <v>-0.007534722222222222</v>
@@ -5519,7 +5522,7 @@
         <v>45547.875</v>
       </c>
       <c r="Q80" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="R80" t="b">
         <v>0</v>
@@ -5528,7 +5531,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T80" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U80" t="b">
         <v>0</v>
@@ -5551,22 +5554,22 @@
         <v>0</v>
       </c>
       <c r="F81" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G81" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H81" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I81" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J81" s="2">
         <v>45545.14299768519</v>
       </c>
       <c r="K81" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L81">
         <v>-0.0003587962962962963</v>
@@ -5584,7 +5587,7 @@
         <v>45545.33333333334</v>
       </c>
       <c r="Q81" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R81" t="b">
         <v>0</v>
@@ -5593,13 +5596,13 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T81" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U81" t="b">
         <v>0</v>
       </c>
       <c r="X81" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="82" spans="1:24">
@@ -5619,19 +5622,19 @@
         <v>1</v>
       </c>
       <c r="F82" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H82" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I82" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J82" s="2">
         <v>45180.90565972222</v>
       </c>
       <c r="K82" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L82">
         <v>-0.05702546296296297</v>
@@ -5649,7 +5652,7 @@
         <v>45182</v>
       </c>
       <c r="Q82" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R82" t="b">
         <v>0</v>
@@ -5658,7 +5661,7 @@
         <v>0.75</v>
       </c>
       <c r="T82" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U82" t="b">
         <v>0</v>
@@ -5681,19 +5684,19 @@
         <v>1</v>
       </c>
       <c r="F83" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H83" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I83" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J83" s="2">
         <v>45182.46465277778</v>
       </c>
       <c r="K83" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L83">
         <v>-0.0003935185185185185</v>
@@ -5711,7 +5714,7 @@
         <v>45183.04166666666</v>
       </c>
       <c r="Q83" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R83" t="b">
         <v>0</v>
@@ -5720,7 +5723,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T83" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U83" t="b">
         <v>0</v>
@@ -5743,19 +5746,19 @@
         <v>1</v>
       </c>
       <c r="F84" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H84" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I84" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J84" s="2">
         <v>45180.95467592592</v>
       </c>
       <c r="K84" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L84">
         <v>-0.0001157407407407407</v>
@@ -5773,7 +5776,7 @@
         <v>45181.33333333334</v>
       </c>
       <c r="Q84" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R84" t="b">
         <v>0</v>
@@ -5782,7 +5785,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T84" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U84" t="b">
         <v>0</v>
@@ -5805,19 +5808,19 @@
         <v>1</v>
       </c>
       <c r="F85" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H85" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I85" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J85" s="2">
         <v>45183.8446412037</v>
       </c>
       <c r="K85" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L85">
         <v>-0.02489583333333333</v>
@@ -5835,7 +5838,7 @@
         <v>45184.79166666666</v>
       </c>
       <c r="Q85" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R85" t="b">
         <v>0</v>
@@ -5844,7 +5847,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T85" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U85" t="b">
         <v>0</v>
@@ -5867,19 +5870,19 @@
         <v>1</v>
       </c>
       <c r="F86" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H86" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I86" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J86" s="2">
         <v>45180.98311342593</v>
       </c>
       <c r="K86" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L86">
         <v>-0.0002083333333333333</v>
@@ -5897,7 +5900,7 @@
         <v>45181.33333333334</v>
       </c>
       <c r="Q86" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R86" t="b">
         <v>0</v>
@@ -5906,7 +5909,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T86" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U86" t="b">
         <v>0</v>
@@ -5929,19 +5932,19 @@
         <v>1</v>
       </c>
       <c r="F87" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H87" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I87" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J87" s="2">
         <v>44817.39240740741</v>
       </c>
       <c r="K87" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L87">
         <v>-0.003252314814814815</v>
@@ -5959,7 +5962,7 @@
         <v>44819.04166666666</v>
       </c>
       <c r="Q87" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R87" t="b">
         <v>0</v>
@@ -5968,7 +5971,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T87" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U87" t="b">
         <v>0</v>
@@ -5991,19 +5994,19 @@
         <v>1</v>
       </c>
       <c r="F88" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H88" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I88" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J88" s="2">
         <v>44818.26855324074</v>
       </c>
       <c r="K88" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L88">
         <v>-0.0005439814814814814</v>
@@ -6021,7 +6024,7 @@
         <v>44819.875</v>
       </c>
       <c r="Q88" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="R88" t="b">
         <v>0</v>
@@ -6030,7 +6033,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T88" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U88" t="b">
         <v>0</v>
@@ -6053,19 +6056,19 @@
         <v>1</v>
       </c>
       <c r="F89" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H89" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I89" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J89" s="2">
         <v>44820.2553125</v>
       </c>
       <c r="K89" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L89">
         <v>-0.0003587962962962963</v>
@@ -6083,7 +6086,7 @@
         <v>44820.79166666666</v>
       </c>
       <c r="Q89" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R89" t="b">
         <v>0</v>
@@ -6092,7 +6095,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T89" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U89" t="b">
         <v>0</v>
@@ -6115,13 +6118,13 @@
         <v>0</v>
       </c>
       <c r="F90" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H90" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I90" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J90" s="2">
         <v>44819.50680555555</v>
@@ -6142,7 +6145,7 @@
         <v>44819.95833333334</v>
       </c>
       <c r="Q90" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="R90" t="b">
         <v>0</v>
@@ -6151,7 +6154,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T90" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U90" t="b">
         <v>0</v>
@@ -6174,13 +6177,13 @@
         <v>0</v>
       </c>
       <c r="F91" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H91" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I91" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J91" s="2">
         <v>44818.92413194444</v>
@@ -6201,7 +6204,7 @@
         <v>44819.125</v>
       </c>
       <c r="Q91" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R91" t="b">
         <v>0</v>
@@ -6210,7 +6213,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T91" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U91" t="b">
         <v>0</v>
@@ -6233,13 +6236,13 @@
         <v>0</v>
       </c>
       <c r="F92" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H92" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I92" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J92" s="2">
         <v>44818.92489583333</v>
@@ -6260,7 +6263,7 @@
         <v>44819.125</v>
       </c>
       <c r="Q92" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R92" t="b">
         <v>0</v>
@@ -6269,7 +6272,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T92" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U92" t="b">
         <v>0</v>
@@ -6292,19 +6295,19 @@
         <v>1</v>
       </c>
       <c r="F93" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H93" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I93" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J93" s="2">
         <v>44456.22016203704</v>
       </c>
       <c r="K93" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L93">
         <v>-0.001018518518518518</v>
@@ -6322,7 +6325,7 @@
         <v>44456.79166666666</v>
       </c>
       <c r="Q93" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R93" t="b">
         <v>0</v>
@@ -6331,7 +6334,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T93" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U93" t="b">
         <v>0</v>
@@ -6354,19 +6357,19 @@
         <v>1</v>
       </c>
       <c r="F94" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H94" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I94" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J94" s="2">
         <v>44456.22016203704</v>
       </c>
       <c r="K94" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L94">
         <v>-0.001018518518518518</v>
@@ -6384,7 +6387,7 @@
         <v>44456.79166666666</v>
       </c>
       <c r="Q94" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R94" t="b">
         <v>0</v>
@@ -6393,7 +6396,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T94" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U94" t="b">
         <v>0</v>
@@ -6416,19 +6419,19 @@
         <v>1</v>
       </c>
       <c r="F95" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H95" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I95" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J95" s="2">
         <v>44817.39240740741</v>
       </c>
       <c r="K95" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L95">
         <v>-0.003252314814814815</v>
@@ -6446,7 +6449,7 @@
         <v>44819.04166666666</v>
       </c>
       <c r="Q95" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R95" t="b">
         <v>0</v>
@@ -6455,7 +6458,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T95" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U95" t="b">
         <v>0</v>
@@ -6478,19 +6481,19 @@
         <v>1</v>
       </c>
       <c r="F96" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H96" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I96" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J96" s="2">
         <v>44818.26855324074</v>
       </c>
       <c r="K96" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L96">
         <v>-0.0005439814814814814</v>
@@ -6508,7 +6511,7 @@
         <v>44819.875</v>
       </c>
       <c r="Q96" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="R96" t="b">
         <v>0</v>
@@ -6517,7 +6520,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T96" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U96" t="b">
         <v>0</v>
@@ -6540,19 +6543,19 @@
         <v>1</v>
       </c>
       <c r="F97" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H97" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I97" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J97" s="2">
         <v>44820.2553125</v>
       </c>
       <c r="K97" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L97">
         <v>-0.0003587962962962963</v>
@@ -6570,7 +6573,7 @@
         <v>44820.79166666666</v>
       </c>
       <c r="Q97" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R97" t="b">
         <v>0</v>
@@ -6579,7 +6582,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T97" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U97" t="b">
         <v>0</v>
@@ -6602,13 +6605,13 @@
         <v>0</v>
       </c>
       <c r="F98" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H98" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I98" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J98" s="2">
         <v>44819.50680555555</v>
@@ -6629,7 +6632,7 @@
         <v>44819.95833333334</v>
       </c>
       <c r="Q98" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="R98" t="b">
         <v>0</v>
@@ -6638,7 +6641,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T98" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U98" t="b">
         <v>0</v>
@@ -6661,13 +6664,13 @@
         <v>0</v>
       </c>
       <c r="F99" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H99" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I99" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J99" s="2">
         <v>44818.92413194444</v>
@@ -6688,7 +6691,7 @@
         <v>44819.125</v>
       </c>
       <c r="Q99" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R99" t="b">
         <v>0</v>
@@ -6697,7 +6700,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T99" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U99" t="b">
         <v>0</v>
@@ -6720,13 +6723,13 @@
         <v>0</v>
       </c>
       <c r="F100" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H100" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I100" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J100" s="2">
         <v>44818.92489583333</v>
@@ -6747,7 +6750,7 @@
         <v>44819.125</v>
       </c>
       <c r="Q100" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R100" t="b">
         <v>0</v>
@@ -6756,7 +6759,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T100" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U100" t="b">
         <v>0</v>
@@ -6779,19 +6782,19 @@
         <v>1</v>
       </c>
       <c r="F101" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H101" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I101" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J101" s="2">
         <v>45180.90565972222</v>
       </c>
       <c r="K101" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L101">
         <v>-0.05702546296296297</v>
@@ -6809,7 +6812,7 @@
         <v>45182</v>
       </c>
       <c r="Q101" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R101" t="b">
         <v>0</v>
@@ -6818,7 +6821,7 @@
         <v>0.75</v>
       </c>
       <c r="T101" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U101" t="b">
         <v>0</v>
@@ -6841,19 +6844,19 @@
         <v>1</v>
       </c>
       <c r="F102" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H102" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I102" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J102" s="2">
         <v>45182.46465277778</v>
       </c>
       <c r="K102" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L102">
         <v>-0.0003935185185185185</v>
@@ -6871,7 +6874,7 @@
         <v>45183.04166666666</v>
       </c>
       <c r="Q102" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R102" t="b">
         <v>0</v>
@@ -6880,7 +6883,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T102" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U102" t="b">
         <v>0</v>
@@ -6903,19 +6906,19 @@
         <v>1</v>
       </c>
       <c r="F103" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H103" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I103" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J103" s="2">
         <v>45180.95467592592</v>
       </c>
       <c r="K103" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L103">
         <v>-0.0001157407407407407</v>
@@ -6933,7 +6936,7 @@
         <v>45181.33333333334</v>
       </c>
       <c r="Q103" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R103" t="b">
         <v>0</v>
@@ -6942,7 +6945,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T103" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U103" t="b">
         <v>0</v>
@@ -6965,19 +6968,19 @@
         <v>1</v>
       </c>
       <c r="F104" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H104" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I104" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J104" s="2">
         <v>45183.8446412037</v>
       </c>
       <c r="K104" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L104">
         <v>-0.02489583333333333</v>
@@ -6995,7 +6998,7 @@
         <v>45184.79166666666</v>
       </c>
       <c r="Q104" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R104" t="b">
         <v>0</v>
@@ -7004,7 +7007,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T104" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U104" t="b">
         <v>0</v>
@@ -7027,19 +7030,19 @@
         <v>1</v>
       </c>
       <c r="F105" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H105" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I105" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J105" s="2">
         <v>45180.98311342593</v>
       </c>
       <c r="K105" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L105">
         <v>-0.0002083333333333333</v>
@@ -7057,7 +7060,7 @@
         <v>45181.33333333334</v>
       </c>
       <c r="Q105" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R105" t="b">
         <v>0</v>
@@ -7066,7 +7069,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T105" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U105" t="b">
         <v>0</v>
@@ -7089,19 +7092,19 @@
         <v>1</v>
       </c>
       <c r="F106" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H106" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I106" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J106" s="2">
         <v>45546.77756944444</v>
       </c>
       <c r="K106" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L106">
         <v>-0.007534722222222222</v>
@@ -7119,7 +7122,7 @@
         <v>45547.875</v>
       </c>
       <c r="Q106" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="R106" t="b">
         <v>0</v>
@@ -7128,7 +7131,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T106" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U106" t="b">
         <v>0</v>
@@ -7151,22 +7154,22 @@
         <v>0</v>
       </c>
       <c r="F107" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G107" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H107" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I107" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J107" s="2">
         <v>45545.14299768519</v>
       </c>
       <c r="K107" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L107">
         <v>-0.0003587962962962963</v>
@@ -7184,7 +7187,7 @@
         <v>45545.33333333334</v>
       </c>
       <c r="Q107" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R107" t="b">
         <v>0</v>
@@ -7193,13 +7196,13 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T107" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U107" t="b">
         <v>0</v>
       </c>
       <c r="X107" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="108" spans="1:24">
@@ -7219,19 +7222,19 @@
         <v>1</v>
       </c>
       <c r="F108" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H108" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I108" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J108" s="2">
         <v>45180.90565972222</v>
       </c>
       <c r="K108" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L108">
         <v>-0.05702546296296297</v>
@@ -7249,7 +7252,7 @@
         <v>45182</v>
       </c>
       <c r="Q108" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R108" t="b">
         <v>0</v>
@@ -7258,7 +7261,7 @@
         <v>0.75</v>
       </c>
       <c r="T108" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U108" t="b">
         <v>0</v>
@@ -7281,19 +7284,19 @@
         <v>1</v>
       </c>
       <c r="F109" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H109" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I109" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J109" s="2">
         <v>45182.46465277778</v>
       </c>
       <c r="K109" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L109">
         <v>-0.0003935185185185185</v>
@@ -7311,7 +7314,7 @@
         <v>45183.04166666666</v>
       </c>
       <c r="Q109" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R109" t="b">
         <v>0</v>
@@ -7320,7 +7323,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T109" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U109" t="b">
         <v>0</v>
@@ -7343,19 +7346,19 @@
         <v>1</v>
       </c>
       <c r="F110" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H110" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I110" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J110" s="2">
         <v>45180.95467592592</v>
       </c>
       <c r="K110" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L110">
         <v>-0.0001157407407407407</v>
@@ -7373,7 +7376,7 @@
         <v>45181.33333333334</v>
       </c>
       <c r="Q110" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R110" t="b">
         <v>0</v>
@@ -7382,7 +7385,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T110" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U110" t="b">
         <v>0</v>
@@ -7405,19 +7408,19 @@
         <v>1</v>
       </c>
       <c r="F111" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H111" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I111" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J111" s="2">
         <v>45183.8446412037</v>
       </c>
       <c r="K111" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L111">
         <v>-0.02489583333333333</v>
@@ -7435,7 +7438,7 @@
         <v>45184.79166666666</v>
       </c>
       <c r="Q111" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R111" t="b">
         <v>0</v>
@@ -7444,7 +7447,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T111" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U111" t="b">
         <v>0</v>
@@ -7467,19 +7470,19 @@
         <v>1</v>
       </c>
       <c r="F112" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H112" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I112" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J112" s="2">
         <v>45180.98311342593</v>
       </c>
       <c r="K112" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L112">
         <v>-0.0002083333333333333</v>
@@ -7497,7 +7500,7 @@
         <v>45181.33333333334</v>
       </c>
       <c r="Q112" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R112" t="b">
         <v>0</v>
@@ -7506,7 +7509,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T112" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U112" t="b">
         <v>0</v>
@@ -7529,19 +7532,19 @@
         <v>1</v>
       </c>
       <c r="F113" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H113" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I113" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J113" s="2">
         <v>44817.39240740741</v>
       </c>
       <c r="K113" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L113">
         <v>-0.003252314814814815</v>
@@ -7559,7 +7562,7 @@
         <v>44819.04166666666</v>
       </c>
       <c r="Q113" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R113" t="b">
         <v>0</v>
@@ -7568,7 +7571,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T113" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U113" t="b">
         <v>0</v>
@@ -7591,19 +7594,19 @@
         <v>1</v>
       </c>
       <c r="F114" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H114" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I114" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J114" s="2">
         <v>44818.26855324074</v>
       </c>
       <c r="K114" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L114">
         <v>-0.0005439814814814814</v>
@@ -7621,7 +7624,7 @@
         <v>44819.875</v>
       </c>
       <c r="Q114" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="R114" t="b">
         <v>0</v>
@@ -7630,7 +7633,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T114" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U114" t="b">
         <v>0</v>
@@ -7653,19 +7656,19 @@
         <v>1</v>
       </c>
       <c r="F115" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H115" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I115" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J115" s="2">
         <v>44820.2553125</v>
       </c>
       <c r="K115" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L115">
         <v>-0.0003587962962962963</v>
@@ -7683,7 +7686,7 @@
         <v>44820.79166666666</v>
       </c>
       <c r="Q115" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R115" t="b">
         <v>0</v>
@@ -7692,7 +7695,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T115" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U115" t="b">
         <v>0</v>
@@ -7715,13 +7718,13 @@
         <v>0</v>
       </c>
       <c r="F116" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H116" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I116" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J116" s="2">
         <v>44819.50680555555</v>
@@ -7742,7 +7745,7 @@
         <v>44819.95833333334</v>
       </c>
       <c r="Q116" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="R116" t="b">
         <v>0</v>
@@ -7751,7 +7754,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T116" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U116" t="b">
         <v>0</v>
@@ -7774,13 +7777,13 @@
         <v>0</v>
       </c>
       <c r="F117" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H117" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I117" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J117" s="2">
         <v>44818.92413194444</v>
@@ -7801,7 +7804,7 @@
         <v>44819.125</v>
       </c>
       <c r="Q117" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R117" t="b">
         <v>0</v>
@@ -7810,7 +7813,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T117" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U117" t="b">
         <v>0</v>
@@ -7833,13 +7836,13 @@
         <v>0</v>
       </c>
       <c r="F118" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H118" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I118" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J118" s="2">
         <v>44818.92489583333</v>
@@ -7860,7 +7863,7 @@
         <v>44819.125</v>
       </c>
       <c r="Q118" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R118" t="b">
         <v>0</v>
@@ -7869,7 +7872,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="T118" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U118" t="b">
         <v>0</v>
@@ -7879,40 +7882,40 @@
       <c r="A119" t="s">
         <v>37</v>
       </c>
-      <c r="B119" t="s">
-        <v>38</v>
+      <c r="B119">
+        <v>2021</v>
       </c>
       <c r="C119" t="s">
         <v>39</v>
       </c>
-      <c r="D119" t="s">
-        <v>40</v>
+      <c r="D119">
+        <v>162</v>
       </c>
       <c r="E119" t="b">
         <v>1</v>
       </c>
       <c r="F119" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H119" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I119" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J119" s="2">
         <v>44456.22016203704</v>
       </c>
       <c r="K119" t="s">
-        <v>55</v>
-      </c>
-      <c r="L119" s="3">
+        <v>56</v>
+      </c>
+      <c r="L119">
         <v>-0.001018518518518518</v>
       </c>
       <c r="M119">
         <v>-88</v>
       </c>
-      <c r="N119" s="3">
+      <c r="N119">
         <v>4.803495370370371</v>
       </c>
       <c r="O119">
@@ -7922,19 +7925,946 @@
         <v>44456.79166666666</v>
       </c>
       <c r="Q119" t="s">
+        <v>63</v>
+      </c>
+      <c r="R119" t="b">
+        <v>0</v>
+      </c>
+      <c r="S119">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T119" t="s">
+        <v>65</v>
+      </c>
+      <c r="U119" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:21">
+      <c r="A120" t="s">
+        <v>37</v>
+      </c>
+      <c r="B120">
+        <v>2021</v>
+      </c>
+      <c r="C120" t="s">
+        <v>39</v>
+      </c>
+      <c r="D120">
+        <v>162</v>
+      </c>
+      <c r="E120" t="b">
+        <v>1</v>
+      </c>
+      <c r="F120" t="s">
+        <v>42</v>
+      </c>
+      <c r="H120" t="s">
+        <v>49</v>
+      </c>
+      <c r="I120" t="s">
+        <v>53</v>
+      </c>
+      <c r="J120" s="2">
+        <v>44456.22016203704</v>
+      </c>
+      <c r="K120" t="s">
+        <v>56</v>
+      </c>
+      <c r="L120">
+        <v>-0.001018518518518518</v>
+      </c>
+      <c r="M120">
+        <v>-88</v>
+      </c>
+      <c r="N120">
+        <v>4.803495370370371</v>
+      </c>
+      <c r="O120">
+        <v>415022</v>
+      </c>
+      <c r="P120" s="2">
+        <v>44456.79166666666</v>
+      </c>
+      <c r="Q120" t="s">
+        <v>63</v>
+      </c>
+      <c r="R120" t="b">
+        <v>0</v>
+      </c>
+      <c r="S120">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T120" t="s">
+        <v>65</v>
+      </c>
+      <c r="U120" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:21">
+      <c r="A121" t="s">
+        <v>37</v>
+      </c>
+      <c r="B121">
+        <v>2021</v>
+      </c>
+      <c r="C121" t="s">
+        <v>39</v>
+      </c>
+      <c r="D121">
+        <v>162</v>
+      </c>
+      <c r="E121" t="b">
+        <v>1</v>
+      </c>
+      <c r="F121" t="s">
+        <v>42</v>
+      </c>
+      <c r="H121" t="s">
+        <v>49</v>
+      </c>
+      <c r="I121" t="s">
+        <v>53</v>
+      </c>
+      <c r="J121" s="2">
+        <v>44456.22016203704</v>
+      </c>
+      <c r="K121" t="s">
+        <v>56</v>
+      </c>
+      <c r="L121">
+        <v>-0.001018518518518518</v>
+      </c>
+      <c r="M121">
+        <v>-88</v>
+      </c>
+      <c r="N121">
+        <v>4.803495370370371</v>
+      </c>
+      <c r="O121">
+        <v>415022</v>
+      </c>
+      <c r="P121" s="2">
+        <v>44456.79166666666</v>
+      </c>
+      <c r="Q121" t="s">
+        <v>63</v>
+      </c>
+      <c r="R121" t="b">
+        <v>0</v>
+      </c>
+      <c r="S121">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T121" t="s">
+        <v>65</v>
+      </c>
+      <c r="U121" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:21">
+      <c r="A122" t="s">
+        <v>31</v>
+      </c>
+      <c r="B122">
+        <v>2022</v>
+      </c>
+      <c r="C122" t="s">
+        <v>39</v>
+      </c>
+      <c r="D122">
+        <v>275</v>
+      </c>
+      <c r="E122" t="b">
+        <v>1</v>
+      </c>
+      <c r="F122" t="s">
+        <v>42</v>
+      </c>
+      <c r="H122" t="s">
+        <v>47</v>
+      </c>
+      <c r="I122" t="s">
+        <v>51</v>
+      </c>
+      <c r="J122" s="2">
+        <v>44817.39240740741</v>
+      </c>
+      <c r="K122" t="s">
+        <v>58</v>
+      </c>
+      <c r="L122">
+        <v>-0.003252314814814815</v>
+      </c>
+      <c r="M122">
+        <v>-281</v>
+      </c>
+      <c r="N122">
+        <v>1.975740740740741</v>
+      </c>
+      <c r="O122">
+        <v>170704</v>
+      </c>
+      <c r="P122" s="2">
+        <v>44819.04166666666</v>
+      </c>
+      <c r="Q122" t="s">
+        <v>61</v>
+      </c>
+      <c r="R122" t="b">
+        <v>0</v>
+      </c>
+      <c r="S122">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T122" t="s">
+        <v>65</v>
+      </c>
+      <c r="U122" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:21">
+      <c r="A123" t="s">
+        <v>32</v>
+      </c>
+      <c r="B123">
+        <v>2022</v>
+      </c>
+      <c r="C123" t="s">
+        <v>39</v>
+      </c>
+      <c r="D123">
+        <v>127</v>
+      </c>
+      <c r="E123" t="b">
+        <v>1</v>
+      </c>
+      <c r="F123" t="s">
+        <v>42</v>
+      </c>
+      <c r="H123" t="s">
+        <v>47</v>
+      </c>
+      <c r="I123" t="s">
+        <v>54</v>
+      </c>
+      <c r="J123" s="2">
+        <v>44818.26855324074</v>
+      </c>
+      <c r="K123" t="s">
+        <v>59</v>
+      </c>
+      <c r="L123">
+        <v>-0.0005439814814814814</v>
+      </c>
+      <c r="M123">
+        <v>-47</v>
+      </c>
+      <c r="N123">
+        <v>2.851886574074074</v>
+      </c>
+      <c r="O123">
+        <v>246403</v>
+      </c>
+      <c r="P123" s="2">
+        <v>44819.875</v>
+      </c>
+      <c r="Q123" t="s">
+        <v>64</v>
+      </c>
+      <c r="R123" t="b">
+        <v>0</v>
+      </c>
+      <c r="S123">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T123" t="s">
+        <v>65</v>
+      </c>
+      <c r="U123" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:21">
+      <c r="A124" t="s">
+        <v>33</v>
+      </c>
+      <c r="B124">
+        <v>2022</v>
+      </c>
+      <c r="C124" t="s">
+        <v>39</v>
+      </c>
+      <c r="D124">
+        <v>549</v>
+      </c>
+      <c r="E124" t="b">
+        <v>1</v>
+      </c>
+      <c r="F124" t="s">
+        <v>42</v>
+      </c>
+      <c r="H124" t="s">
+        <v>47</v>
+      </c>
+      <c r="I124" t="s">
+        <v>53</v>
+      </c>
+      <c r="J124" s="2">
+        <v>44820.2553125</v>
+      </c>
+      <c r="K124" t="s">
+        <v>56</v>
+      </c>
+      <c r="L124">
+        <v>-0.0003587962962962963</v>
+      </c>
+      <c r="M124">
+        <v>-31</v>
+      </c>
+      <c r="N124">
+        <v>4.838645833333334</v>
+      </c>
+      <c r="O124">
+        <v>418059</v>
+      </c>
+      <c r="P124" s="2">
+        <v>44820.79166666666</v>
+      </c>
+      <c r="Q124" t="s">
+        <v>63</v>
+      </c>
+      <c r="R124" t="b">
+        <v>0</v>
+      </c>
+      <c r="S124">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T124" t="s">
+        <v>65</v>
+      </c>
+      <c r="U124" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:21">
+      <c r="A125" t="s">
+        <v>34</v>
+      </c>
+      <c r="B125">
+        <v>2022</v>
+      </c>
+      <c r="C125" t="s">
+        <v>39</v>
+      </c>
+      <c r="D125">
+        <v>1005</v>
+      </c>
+      <c r="E125" t="b">
+        <v>0</v>
+      </c>
+      <c r="F125" t="s">
+        <v>44</v>
+      </c>
+      <c r="H125" t="s">
+        <v>48</v>
+      </c>
+      <c r="I125" t="s">
+        <v>54</v>
+      </c>
+      <c r="J125" s="2">
+        <v>44819.50680555555</v>
+      </c>
+      <c r="L125">
+        <v>-0.0002777777777777778</v>
+      </c>
+      <c r="M125">
+        <v>-24</v>
+      </c>
+      <c r="N125">
+        <v>4.006805555555555</v>
+      </c>
+      <c r="O125">
+        <v>346188</v>
+      </c>
+      <c r="P125" s="2">
+        <v>44819.95833333334</v>
+      </c>
+      <c r="Q125" t="s">
+        <v>64</v>
+      </c>
+      <c r="R125" t="b">
+        <v>0</v>
+      </c>
+      <c r="S125">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T125" t="s">
+        <v>65</v>
+      </c>
+      <c r="U125" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:21">
+      <c r="A126" t="s">
+        <v>35</v>
+      </c>
+      <c r="B126">
+        <v>2022</v>
+      </c>
+      <c r="C126" t="s">
+        <v>39</v>
+      </c>
+      <c r="D126">
+        <v>1205</v>
+      </c>
+      <c r="E126" t="b">
+        <v>0</v>
+      </c>
+      <c r="F126" t="s">
+        <v>45</v>
+      </c>
+      <c r="H126" t="s">
+        <v>48</v>
+      </c>
+      <c r="I126" t="s">
+        <v>51</v>
+      </c>
+      <c r="J126" s="2">
+        <v>44818.92413194444</v>
+      </c>
+      <c r="L126">
+        <v>-0.0002199074074074074</v>
+      </c>
+      <c r="M126">
+        <v>-19</v>
+      </c>
+      <c r="N126">
+        <v>3.424131944444444</v>
+      </c>
+      <c r="O126">
+        <v>295845</v>
+      </c>
+      <c r="P126" s="2">
+        <v>44819.125</v>
+      </c>
+      <c r="Q126" t="s">
+        <v>61</v>
+      </c>
+      <c r="R126" t="b">
+        <v>0</v>
+      </c>
+      <c r="S126">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T126" t="s">
+        <v>65</v>
+      </c>
+      <c r="U126" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:21">
+      <c r="A127" t="s">
+        <v>36</v>
+      </c>
+      <c r="B127">
+        <v>2022</v>
+      </c>
+      <c r="C127" t="s">
+        <v>39</v>
+      </c>
+      <c r="D127">
+        <v>1268</v>
+      </c>
+      <c r="E127" t="b">
+        <v>0</v>
+      </c>
+      <c r="F127" t="s">
+        <v>45</v>
+      </c>
+      <c r="H127" t="s">
+        <v>48</v>
+      </c>
+      <c r="I127" t="s">
+        <v>51</v>
+      </c>
+      <c r="J127" s="2">
+        <v>44818.92489583333</v>
+      </c>
+      <c r="L127">
+        <v>-0.0008333333333333334</v>
+      </c>
+      <c r="M127">
+        <v>-72</v>
+      </c>
+      <c r="N127">
+        <v>3.424895833333333</v>
+      </c>
+      <c r="O127">
+        <v>295911</v>
+      </c>
+      <c r="P127" s="2">
+        <v>44819.125</v>
+      </c>
+      <c r="Q127" t="s">
+        <v>61</v>
+      </c>
+      <c r="R127" t="b">
+        <v>0</v>
+      </c>
+      <c r="S127">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T127" t="s">
+        <v>65</v>
+      </c>
+      <c r="U127" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:21">
+      <c r="A128" t="s">
+        <v>24</v>
+      </c>
+      <c r="B128">
+        <v>2023</v>
+      </c>
+      <c r="C128" t="s">
+        <v>39</v>
+      </c>
+      <c r="D128">
+        <v>334</v>
+      </c>
+      <c r="E128" t="b">
+        <v>1</v>
+      </c>
+      <c r="F128" t="s">
+        <v>42</v>
+      </c>
+      <c r="H128" t="s">
+        <v>47</v>
+      </c>
+      <c r="I128" t="s">
+        <v>50</v>
+      </c>
+      <c r="J128" s="2">
+        <v>45180.90565972222</v>
+      </c>
+      <c r="K128" t="s">
+        <v>55</v>
+      </c>
+      <c r="L128">
+        <v>-0.05702546296296297</v>
+      </c>
+      <c r="M128">
+        <v>-4927</v>
+      </c>
+      <c r="N128">
+        <v>1.488993055555556</v>
+      </c>
+      <c r="O128">
+        <v>128649</v>
+      </c>
+      <c r="P128" s="2">
+        <v>45182</v>
+      </c>
+      <c r="Q128" t="s">
+        <v>60</v>
+      </c>
+      <c r="R128" t="b">
+        <v>0</v>
+      </c>
+      <c r="S128">
+        <v>0.75</v>
+      </c>
+      <c r="T128" t="s">
+        <v>65</v>
+      </c>
+      <c r="U128" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:24">
+      <c r="A129" t="s">
+        <v>25</v>
+      </c>
+      <c r="B129">
+        <v>2023</v>
+      </c>
+      <c r="C129" t="s">
+        <v>39</v>
+      </c>
+      <c r="D129">
+        <v>343</v>
+      </c>
+      <c r="E129" t="b">
+        <v>1</v>
+      </c>
+      <c r="F129" t="s">
+        <v>42</v>
+      </c>
+      <c r="H129" t="s">
+        <v>47</v>
+      </c>
+      <c r="I129" t="s">
+        <v>51</v>
+      </c>
+      <c r="J129" s="2">
+        <v>45182.46465277778</v>
+      </c>
+      <c r="K129" t="s">
+        <v>56</v>
+      </c>
+      <c r="L129">
+        <v>-0.0003935185185185185</v>
+      </c>
+      <c r="M129">
+        <v>-34</v>
+      </c>
+      <c r="N129">
+        <v>3.047986111111111</v>
+      </c>
+      <c r="O129">
+        <v>263346</v>
+      </c>
+      <c r="P129" s="2">
+        <v>45183.04166666666</v>
+      </c>
+      <c r="Q129" t="s">
+        <v>61</v>
+      </c>
+      <c r="R129" t="b">
+        <v>0</v>
+      </c>
+      <c r="S129">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T129" t="s">
+        <v>65</v>
+      </c>
+      <c r="U129" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:24">
+      <c r="A130" t="s">
+        <v>26</v>
+      </c>
+      <c r="B130">
+        <v>2023</v>
+      </c>
+      <c r="C130" t="s">
+        <v>39</v>
+      </c>
+      <c r="D130">
+        <v>1291</v>
+      </c>
+      <c r="E130" t="b">
+        <v>1</v>
+      </c>
+      <c r="F130" t="s">
+        <v>42</v>
+      </c>
+      <c r="H130" t="s">
+        <v>48</v>
+      </c>
+      <c r="I130" t="s">
+        <v>52</v>
+      </c>
+      <c r="J130" s="2">
+        <v>45180.95467592592</v>
+      </c>
+      <c r="K130" t="s">
+        <v>57</v>
+      </c>
+      <c r="L130">
+        <v>-0.0001157407407407407</v>
+      </c>
+      <c r="M130">
+        <v>-10</v>
+      </c>
+      <c r="N130">
+        <v>1.454675925925926</v>
+      </c>
+      <c r="O130">
+        <v>125684</v>
+      </c>
+      <c r="P130" s="2">
+        <v>45181.33333333334</v>
+      </c>
+      <c r="Q130" t="s">
         <v>62</v>
       </c>
-      <c r="R119" t="b">
-        <v>0</v>
-      </c>
-      <c r="S119" s="3">
-        <v>0.08333333333333333</v>
-      </c>
-      <c r="T119" t="s">
+      <c r="R130" t="b">
+        <v>0</v>
+      </c>
+      <c r="S130">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T130" t="s">
+        <v>65</v>
+      </c>
+      <c r="U130" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:24">
+      <c r="A131" t="s">
+        <v>27</v>
+      </c>
+      <c r="B131">
+        <v>2023</v>
+      </c>
+      <c r="C131" t="s">
+        <v>39</v>
+      </c>
+      <c r="D131">
+        <v>423</v>
+      </c>
+      <c r="E131" t="b">
+        <v>1</v>
+      </c>
+      <c r="F131" t="s">
+        <v>42</v>
+      </c>
+      <c r="H131" t="s">
+        <v>47</v>
+      </c>
+      <c r="I131" t="s">
+        <v>53</v>
+      </c>
+      <c r="J131" s="2">
+        <v>45183.8446412037</v>
+      </c>
+      <c r="K131" t="s">
+        <v>57</v>
+      </c>
+      <c r="L131">
+        <v>-0.02489583333333333</v>
+      </c>
+      <c r="M131">
+        <v>-2151</v>
+      </c>
+      <c r="N131">
+        <v>4.427974537037037</v>
+      </c>
+      <c r="O131">
+        <v>382577</v>
+      </c>
+      <c r="P131" s="2">
+        <v>45184.79166666666</v>
+      </c>
+      <c r="Q131" t="s">
+        <v>63</v>
+      </c>
+      <c r="R131" t="b">
+        <v>0</v>
+      </c>
+      <c r="S131">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T131" t="s">
+        <v>65</v>
+      </c>
+      <c r="U131" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:24">
+      <c r="A132" t="s">
+        <v>28</v>
+      </c>
+      <c r="B132">
+        <v>2023</v>
+      </c>
+      <c r="C132" t="s">
+        <v>39</v>
+      </c>
+      <c r="D132">
+        <v>1334</v>
+      </c>
+      <c r="E132" t="b">
+        <v>1</v>
+      </c>
+      <c r="F132" t="s">
+        <v>42</v>
+      </c>
+      <c r="H132" t="s">
+        <v>48</v>
+      </c>
+      <c r="I132" t="s">
+        <v>52</v>
+      </c>
+      <c r="J132" s="2">
+        <v>45180.98311342593</v>
+      </c>
+      <c r="K132" t="s">
+        <v>57</v>
+      </c>
+      <c r="L132">
+        <v>-0.0002083333333333333</v>
+      </c>
+      <c r="M132">
+        <v>-18</v>
+      </c>
+      <c r="N132">
+        <v>1.483113425925926</v>
+      </c>
+      <c r="O132">
+        <v>128141</v>
+      </c>
+      <c r="P132" s="2">
+        <v>45181.33333333334</v>
+      </c>
+      <c r="Q132" t="s">
+        <v>62</v>
+      </c>
+      <c r="R132" t="b">
+        <v>0</v>
+      </c>
+      <c r="S132">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T132" t="s">
+        <v>65</v>
+      </c>
+      <c r="U132" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:24">
+      <c r="A133" t="s">
+        <v>29</v>
+      </c>
+      <c r="B133" t="s">
+        <v>38</v>
+      </c>
+      <c r="C133" t="s">
+        <v>39</v>
+      </c>
+      <c r="D133" t="s">
+        <v>40</v>
+      </c>
+      <c r="E133" t="b">
+        <v>1</v>
+      </c>
+      <c r="F133" t="s">
+        <v>42</v>
+      </c>
+      <c r="H133" t="s">
+        <v>47</v>
+      </c>
+      <c r="I133" t="s">
+        <v>54</v>
+      </c>
+      <c r="J133" s="2">
+        <v>45546.77756944444</v>
+      </c>
+      <c r="K133" t="s">
+        <v>55</v>
+      </c>
+      <c r="L133" s="3">
+        <v>-0.007534722222222222</v>
+      </c>
+      <c r="M133">
+        <v>-651</v>
+      </c>
+      <c r="N133" s="3">
+        <v>3.360902777777778</v>
+      </c>
+      <c r="O133">
+        <v>290382</v>
+      </c>
+      <c r="P133" s="2">
+        <v>45547.875</v>
+      </c>
+      <c r="Q133" t="s">
         <v>64</v>
       </c>
-      <c r="U119" t="b">
-        <v>0</v>
+      <c r="R133" t="b">
+        <v>0</v>
+      </c>
+      <c r="S133" s="3">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T133" t="s">
+        <v>65</v>
+      </c>
+      <c r="U133" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:24">
+      <c r="A134" t="s">
+        <v>30</v>
+      </c>
+      <c r="B134" t="s">
+        <v>38</v>
+      </c>
+      <c r="C134" t="s">
+        <v>39</v>
+      </c>
+      <c r="D134" t="s">
+        <v>41</v>
+      </c>
+      <c r="E134" t="b">
+        <v>0</v>
+      </c>
+      <c r="F134" t="s">
+        <v>43</v>
+      </c>
+      <c r="G134" t="s">
+        <v>46</v>
+      </c>
+      <c r="H134" t="s">
+        <v>48</v>
+      </c>
+      <c r="I134" t="s">
+        <v>52</v>
+      </c>
+      <c r="J134" s="2">
+        <v>45545.14299768519</v>
+      </c>
+      <c r="K134" t="s">
+        <v>43</v>
+      </c>
+      <c r="L134" s="3">
+        <v>-0.0003587962962962963</v>
+      </c>
+      <c r="M134">
+        <v>-31</v>
+      </c>
+      <c r="N134" s="3">
+        <v>1.642997685185185</v>
+      </c>
+      <c r="O134">
+        <v>141955</v>
+      </c>
+      <c r="P134" s="2">
+        <v>45545.33333333334</v>
+      </c>
+      <c r="Q134" t="s">
+        <v>62</v>
+      </c>
+      <c r="R134" t="b">
+        <v>0</v>
+      </c>
+      <c r="S134" s="3">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T134" t="s">
+        <v>65</v>
+      </c>
+      <c r="U134" t="b">
+        <v>0</v>
+      </c>
+      <c r="X134" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
